--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>8311</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>11.1499996185303</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>10.9499998092651</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>11.0500001907349</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>10.8999996185303</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -62897,7 +62897,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="D2719" t="n">
-        <v>10.9499998092651</v>
+        <v>10.8999996185303</v>
       </c>
       <c r="E2719" t="n">
         <v>11.0500001907349</v>
@@ -62906,6 +62906,29 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>15291</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>10.9499998092651</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>10.8999996185303</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="G2720" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>8029</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>10.9499998092651</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>10.6499996185303</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>10.6499996185303</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>10.9499998092651</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>34378</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>11.4499998092651</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>10.8000001907349</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>10.9499998092651</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>11.4499998092651</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>23889</v>
+        <v>9672</v>
       </c>
       <c r="C2715" t="n">
-        <v>11.3999996185303</v>
+        <v>11.6499996185303</v>
       </c>
       <c r="D2715" t="n">
-        <v>10.25</v>
+        <v>11.3000001907349</v>
       </c>
       <c r="E2715" t="n">
+        <v>11.5500001907349</v>
+      </c>
+      <c r="F2715" t="n">
         <v>11.3000001907349</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>11</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>6847</v>
+        <v>23889</v>
       </c>
       <c r="C2716" t="n">
-        <v>11.25</v>
+        <v>11.3999996185303</v>
       </c>
       <c r="D2716" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="E2716" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="F2716" t="n">
         <v>11</v>
-      </c>
-      <c r="E2716" t="n">
-        <v>11</v>
-      </c>
-      <c r="F2716" t="n">
-        <v>11.25</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,19 +62842,19 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>7000</v>
+        <v>6847</v>
       </c>
       <c r="C2717" t="n">
-        <v>11.3999996185303</v>
+        <v>11.25</v>
       </c>
       <c r="D2717" t="n">
-        <v>11.1999998092651</v>
+        <v>11</v>
       </c>
       <c r="E2717" t="n">
-        <v>11.3000001907349</v>
+        <v>11</v>
       </c>
       <c r="F2717" t="n">
         <v>11.25</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>11445</v>
+        <v>7000</v>
       </c>
       <c r="C2718" t="n">
         <v>11.3999996185303</v>
       </c>
       <c r="D2718" t="n">
-        <v>10.9499998092651</v>
+        <v>11.1999998092651</v>
       </c>
       <c r="E2718" t="n">
-        <v>11.3500003814697</v>
+        <v>11.3000001907349</v>
       </c>
       <c r="F2718" t="n">
-        <v>10.9499998092651</v>
+        <v>11.25</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>8311</v>
+        <v>11445</v>
       </c>
       <c r="C2719" t="n">
-        <v>11.1499996185303</v>
+        <v>11.3999996185303</v>
       </c>
       <c r="D2719" t="n">
-        <v>10.8999996185303</v>
+        <v>10.9499998092651</v>
       </c>
       <c r="E2719" t="n">
-        <v>11.0500001907349</v>
+        <v>11.3500003814697</v>
       </c>
       <c r="F2719" t="n">
-        <v>10.8999996185303</v>
+        <v>10.9499998092651</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>15291</v>
+        <v>8311</v>
       </c>
       <c r="C2720" t="n">
-        <v>10.9499998092651</v>
+        <v>11.1499996185303</v>
       </c>
       <c r="D2720" t="n">
-        <v>10.5</v>
+        <v>10.8999996185303</v>
       </c>
       <c r="E2720" t="n">
+        <v>11.0500001907349</v>
+      </c>
+      <c r="F2720" t="n">
         <v>10.8999996185303</v>
-      </c>
-      <c r="F2720" t="n">
-        <v>10.75</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>8029</v>
+        <v>15291</v>
       </c>
       <c r="C2721" t="n">
         <v>10.9499998092651</v>
       </c>
       <c r="D2721" t="n">
-        <v>10.6499996185303</v>
+        <v>10.5</v>
       </c>
       <c r="E2721" t="n">
-        <v>10.6499996185303</v>
+        <v>10.8999996185303</v>
       </c>
       <c r="F2721" t="n">
-        <v>10.9499998092651</v>
+        <v>10.75</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>34378</v>
+        <v>8029</v>
       </c>
       <c r="C2722" t="n">
-        <v>11.4499998092651</v>
+        <v>10.9499998092651</v>
       </c>
       <c r="D2722" t="n">
-        <v>10.8000001907349</v>
+        <v>10.6499996185303</v>
       </c>
       <c r="E2722" t="n">
+        <v>10.6499996185303</v>
+      </c>
+      <c r="F2722" t="n">
         <v>10.9499998092651</v>
       </c>
-      <c r="F2722" t="n">
-        <v>11.4499998092651</v>
-      </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>8081</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>11.3500003814697</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -421,7 +421,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G2" t="n">
-        <v>8.21081829071045</v>
+        <v>8.21081733703613</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G3" t="n">
-        <v>8.26118946075439</v>
+        <v>8.26119041442871</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G4" t="n">
-        <v>8.13165950775146</v>
+        <v>8.13165760040283</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>7.98773670196533</v>
+        <v>7.98773717880249</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G6" t="n">
-        <v>8.02371597290039</v>
+        <v>8.02371692657471</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>8.02371597290039</v>
+        <v>8.02371692657471</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G8" t="n">
-        <v>7.97334289550781</v>
+        <v>7.97334337234497</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>7.91577434539795</v>
+        <v>7.91577339172363</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G10" t="n">
-        <v>7.82222318649292</v>
+        <v>7.82222509384155</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10.5</v>
       </c>
       <c r="G11" t="n">
-        <v>7.55596590042114</v>
+        <v>7.55596733093262</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G12" t="n">
-        <v>7.21774625778198</v>
+        <v>7.2177472114563</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G13" t="n">
-        <v>7.34727716445923</v>
+        <v>7.34727811813354</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G14" t="n">
-        <v>7.31129598617554</v>
+        <v>7.3112964630127</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G16" t="n">
-        <v>7.41923999786377</v>
+        <v>7.41924142837524</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G17" t="n">
-        <v>7.43363094329834</v>
+        <v>7.43363285064697</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G18" t="n">
-        <v>7.4480242729187</v>
+        <v>7.44802379608154</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G19" t="n">
-        <v>7.57035875320435</v>
+        <v>7.57035827636719</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>7.30410051345825</v>
+        <v>7.30410194396973</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>7.4480242729187</v>
+        <v>7.44802379608154</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G22" t="n">
-        <v>7.47680950164795</v>
+        <v>7.47680902481079</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G23" t="n">
-        <v>7.40484809875488</v>
+        <v>7.40484666824341</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G24" t="n">
-        <v>7.4480242729187</v>
+        <v>7.44802379608154</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>7.34008169174194</v>
+        <v>7.34008121490479</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>7.31129598617554</v>
+        <v>7.3112964630127</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>7.19615793228149</v>
+        <v>7.19615888595581</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G28" t="n">
-        <v>7.03784275054932</v>
+        <v>7.03784322738647</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>7.23214054107666</v>
+        <v>7.23213958740234</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G30" t="n">
-        <v>7.08461809158325</v>
+        <v>7.08461761474609</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>7.26811981201172</v>
+        <v>7.26812076568604</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>7.26811981201172</v>
+        <v>7.26812076568604</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>7.75026226043701</v>
+        <v>7.75026321411133</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G35" t="n">
-        <v>7.77904844284058</v>
+        <v>7.77904796600342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>7.62792873382568</v>
+        <v>7.62792825698853</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G37" t="n">
-        <v>7.72867393493652</v>
+        <v>7.72867488861084</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G38" t="n">
-        <v>7.69988822937012</v>
+        <v>7.69988918304443</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G39" t="n">
-        <v>7.59194707870483</v>
+        <v>7.59194803237915</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G40" t="n">
-        <v>7.45522022247314</v>
+        <v>7.45521926879883</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>7.54157447814941</v>
+        <v>7.54157400131226</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>7.48400449752808</v>
+        <v>7.48400497436523</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G43" t="n">
-        <v>7.65671300888062</v>
+        <v>7.65671396255493</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G45" t="n">
-        <v>7.66390895843506</v>
+        <v>7.6639084815979</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>7.66390895843506</v>
+        <v>7.6639084815979</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>10.5</v>
       </c>
       <c r="G48" t="n">
-        <v>7.55596590042114</v>
+        <v>7.55596733093262</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>7.62792873382568</v>
+        <v>7.62792825698853</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G50" t="n">
-        <v>7.57755517959595</v>
+        <v>7.57755422592163</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G54" t="n">
-        <v>7.5631628036499</v>
+        <v>7.56316184997559</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>7.59194707870483</v>
+        <v>7.59194803237915</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G58" t="n">
-        <v>7.57755517959595</v>
+        <v>7.57755422592163</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G59" t="n">
-        <v>7.50559377670288</v>
+        <v>7.50559329986572</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G60" t="n">
-        <v>7.49119997024536</v>
+        <v>7.49120044708252</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G61" t="n">
-        <v>7.45522022247314</v>
+        <v>7.45521926879883</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>7.48400449752808</v>
+        <v>7.48400497436523</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>7.41204357147217</v>
+        <v>7.41204404830933</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G64" t="n">
-        <v>7.34008169174194</v>
+        <v>7.34008121490479</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>7.41204357147217</v>
+        <v>7.41204404830933</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>7.30410051345825</v>
+        <v>7.30410194396973</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G70" t="n">
-        <v>7.34008169174194</v>
+        <v>7.34008121490479</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G71" t="n">
-        <v>7.31849336624146</v>
+        <v>7.31849384307861</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G72" t="n">
-        <v>7.43363094329834</v>
+        <v>7.43363285064697</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G74" t="n">
-        <v>7.20335483551025</v>
+        <v>7.20335578918457</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>7.34008169174194</v>
+        <v>7.34008121490479</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G78" t="n">
-        <v>7.31129598617554</v>
+        <v>7.3112964630127</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G80" t="n">
-        <v>7.41923999786377</v>
+        <v>7.41924142837524</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G81" t="n">
-        <v>7.42643594741821</v>
+        <v>7.42643547058105</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>7.41204357147217</v>
+        <v>7.41204404830933</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G83" t="n">
-        <v>7.16017818450928</v>
+        <v>7.1601767539978</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>10.25</v>
       </c>
       <c r="G84" t="n">
-        <v>7.37606239318848</v>
+        <v>7.37606143951416</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.95499992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>7.16377639770508</v>
+        <v>7.16377592086792</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.99499988555908</v>
       </c>
       <c r="G88" t="n">
-        <v>7.19255971908569</v>
+        <v>7.19256067276001</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.96500015258789</v>
       </c>
       <c r="G89" t="n">
-        <v>7.17097139358521</v>
+        <v>7.17097091674805</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>10</v>
       </c>
       <c r="G90" t="n">
-        <v>7.19615793228149</v>
+        <v>7.19615888595581</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>7.23214054107666</v>
+        <v>7.23213958740234</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G92" t="n">
-        <v>7.26811981201172</v>
+        <v>7.26812076568604</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.89500045776367</v>
       </c>
       <c r="G94" t="n">
-        <v>7.12059926986694</v>
+        <v>7.12059831619263</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>7.06662654876709</v>
+        <v>7.06662797927856</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G98" t="n">
-        <v>6.98027324676514</v>
+        <v>6.98027420043945</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G100" t="n">
-        <v>7.20962762832642</v>
+        <v>7.20962810516357</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G101" t="n">
-        <v>7.48197555541992</v>
+        <v>7.48197603225708</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G102" t="n">
-        <v>7.4290189743042</v>
+        <v>7.42901945114136</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>7.43658494949341</v>
+        <v>7.43658542633057</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>7.5349326133728</v>
+        <v>7.53493165969849</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G106" t="n">
-        <v>7.43658494949341</v>
+        <v>7.43658542633057</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G109" t="n">
-        <v>7.27014970779419</v>
+        <v>7.27015066146851</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G110" t="n">
-        <v>7.20962762832642</v>
+        <v>7.20962810516357</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G111" t="n">
-        <v>7.36849784851074</v>
+        <v>7.36849689483643</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G112" t="n">
-        <v>7.2625846862793</v>
+        <v>7.26258516311646</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>7.22475814819336</v>
+        <v>7.22475910186768</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G114" t="n">
-        <v>7.2625846862793</v>
+        <v>7.26258516311646</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.5</v>
       </c>
       <c r="G115" t="n">
-        <v>7.18693256378174</v>
+        <v>7.18693351745605</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.5</v>
       </c>
       <c r="G116" t="n">
-        <v>7.18693256378174</v>
+        <v>7.18693351745605</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G117" t="n">
-        <v>6.98267269134521</v>
+        <v>6.98267316818237</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G118" t="n">
-        <v>6.63845539093018</v>
+        <v>6.63845586776733</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G119" t="n">
-        <v>6.78597736358643</v>
+        <v>6.78597784042358</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G120" t="n">
-        <v>6.92971658706665</v>
+        <v>6.92971706390381</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.5</v>
       </c>
       <c r="G122" t="n">
-        <v>7.18693256378174</v>
+        <v>7.18693351745605</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.5</v>
       </c>
       <c r="G123" t="n">
-        <v>7.18693256378174</v>
+        <v>7.18693351745605</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G127" t="n">
-        <v>7.04319381713867</v>
+        <v>7.04319524765015</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G128" t="n">
-        <v>7.16045475006104</v>
+        <v>7.16045427322388</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G129" t="n">
-        <v>7.06210660934448</v>
+        <v>7.0621075630188</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G130" t="n">
-        <v>7.07345533370972</v>
+        <v>7.07345581054688</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9</v>
       </c>
       <c r="G135" t="n">
-        <v>6.8086724281311</v>
+        <v>6.80867385864258</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G136" t="n">
-        <v>6.85406541824341</v>
+        <v>6.85406494140625</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9</v>
       </c>
       <c r="G137" t="n">
-        <v>6.8086724281311</v>
+        <v>6.80867385864258</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>6.81245565414429</v>
+        <v>6.81245613098145</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G139" t="n">
-        <v>6.92971658706665</v>
+        <v>6.92971706390381</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G140" t="n">
-        <v>6.90702152252197</v>
+        <v>6.90702056884766</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G142" t="n">
-        <v>6.9221510887146</v>
+        <v>6.92215061187744</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G143" t="n">
-        <v>6.89567279815674</v>
+        <v>6.89567232131958</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G145" t="n">
-        <v>6.9486289024353</v>
+        <v>6.94862937927246</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G147" t="n">
-        <v>6.88810729980469</v>
+        <v>6.88810777664185</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G149" t="n">
-        <v>6.91080379486084</v>
+        <v>6.91080331802368</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G150" t="n">
-        <v>7.0129337310791</v>
+        <v>7.01293325424194</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G151" t="n">
-        <v>6.81245565414429</v>
+        <v>6.81245613098145</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G152" t="n">
-        <v>6.91458559036255</v>
+        <v>6.91458654403687</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G153" t="n">
-        <v>6.91458559036255</v>
+        <v>6.91458654403687</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G154" t="n">
-        <v>6.91458559036255</v>
+        <v>6.91458654403687</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>6.86919450759888</v>
+        <v>6.86919546127319</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G156" t="n">
-        <v>6.94484710693359</v>
+        <v>6.94484663009644</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>6.90702152252197</v>
+        <v>6.90702056884766</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G159" t="n">
-        <v>6.90702152252197</v>
+        <v>6.90702056884766</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G161" t="n">
-        <v>6.88054227828979</v>
+        <v>6.88054275512695</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G162" t="n">
-        <v>6.91458559036255</v>
+        <v>6.91458654403687</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>6.9334979057312</v>
+        <v>6.93349885940552</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G164" t="n">
-        <v>6.9334979057312</v>
+        <v>6.93349885940552</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G165" t="n">
-        <v>6.94484710693359</v>
+        <v>6.94484663009644</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G166" t="n">
-        <v>6.94484710693359</v>
+        <v>6.94484663009644</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G167" t="n">
-        <v>6.97510814666748</v>
+        <v>6.97510766983032</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.25</v>
       </c>
       <c r="G168" t="n">
-        <v>6.99780368804932</v>
+        <v>6.99780225753784</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.25</v>
       </c>
       <c r="G169" t="n">
-        <v>6.99780368804932</v>
+        <v>6.99780225753784</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G170" t="n">
-        <v>6.99023723602295</v>
+        <v>6.99023675918579</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.25</v>
       </c>
       <c r="G171" t="n">
-        <v>6.99780368804932</v>
+        <v>6.99780225753784</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.25</v>
       </c>
       <c r="G172" t="n">
-        <v>6.99780368804932</v>
+        <v>6.99780225753784</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G173" t="n">
-        <v>6.94106435775757</v>
+        <v>6.94106483459473</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.25</v>
       </c>
       <c r="G174" t="n">
-        <v>6.99780368804932</v>
+        <v>6.99780225753784</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>6.9486289024353</v>
+        <v>6.94862937927246</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G176" t="n">
-        <v>6.86919450759888</v>
+        <v>6.86919546127319</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>6.86919450759888</v>
+        <v>6.86919546127319</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G178" t="n">
-        <v>6.82380342483521</v>
+        <v>6.82380437850952</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>8.875</v>
       </c>
       <c r="G180" t="n">
-        <v>6.71410799026489</v>
+        <v>6.71410894393921</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>6.6573691368103</v>
+        <v>6.65736961364746</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>6.64602136611938</v>
+        <v>6.64602088928223</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9</v>
       </c>
       <c r="G183" t="n">
-        <v>6.8086724281311</v>
+        <v>6.80867385864258</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G186" t="n">
-        <v>6.88054227828979</v>
+        <v>6.88054275512695</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G188" t="n">
-        <v>6.91080379486084</v>
+        <v>6.91080331802368</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G189" t="n">
-        <v>6.85784721374512</v>
+        <v>6.85784673690796</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G190" t="n">
-        <v>6.64602136611938</v>
+        <v>6.64602088928223</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G191" t="n">
-        <v>6.82380342483521</v>
+        <v>6.82380437850952</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G192" t="n">
-        <v>6.84271717071533</v>
+        <v>6.84271621704102</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G195" t="n">
-        <v>6.86162900924683</v>
+        <v>6.8616304397583</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G196" t="n">
-        <v>6.86162900924683</v>
+        <v>6.8616304397583</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G197" t="n">
-        <v>6.76328277587891</v>
+        <v>6.76328134536743</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G198" t="n">
-        <v>6.85784721374512</v>
+        <v>6.85784673690796</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G199" t="n">
-        <v>6.88054227828979</v>
+        <v>6.88054275512695</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G200" t="n">
-        <v>6.85406541824341</v>
+        <v>6.85406494140625</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G201" t="n">
-        <v>6.77841234207153</v>
+        <v>6.77841281890869</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>8.95499992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>6.77463006973267</v>
+        <v>6.77462911605835</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9</v>
       </c>
       <c r="G203" t="n">
-        <v>6.8086724281311</v>
+        <v>6.80867385864258</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G204" t="n">
-        <v>6.73302030563354</v>
+        <v>6.73302125930786</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G205" t="n">
-        <v>6.73302030563354</v>
+        <v>6.73302125930786</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G206" t="n">
-        <v>6.75571632385254</v>
+        <v>6.7557168006897</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9</v>
       </c>
       <c r="G208" t="n">
-        <v>6.8086724281311</v>
+        <v>6.80867385864258</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G209" t="n">
-        <v>6.81245565414429</v>
+        <v>6.81245613098145</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G210" t="n">
-        <v>6.81245565414429</v>
+        <v>6.81245613098145</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G211" t="n">
-        <v>6.78976058959961</v>
+        <v>6.78976011276245</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>6.77841234207153</v>
+        <v>6.77841281890869</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>8.92500019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>6.75193405151367</v>
+        <v>6.75193357467651</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>8.94499969482422</v>
       </c>
       <c r="G217" t="n">
-        <v>6.7670636177063</v>
+        <v>6.76706409454346</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G218" t="n">
-        <v>6.73302030563354</v>
+        <v>6.73302125930786</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G219" t="n">
-        <v>6.73302030563354</v>
+        <v>6.73302125930786</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G220" t="n">
-        <v>6.82380342483521</v>
+        <v>6.82380437850952</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>9</v>
       </c>
       <c r="G222" t="n">
-        <v>6.8086724281311</v>
+        <v>6.80867385864258</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G224" t="n">
-        <v>6.76328277587891</v>
+        <v>6.76328134536743</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G225" t="n">
-        <v>6.76328277587891</v>
+        <v>6.76328134536743</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G227" t="n">
-        <v>6.9221510887146</v>
+        <v>6.92215061187744</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G228" t="n">
-        <v>6.87675952911377</v>
+        <v>6.87676048278809</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G229" t="n">
-        <v>6.78597736358643</v>
+        <v>6.78597784042358</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G231" t="n">
-        <v>6.76328277587891</v>
+        <v>6.76328134536743</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>8.75</v>
       </c>
       <c r="G232" t="n">
-        <v>6.61954307556152</v>
+        <v>6.61954355239868</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>6.64980459213257</v>
+        <v>6.64980411529541</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.6573691368103</v>
+        <v>6.65736961364746</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>6.6573691368103</v>
+        <v>6.65736961364746</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G237" t="n">
-        <v>6.63467454910278</v>
+        <v>6.63467311859131</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G238" t="n">
-        <v>6.63467454910278</v>
+        <v>6.63467311859131</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>6.6573691368103</v>
+        <v>6.65736961364746</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>6.65358781814575</v>
+        <v>6.65358591079712</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>6.68006372451782</v>
+        <v>6.68006467819214</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>6.68006372451782</v>
+        <v>6.68006467819214</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G243" t="n">
-        <v>6.85406541824341</v>
+        <v>6.85406494140625</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G244" t="n">
-        <v>6.91080379486084</v>
+        <v>6.91080331802368</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G245" t="n">
-        <v>6.91080379486084</v>
+        <v>6.91080331802368</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>6.84649896621704</v>
+        <v>6.84649991989136</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>9.25</v>
       </c>
       <c r="G248" t="n">
-        <v>6.99780368804932</v>
+        <v>6.99780225753784</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G249" t="n">
-        <v>7.14154052734375</v>
+        <v>7.14154100418091</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G252" t="n">
-        <v>7.48197555541992</v>
+        <v>7.48197603225708</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>9.875</v>
       </c>
       <c r="G253" t="n">
-        <v>7.47062683105469</v>
+        <v>7.47062730789185</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G254" t="n">
-        <v>7.59545230865479</v>
+        <v>7.5954532623291</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G255" t="n">
-        <v>7.59545230865479</v>
+        <v>7.5954532623291</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>7.86779928207397</v>
+        <v>7.86780023574829</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>7.82997465133667</v>
+        <v>7.82997369766235</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.25</v>
       </c>
       <c r="G260" t="n">
-        <v>7.75432300567627</v>
+        <v>7.75432109832764</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G261" t="n">
-        <v>7.86023426055908</v>
+        <v>7.8602352142334</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>7.86779928207397</v>
+        <v>7.86780023574829</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G265" t="n">
-        <v>7.8375391960144</v>
+        <v>7.83753824234009</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G266" t="n">
-        <v>7.86779928207397</v>
+        <v>7.86780023574829</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G267" t="n">
-        <v>7.86023426055908</v>
+        <v>7.8602352142334</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G268" t="n">
-        <v>7.86023426055908</v>
+        <v>7.8602352142334</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G270" t="n">
-        <v>8.20066833496094</v>
+        <v>8.20066738128662</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G273" t="n">
-        <v>8.01153945922852</v>
+        <v>8.0115385055542</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G274" t="n">
-        <v>8.04936408996582</v>
+        <v>8.04936599731445</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G278" t="n">
-        <v>7.92075681686401</v>
+        <v>7.92075777053833</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G279" t="n">
-        <v>7.8451042175293</v>
+        <v>7.84510326385498</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G281" t="n">
-        <v>7.95858383178711</v>
+        <v>7.95858192443848</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G282" t="n">
-        <v>8.01153945922852</v>
+        <v>8.0115385055542</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.5</v>
       </c>
       <c r="G284" t="n">
-        <v>7.94345188140869</v>
+        <v>7.94345283508301</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G287" t="n">
-        <v>8.01153945922852</v>
+        <v>8.0115385055542</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G289" t="n">
-        <v>8.00397396087646</v>
+        <v>8.00397300720215</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G296" t="n">
-        <v>7.98884296417236</v>
+        <v>7.98884391784668</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G300" t="n">
-        <v>8.10988521575928</v>
+        <v>8.10988616943359</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G301" t="n">
-        <v>8.26875591278076</v>
+        <v>8.26875686645508</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G302" t="n">
-        <v>8.38223361968994</v>
+        <v>8.38223266601562</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G303" t="n">
-        <v>8.51840686798096</v>
+        <v>8.51840782165527</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G305" t="n">
-        <v>8.85127544403076</v>
+        <v>8.85127449035645</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G306" t="n">
-        <v>8.91936111450195</v>
+        <v>8.91936206817627</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G307" t="n">
-        <v>8.88153457641602</v>
+        <v>8.88153648376465</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G310" t="n">
-        <v>8.86640548706055</v>
+        <v>8.86640644073486</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G311" t="n">
-        <v>8.9117956161499</v>
+        <v>8.91179656982422</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G312" t="n">
-        <v>8.97988510131836</v>
+        <v>8.97988224029541</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>9.15388298034668</v>
+        <v>9.15388202667236</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>9.34301280975342</v>
+        <v>9.34301376342773</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G317" t="n">
-        <v>10.0465755462646</v>
+        <v>10.0465745925903</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>13.25</v>
       </c>
       <c r="G318" t="n">
-        <v>10.0238809585571</v>
+        <v>10.0238790512085</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G319" t="n">
-        <v>9.86501121520996</v>
+        <v>9.86501026153564</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G321" t="n">
-        <v>9.72883701324463</v>
+        <v>9.72883796691895</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G326" t="n">
-        <v>9.74396705627441</v>
+        <v>9.74396800994873</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G327" t="n">
-        <v>9.63805675506592</v>
+        <v>9.63805484771729</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G336" t="n">
-        <v>9.60779285430908</v>
+        <v>9.60779476165771</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>9.72883701324463</v>
+        <v>9.72883796691895</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G339" t="n">
-        <v>9.98605442047119</v>
+        <v>9.98605346679688</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G340" t="n">
-        <v>9.8877067565918</v>
+        <v>9.88770580291748</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G342" t="n">
-        <v>10.0163145065308</v>
+        <v>10.0163135528564</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G343" t="n">
-        <v>10.1222276687622</v>
+        <v>10.1222267150879</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G344" t="n">
-        <v>10.1978797912598</v>
+        <v>10.1978788375854</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G348" t="n">
-        <v>10.8711824417114</v>
+        <v>10.8711805343628</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G349" t="n">
-        <v>11.5596132278442</v>
+        <v>11.5596141815186</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G351" t="n">
-        <v>11.5520496368408</v>
+        <v>11.5520505905151</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G352" t="n">
-        <v>11.2040510177612</v>
+        <v>11.2040500640869</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G353" t="n">
-        <v>11.1964836120605</v>
+        <v>11.1964855194092</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>16</v>
       </c>
       <c r="G355" t="n">
-        <v>12.1043071746826</v>
+        <v>12.1043090820312</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G356" t="n">
-        <v>12.021089553833</v>
+        <v>12.0210905075073</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G357" t="n">
-        <v>12.1496982574463</v>
+        <v>12.1496992111206</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>16</v>
       </c>
       <c r="G359" t="n">
-        <v>12.1043071746826</v>
+        <v>12.1043090820312</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G360" t="n">
-        <v>11.9561233520508</v>
+        <v>11.9561243057251</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G361" t="n">
-        <v>12.1277046203613</v>
+        <v>12.12770652771</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G362" t="n">
-        <v>12.314884185791</v>
+        <v>12.3148851394653</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G364" t="n">
-        <v>12.3850784301758</v>
+        <v>12.3850774765015</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>12.4006767272949</v>
+        <v>12.4006748199463</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G367" t="n">
-        <v>12.2758884429932</v>
+        <v>12.2758893966675</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G368" t="n">
-        <v>12.1199054718018</v>
+        <v>12.1199064254761</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G370" t="n">
-        <v>11.0436201095581</v>
+        <v>11.0436210632324</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G371" t="n">
-        <v>11.3555879592896</v>
+        <v>11.3555870056152</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G372" t="n">
-        <v>11.293194770813</v>
+        <v>11.2931938171387</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G373" t="n">
-        <v>11.4179801940918</v>
+        <v>11.4179811477661</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G374" t="n">
-        <v>11.4335794448853</v>
+        <v>11.4335784912109</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G377" t="n">
-        <v>11.6285581588745</v>
+        <v>11.6285572052002</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>14.75</v>
       </c>
       <c r="G378" t="n">
-        <v>11.5037717819214</v>
+        <v>11.5037727355957</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>11.5427665710449</v>
+        <v>11.5427656173706</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.5817623138428</v>
+        <v>11.5817632675171</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G382" t="n">
-        <v>11.4803743362427</v>
+        <v>11.480375289917</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>10.9968271255493</v>
+        <v>10.996826171875</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G387" t="n">
-        <v>11.1060123443604</v>
+        <v>11.106014251709</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>14.5</v>
       </c>
       <c r="G388" t="n">
-        <v>11.3087921142578</v>
+        <v>11.3087940216064</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G389" t="n">
-        <v>11.4023818969727</v>
+        <v>11.402382850647</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G390" t="n">
-        <v>11.6285581588745</v>
+        <v>11.6285572052002</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G393" t="n">
-        <v>11.6597557067871</v>
+        <v>11.6597547531128</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G394" t="n">
-        <v>11.5739641189575</v>
+        <v>11.5739650726318</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>15</v>
       </c>
       <c r="G397" t="n">
-        <v>11.698751449585</v>
+        <v>11.6987504959106</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G399" t="n">
-        <v>11.5739641189575</v>
+        <v>11.5739650726318</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G400" t="n">
-        <v>11.4803743362427</v>
+        <v>11.480375289917</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G401" t="n">
-        <v>11.644157409668</v>
+        <v>11.6441564559937</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G403" t="n">
-        <v>11.7455463409424</v>
+        <v>11.7455472946167</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G407" t="n">
-        <v>11.6597557067871</v>
+        <v>11.6597547531128</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>12.3616800308228</v>
+        <v>12.3616790771484</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>12.3616800308228</v>
+        <v>12.3616790771484</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G412" t="n">
-        <v>12.4708671569824</v>
+        <v>12.4708681106567</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>12.3226842880249</v>
+        <v>12.3226852416992</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G415" t="n">
-        <v>12.2056970596313</v>
+        <v>12.205696105957</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>12.2056970596313</v>
+        <v>12.205696105957</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G418" t="n">
-        <v>12.2446928024292</v>
+        <v>12.2446908950806</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G419" t="n">
-        <v>12.3226842880249</v>
+        <v>12.3226852416992</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G420" t="n">
-        <v>12.447470664978</v>
+        <v>12.4474716186523</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>13.1181983947754</v>
+        <v>13.1181974411011</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G423" t="n">
-        <v>13.3521738052368</v>
+        <v>13.3521747589111</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G425" t="n">
-        <v>13.180591583252</v>
+        <v>13.1805934906006</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G426" t="n">
-        <v>13.2429847717285</v>
+        <v>13.2429857254028</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>17</v>
       </c>
       <c r="G427" t="n">
-        <v>13.2585849761963</v>
+        <v>13.258584022522</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G428" t="n">
-        <v>13.4379663467407</v>
+        <v>13.4379653930664</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G429" t="n">
-        <v>13.4457635879517</v>
+        <v>13.4457626342773</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G430" t="n">
-        <v>13.5939483642578</v>
+        <v>13.5939474105835</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G431" t="n">
-        <v>13.5705490112305</v>
+        <v>13.5705509185791</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G432" t="n">
-        <v>13.6407432556152</v>
+        <v>13.6407442092896</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>15.1693782806396</v>
+        <v>15.1693811416626</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G441" t="n">
-        <v>14.8652114868164</v>
+        <v>14.8652124404907</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G442" t="n">
-        <v>15.192777633667</v>
+        <v>15.1927757263184</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>19.5</v>
       </c>
       <c r="G443" t="n">
-        <v>15.2083759307861</v>
+        <v>15.2083749771118</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G444" t="n">
-        <v>14.873010635376</v>
+        <v>14.8730125427246</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>20.6200008392334</v>
       </c>
       <c r="G447" t="n">
-        <v>16.0818843841553</v>
+        <v>16.0818824768066</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G448" t="n">
-        <v>16.2534637451172</v>
+        <v>16.2534675598145</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G449" t="n">
-        <v>16.6902160644531</v>
+        <v>16.6902198791504</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G450" t="n">
-        <v>16.3392562866211</v>
+        <v>16.3392543792725</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G451" t="n">
-        <v>17.3297500610352</v>
+        <v>17.3297481536865</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>21.6900005340576</v>
       </c>
       <c r="G452" t="n">
-        <v>16.9163932800293</v>
+        <v>16.9163913726807</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G455" t="n">
-        <v>17.3765468597412</v>
+        <v>17.3765449523926</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G456" t="n">
-        <v>17.5403251647949</v>
+        <v>17.5403289794922</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G457" t="n">
-        <v>17.6495151519775</v>
+        <v>17.6495170593262</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G459" t="n">
-        <v>17.3297500610352</v>
+        <v>17.3297481536865</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G461" t="n">
-        <v>17.1737670898438</v>
+        <v>17.1737651824951</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G465" t="n">
-        <v>16.5810298919678</v>
+        <v>16.5810279846191</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>16.4172458648682</v>
+        <v>16.4172496795654</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G469" t="n">
-        <v>16.3704509735107</v>
+        <v>16.3704528808594</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G470" t="n">
-        <v>16.3392562866211</v>
+        <v>16.3392543792725</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>16.1676712036133</v>
+        <v>16.1676731109619</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G472" t="n">
-        <v>16.0896816253662</v>
+        <v>16.0896835327148</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G473" t="n">
-        <v>16.2846603393555</v>
+        <v>16.2846584320068</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>16.2612648010254</v>
+        <v>16.2612628936768</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G479" t="n">
-        <v>16.2222652435303</v>
+        <v>16.2222671508789</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G481" t="n">
-        <v>16.3626518249512</v>
+        <v>16.3626537322998</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G483" t="n">
-        <v>16.4562454223633</v>
+        <v>16.4562435150146</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G484" t="n">
-        <v>16.9319934844971</v>
+        <v>16.9319915771484</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G485" t="n">
-        <v>17.4701347351074</v>
+        <v>17.4701328277588</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G486" t="n">
-        <v>18.0784702301025</v>
+        <v>18.0784721374512</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G489" t="n">
-        <v>17.8600940704346</v>
+        <v>17.8600921630859</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>23.0300006866455</v>
       </c>
       <c r="G490" t="n">
-        <v>17.961483001709</v>
+        <v>17.9614810943604</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>23</v>
       </c>
       <c r="G491" t="n">
-        <v>17.9380855560303</v>
+        <v>17.9380874633789</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>17.8210964202881</v>
+        <v>17.8210983276367</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>22.5</v>
       </c>
       <c r="G493" t="n">
-        <v>17.5481262207031</v>
+        <v>17.5481281280518</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>22.5</v>
       </c>
       <c r="G494" t="n">
-        <v>17.5481262207031</v>
+        <v>17.5481281280518</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G499" t="n">
-        <v>17.696310043335</v>
+        <v>17.6963119506836</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G501" t="n">
-        <v>16.8150062561035</v>
+        <v>16.8150043487549</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>20.6200008392334</v>
       </c>
       <c r="G502" t="n">
-        <v>16.0818843841553</v>
+        <v>16.0818824768066</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>20.25</v>
       </c>
       <c r="G504" t="n">
-        <v>15.7933149337769</v>
+        <v>15.7933130264282</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>15.4423522949219</v>
+        <v>15.4423503875732</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>20.0100002288818</v>
       </c>
       <c r="G508" t="n">
-        <v>15.6061344146729</v>
+        <v>15.6061363220215</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>20.0100002288818</v>
       </c>
       <c r="G509" t="n">
-        <v>15.6061344146729</v>
+        <v>15.6061363220215</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>20.1299991607666</v>
       </c>
       <c r="G510" t="n">
-        <v>15.6997241973877</v>
+        <v>15.6997213363647</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G511" t="n">
-        <v>15.5281429290771</v>
+        <v>15.5281410217285</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G512" t="n">
-        <v>15.5515403747559</v>
+        <v>15.5515384674072</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>20.25</v>
       </c>
       <c r="G513" t="n">
-        <v>15.7933149337769</v>
+        <v>15.7933130264282</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>20</v>
       </c>
       <c r="G514" t="n">
-        <v>15.5983324050903</v>
+        <v>15.598334312439</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>20.5</v>
       </c>
       <c r="G516" t="n">
-        <v>15.9882936477661</v>
+        <v>15.9882955551147</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G517" t="n">
-        <v>16.4172458648682</v>
+        <v>16.4172496795654</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>20.25</v>
       </c>
       <c r="G521" t="n">
-        <v>15.7933149337769</v>
+        <v>15.7933130264282</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>20.25</v>
       </c>
       <c r="G522" t="n">
-        <v>15.7933149337769</v>
+        <v>15.7933130264282</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>20.25</v>
       </c>
       <c r="G525" t="n">
-        <v>15.7933149337769</v>
+        <v>15.7933130264282</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G528" t="n">
-        <v>15.4267530441284</v>
+        <v>15.4267511367798</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>15.2863674163818</v>
+        <v>15.2863702774048</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>15.5203418731689</v>
+        <v>15.5203437805176</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>15.6763257980347</v>
+        <v>15.6763277053833</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G534" t="n">
-        <v>15.2551717758179</v>
+        <v>15.2551708221436</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G536" t="n">
-        <v>14.5532464981079</v>
+        <v>14.5532445907593</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G538" t="n">
-        <v>14.4752540588379</v>
+        <v>14.4752531051636</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G539" t="n">
-        <v>14.2568769454956</v>
+        <v>14.2568788528442</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G540" t="n">
-        <v>13.4457635879517</v>
+        <v>13.4457626342773</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G541" t="n">
-        <v>13.6329441070557</v>
+        <v>13.6329431533813</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G542" t="n">
-        <v>13.2741832733154</v>
+        <v>13.2741823196411</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G543" t="n">
-        <v>14.2724761962891</v>
+        <v>14.2724752426147</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G544" t="n">
-        <v>14.5532464981079</v>
+        <v>14.5532445907593</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G545" t="n">
-        <v>14.5688447952271</v>
+        <v>14.5688438415527</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G546" t="n">
-        <v>14.7560243606567</v>
+        <v>14.7560253143311</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>14.8964071273804</v>
+        <v>14.896409034729</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G548" t="n">
-        <v>14.3192720413208</v>
+        <v>14.3192729949951</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G549" t="n">
-        <v>13.9917049407959</v>
+        <v>13.9917068481445</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>13.8045263290405</v>
+        <v>13.8045272827148</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G551" t="n">
-        <v>13.6173458099365</v>
+        <v>13.6173467636108</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G552" t="n">
-        <v>13.5237560272217</v>
+        <v>13.523756980896</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G553" t="n">
-        <v>13.4769620895386</v>
+        <v>13.4769601821899</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G554" t="n">
-        <v>13.336576461792</v>
+        <v>13.3365745544434</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G556" t="n">
-        <v>13.4769620895386</v>
+        <v>13.4769601821899</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>13.7265338897705</v>
+        <v>13.7265348434448</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>18</v>
       </c>
       <c r="G558" t="n">
-        <v>14.0384998321533</v>
+        <v>14.0385007858276</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G559" t="n">
-        <v>14.1320934295654</v>
+        <v>14.1320915222168</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>14.1164922714233</v>
+        <v>14.1164932250977</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G561" t="n">
-        <v>14.2568769454956</v>
+        <v>14.2568788528442</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G562" t="n">
-        <v>14.5844440460205</v>
+        <v>14.5844449996948</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>14.1944856643677</v>
+        <v>14.1944847106934</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G564" t="n">
-        <v>14.2412805557251</v>
+        <v>14.2412786483765</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G565" t="n">
-        <v>14.3348684310913</v>
+        <v>14.3348665237427</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G566" t="n">
-        <v>14.1788854598999</v>
+        <v>14.1788845062256</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G568" t="n">
-        <v>14.5844440460205</v>
+        <v>14.5844449996948</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>14.2724761962891</v>
+        <v>14.2724752426147</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G570" t="n">
-        <v>14.3192720413208</v>
+        <v>14.3192729949951</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G571" t="n">
-        <v>14.2568769454956</v>
+        <v>14.2568788528442</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>14.2724761962891</v>
+        <v>14.2724752426147</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>18</v>
       </c>
       <c r="G573" t="n">
-        <v>14.0384998321533</v>
+        <v>14.0385007858276</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G574" t="n">
-        <v>13.6797409057617</v>
+        <v>13.6797380447388</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G575" t="n">
-        <v>14.3816661834717</v>
+        <v>14.3816623687744</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>13.8825159072876</v>
+        <v>13.8825178146362</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G579" t="n">
-        <v>14.3972625732422</v>
+        <v>14.3972616195679</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G580" t="n">
-        <v>14.3972625732422</v>
+        <v>14.3972616195679</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G581" t="n">
-        <v>14.3192720413208</v>
+        <v>14.3192729949951</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>20</v>
       </c>
       <c r="G584" t="n">
-        <v>15.5983324050903</v>
+        <v>15.598334312439</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G585" t="n">
-        <v>15.5827350616455</v>
+        <v>15.5827331542969</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G586" t="n">
-        <v>15.2863674163818</v>
+        <v>15.2863702774048</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G587" t="n">
-        <v>15.4267530441284</v>
+        <v>15.4267511367798</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G588" t="n">
-        <v>15.4423522949219</v>
+        <v>15.4423503875732</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G590" t="n">
-        <v>15.192777633667</v>
+        <v>15.1927757263184</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G591" t="n">
-        <v>15.2863674163818</v>
+        <v>15.2863702774048</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G592" t="n">
-        <v>15.0835886001587</v>
+        <v>15.0835876464844</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G593" t="n">
-        <v>15.1615791320801</v>
+        <v>15.1615810394287</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G594" t="n">
-        <v>14.974401473999</v>
+        <v>14.9743995666504</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>14.974401473999</v>
+        <v>14.9743995666504</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G597" t="n">
-        <v>15.5203418731689</v>
+        <v>15.5203437805176</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G599" t="n">
-        <v>15.2863674163818</v>
+        <v>15.2863702774048</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G600" t="n">
-        <v>15.2707719802856</v>
+        <v>15.270770072937</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G601" t="n">
-        <v>15.0367946624756</v>
+        <v>15.0367956161499</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G602" t="n">
-        <v>15.0679903030396</v>
+        <v>15.0679922103882</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G603" t="n">
-        <v>15.0523910522461</v>
+        <v>15.0523920059204</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G604" t="n">
-        <v>15.192777633667</v>
+        <v>15.1927757263184</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>14.974401473999</v>
+        <v>14.9743995666504</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G606" t="n">
-        <v>15.0211954116821</v>
+        <v>15.0211963653564</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G607" t="n">
-        <v>14.9588060379028</v>
+        <v>14.9588041305542</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G608" t="n">
-        <v>15.0835886001587</v>
+        <v>15.0835876464844</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>19.5</v>
       </c>
       <c r="G609" t="n">
-        <v>15.2083759307861</v>
+        <v>15.2083749771118</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>15.0523910522461</v>
+        <v>15.0523920059204</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>15.0523910522461</v>
+        <v>15.0523920059204</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G612" t="n">
-        <v>14.8964071273804</v>
+        <v>14.896409034729</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G613" t="n">
-        <v>14.9205017089844</v>
+        <v>14.9205007553101</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G615" t="n">
-        <v>14.4065542221069</v>
+        <v>14.4065551757812</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G616" t="n">
-        <v>14.4386768341064</v>
+        <v>14.4386749267578</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G617" t="n">
-        <v>14.6153478622437</v>
+        <v>14.6153469085693</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G618" t="n">
-        <v>14.5992851257324</v>
+        <v>14.5992841720581</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G619" t="n">
-        <v>14.8883800506592</v>
+        <v>14.8883790969849</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G620" t="n">
-        <v>15.0650491714478</v>
+        <v>15.0650501251221</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G621" t="n">
-        <v>15.2095956802368</v>
+        <v>15.2095937728882</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G622" t="n">
-        <v>15.0650491714478</v>
+        <v>15.0650501251221</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>14.9365634918213</v>
+        <v>14.936562538147</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>18.5</v>
       </c>
       <c r="G624" t="n">
-        <v>14.8562593460083</v>
+        <v>14.8562564849854</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G625" t="n">
-        <v>14.8401956558228</v>
+        <v>14.8401985168457</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G628" t="n">
-        <v>14.5511045455933</v>
+        <v>14.5511016845703</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>18</v>
       </c>
       <c r="G629" t="n">
-        <v>14.4547357559204</v>
+        <v>14.454737663269</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>18</v>
       </c>
       <c r="G630" t="n">
-        <v>14.4547357559204</v>
+        <v>14.454737663269</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G631" t="n">
-        <v>14.4868593215942</v>
+        <v>14.4868602752686</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G632" t="n">
-        <v>14.4868593215942</v>
+        <v>14.4868602752686</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G633" t="n">
-        <v>14.4868593215942</v>
+        <v>14.4868602752686</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>18</v>
       </c>
       <c r="G634" t="n">
-        <v>14.4547357559204</v>
+        <v>14.454737663269</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G635" t="n">
-        <v>14.4868593215942</v>
+        <v>14.4868602752686</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G636" t="n">
-        <v>13.7641229629517</v>
+        <v>13.7641220092773</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G637" t="n">
-        <v>13.7641229629517</v>
+        <v>13.7641220092773</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G638" t="n">
-        <v>13.7641229629517</v>
+        <v>13.7641220092773</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G639" t="n">
-        <v>13.7641229629517</v>
+        <v>13.7641220092773</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G641" t="n">
-        <v>13.6677579879761</v>
+        <v>13.6677570343018</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G642" t="n">
-        <v>13.8604869842529</v>
+        <v>13.8604888916016</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>13.8123054504395</v>
+        <v>13.8123044967651</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G645" t="n">
-        <v>13.8123054504395</v>
+        <v>13.8123044967651</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>16</v>
       </c>
       <c r="G646" t="n">
-        <v>12.8486547470093</v>
+        <v>12.8486557006836</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>12.9289588928223</v>
+        <v>12.9289608001709</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G648" t="n">
-        <v>12.6880474090576</v>
+        <v>12.6880483627319</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>12.9289588928223</v>
+        <v>12.9289608001709</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>16</v>
       </c>
       <c r="G651" t="n">
-        <v>12.8486547470093</v>
+        <v>12.8486557006836</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>16</v>
       </c>
       <c r="G652" t="n">
-        <v>12.8486547470093</v>
+        <v>12.8486557006836</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G653" t="n">
-        <v>12.8807783126831</v>
+        <v>12.8807773590088</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G655" t="n">
-        <v>13.0253238677979</v>
+        <v>13.0253229141235</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G657" t="n">
-        <v>12.8647174835205</v>
+        <v>12.8647165298462</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G658" t="n">
-        <v>12.9610815048218</v>
+        <v>12.9610805511475</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G659" t="n">
-        <v>13.0092630386353</v>
+        <v>13.0092639923096</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>16</v>
       </c>
       <c r="G660" t="n">
-        <v>12.8486547470093</v>
+        <v>12.8486557006836</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>12.7683525085449</v>
+        <v>12.7683506011963</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G664" t="n">
-        <v>12.671986579895</v>
+        <v>12.6719856262207</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G666" t="n">
-        <v>12.7522916793823</v>
+        <v>12.7522897720337</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>16</v>
       </c>
       <c r="G667" t="n">
-        <v>12.8486547470093</v>
+        <v>12.8486557006836</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>12.6880474090576</v>
+        <v>12.6880483627319</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G669" t="n">
-        <v>12.3186492919922</v>
+        <v>12.3186502456665</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G670" t="n">
-        <v>12.1580410003662</v>
+        <v>12.1580400466919</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G672" t="n">
-        <v>12.1580410003662</v>
+        <v>12.1580400466919</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G673" t="n">
-        <v>12.3668298721313</v>
+        <v>12.3668308258057</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G674" t="n">
-        <v>12.3025875091553</v>
+        <v>12.302586555481</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>14.5</v>
       </c>
       <c r="G676" t="n">
-        <v>11.6440925598145</v>
+        <v>11.6440935134888</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G677" t="n">
-        <v>11.5798511505127</v>
+        <v>11.5798501968384</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>14.5</v>
       </c>
       <c r="G678" t="n">
-        <v>11.6440925598145</v>
+        <v>11.6440935134888</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G684" t="n">
-        <v>10.7607488632202</v>
+        <v>10.7607469558716</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G685" t="n">
-        <v>11.9171276092529</v>
+        <v>11.9171285629272</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G687" t="n">
-        <v>12.7041072845459</v>
+        <v>12.7041082382202</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>16</v>
       </c>
       <c r="G689" t="n">
-        <v>12.8486547470093</v>
+        <v>12.8486557006836</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>12.9289588928223</v>
+        <v>12.9289608001709</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G691" t="n">
-        <v>12.8647174835205</v>
+        <v>12.8647165298462</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G692" t="n">
-        <v>12.7362279891968</v>
+        <v>12.7362289428711</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G694" t="n">
-        <v>12.2383441925049</v>
+        <v>12.2383451461792</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>12.3668298721313</v>
+        <v>12.3668308258057</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G696" t="n">
-        <v>12.671986579895</v>
+        <v>12.6719856262207</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G697" t="n">
-        <v>12.8004713058472</v>
+        <v>12.8004722595215</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>16</v>
       </c>
       <c r="G698" t="n">
-        <v>12.8486547470093</v>
+        <v>12.8486557006836</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G699" t="n">
-        <v>12.8807783126831</v>
+        <v>12.8807773590088</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G701" t="n">
-        <v>12.6880474090576</v>
+        <v>12.6880483627319</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G705" t="n">
-        <v>12.1098585128784</v>
+        <v>12.1098566055298</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G706" t="n">
-        <v>12.1580410003662</v>
+        <v>12.1580400466919</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G708" t="n">
-        <v>12.1580410003662</v>
+        <v>12.1580400466919</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G714" t="n">
-        <v>11.13014793396</v>
+        <v>11.1301469802856</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G718" t="n">
-        <v>11.4031810760498</v>
+        <v>11.4031820297241</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G719" t="n">
-        <v>11.1783294677734</v>
+        <v>11.1783304214478</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G726" t="n">
-        <v>10.4716548919678</v>
+        <v>10.4716539382935</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G728" t="n">
-        <v>10.5198364257812</v>
+        <v>10.5198373794556</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G730" t="n">
-        <v>11.2265129089355</v>
+        <v>11.2265119552612</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G732" t="n">
-        <v>11.8528852462769</v>
+        <v>11.8528842926025</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G734" t="n">
-        <v>10.9855995178223</v>
+        <v>10.9856004714966</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G735" t="n">
-        <v>11.1783294677734</v>
+        <v>11.1783304214478</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G739" t="n">
-        <v>10.7607488632202</v>
+        <v>10.7607469558716</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G740" t="n">
-        <v>10.6643838882446</v>
+        <v>10.6643829345703</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G743" t="n">
-        <v>10.9052963256836</v>
+        <v>10.9052972793579</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>11.4031810760498</v>
+        <v>11.4031820297241</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G748" t="n">
-        <v>11.4353017807007</v>
+        <v>11.4353036880493</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G750" t="n">
-        <v>11.3871221542358</v>
+        <v>11.3871202468872</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G751" t="n">
-        <v>11.6922769546509</v>
+        <v>11.6922760009766</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G752" t="n">
-        <v>11.7404584884644</v>
+        <v>11.74045753479</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>11.4031810760498</v>
+        <v>11.4031820297241</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G755" t="n">
-        <v>11.6280326843262</v>
+        <v>11.6280336380005</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G756" t="n">
-        <v>11.676215171814</v>
+        <v>11.6762161254883</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G758" t="n">
-        <v>11.8207626342773</v>
+        <v>11.8207635879517</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G759" t="n">
-        <v>11.8207626342773</v>
+        <v>11.8207635879517</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G760" t="n">
-        <v>11.676215171814</v>
+        <v>11.6762161254883</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>14.5</v>
       </c>
       <c r="G762" t="n">
-        <v>11.6440925598145</v>
+        <v>11.6440935134888</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G763" t="n">
-        <v>11.9492502212524</v>
+        <v>11.9492492675781</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G768" t="n">
-        <v>12.0777359008789</v>
+        <v>12.0777368545532</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G773" t="n">
-        <v>12.6559267044067</v>
+        <v>12.6559257507324</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G779" t="n">
-        <v>12.3186492919922</v>
+        <v>12.3186502456665</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G781" t="n">
-        <v>12.2865257263184</v>
+        <v>12.2865266799927</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>12.1259183883667</v>
+        <v>12.125919342041</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>12.3668298721313</v>
+        <v>12.3668308258057</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G785" t="n">
-        <v>12.2865257263184</v>
+        <v>12.2865266799927</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G787" t="n">
-        <v>12.3668298721313</v>
+        <v>12.3668308258057</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G788" t="n">
-        <v>12.2383441925049</v>
+        <v>12.2383451461792</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G791" t="n">
-        <v>12.1741008758545</v>
+        <v>12.1741018295288</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>12.1259183883667</v>
+        <v>12.125919342041</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G794" t="n">
-        <v>12.1580410003662</v>
+        <v>12.1580400466919</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>12.1259183883667</v>
+        <v>12.125919342041</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G797" t="n">
-        <v>12.2544040679932</v>
+        <v>12.2544050216675</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G798" t="n">
-        <v>12.3668298721313</v>
+        <v>12.3668308258057</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G799" t="n">
-        <v>12.2383441925049</v>
+        <v>12.2383451461792</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G801" t="n">
-        <v>12.3668298721313</v>
+        <v>12.3668308258057</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G803" t="n">
-        <v>12.2383441925049</v>
+        <v>12.2383451461792</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G805" t="n">
-        <v>12.6880474090576</v>
+        <v>12.6880483627319</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G806" t="n">
-        <v>12.7041072845459</v>
+        <v>12.7041082382202</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G807" t="n">
-        <v>12.4953174591064</v>
+        <v>12.4953165054321</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>12.1259183883667</v>
+        <v>12.125919342041</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G813" t="n">
-        <v>12.0295524597168</v>
+        <v>12.0295534133911</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G814" t="n">
-        <v>12.3668298721313</v>
+        <v>12.3668308258057</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G815" t="n">
-        <v>12.3989524841309</v>
+        <v>12.3989515304565</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>12.2865257263184</v>
+        <v>12.2865266799927</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G817" t="n">
-        <v>12.1741008758545</v>
+        <v>12.1741018295288</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G818" t="n">
-        <v>12.3989524841309</v>
+        <v>12.3989515304565</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G819" t="n">
-        <v>12.3828916549683</v>
+        <v>12.3828907012939</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G821" t="n">
-        <v>13.0574464797974</v>
+        <v>13.057445526123</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>13.0092630386353</v>
+        <v>13.0092639923096</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G826" t="n">
-        <v>12.8647174835205</v>
+        <v>12.8647165298462</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G827" t="n">
-        <v>12.8647174835205</v>
+        <v>12.8647165298462</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G829" t="n">
-        <v>13.0092630386353</v>
+        <v>13.0092639923096</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G831" t="n">
-        <v>12.8807783126831</v>
+        <v>12.8807773590088</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G832" t="n">
-        <v>13.07350730896</v>
+        <v>13.0735082626343</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G833" t="n">
-        <v>13.1538095474243</v>
+        <v>13.1538105010986</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G834" t="n">
-        <v>12.8165330886841</v>
+        <v>12.8165340423584</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>16</v>
       </c>
       <c r="G835" t="n">
-        <v>12.8486547470093</v>
+        <v>12.8486557006836</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G836" t="n">
-        <v>12.9610815048218</v>
+        <v>12.9610805511475</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G837" t="n">
-        <v>13.0574464797974</v>
+        <v>13.057445526123</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G838" t="n">
-        <v>12.9289588928223</v>
+        <v>12.9289608001709</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G839" t="n">
-        <v>12.6559267044067</v>
+        <v>12.6559257507324</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G840" t="n">
-        <v>12.7041072845459</v>
+        <v>12.7041082382202</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G843" t="n">
-        <v>12.3989524841309</v>
+        <v>12.3989515304565</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G844" t="n">
-        <v>12.6238031387329</v>
+        <v>12.6238040924072</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G845" t="n">
-        <v>12.6880474090576</v>
+        <v>12.6880483627319</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G846" t="n">
-        <v>12.5595598220825</v>
+        <v>12.5595617294312</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G847" t="n">
-        <v>12.6559267044067</v>
+        <v>12.6559257507324</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G849" t="n">
-        <v>12.4953174591064</v>
+        <v>12.4953165054321</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>12.3668298721313</v>
+        <v>12.3668308258057</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G854" t="n">
-        <v>12.3186492919922</v>
+        <v>12.3186502456665</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G861" t="n">
-        <v>11.8528852462769</v>
+        <v>11.8528842926025</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>14.5</v>
       </c>
       <c r="G862" t="n">
-        <v>11.6440925598145</v>
+        <v>11.6440935134888</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G863" t="n">
-        <v>12.2200393676758</v>
+        <v>12.2200374603271</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G866" t="n">
-        <v>11.719217300415</v>
+        <v>11.7192163467407</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G868" t="n">
-        <v>11.8026876449585</v>
+        <v>11.8026866912842</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G870" t="n">
-        <v>11.719217300415</v>
+        <v>11.7192163467407</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G871" t="n">
-        <v>11.8193807601929</v>
+        <v>11.8193817138672</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G872" t="n">
-        <v>11.6190519332886</v>
+        <v>11.6190528869629</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G873" t="n">
-        <v>11.8026876449585</v>
+        <v>11.8026866912842</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G875" t="n">
-        <v>12.0030164718628</v>
+        <v>12.0030155181885</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G877" t="n">
-        <v>12.0030164718628</v>
+        <v>12.0030155181885</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G879" t="n">
-        <v>11.8026876449585</v>
+        <v>11.8026866912842</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G880" t="n">
-        <v>11.9362382888794</v>
+        <v>11.936240196228</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G882" t="n">
-        <v>12.0030164718628</v>
+        <v>12.0030155181885</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G883" t="n">
-        <v>11.9362382888794</v>
+        <v>11.936240196228</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G884" t="n">
-        <v>11.8193807601929</v>
+        <v>11.8193817138672</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G885" t="n">
-        <v>11.8193807601929</v>
+        <v>11.8193817138672</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G889" t="n">
-        <v>11.6190519332886</v>
+        <v>11.6190528869629</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G890" t="n">
-        <v>11.7025232315063</v>
+        <v>11.7025241851807</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G891" t="n">
-        <v>11.9362382888794</v>
+        <v>11.936240196228</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G893" t="n">
-        <v>12.2367315292358</v>
+        <v>12.2367334365845</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G894" t="n">
-        <v>12.0030164718628</v>
+        <v>12.0030155181885</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G896" t="n">
-        <v>11.8861560821533</v>
+        <v>11.8861570358276</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>14.5</v>
       </c>
       <c r="G897" t="n">
-        <v>12.1031799316406</v>
+        <v>12.1031789779663</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G898" t="n">
-        <v>12.2200393676758</v>
+        <v>12.2200374603271</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G899" t="n">
-        <v>12.0197095870972</v>
+        <v>12.0197105407715</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G900" t="n">
-        <v>12.3368978500366</v>
+        <v>12.3368968963623</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G905" t="n">
-        <v>12.0197095870972</v>
+        <v>12.0197105407715</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G906" t="n">
-        <v>12.1699552536011</v>
+        <v>12.1699562072754</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>14.5</v>
       </c>
       <c r="G907" t="n">
-        <v>12.1031799316406</v>
+        <v>12.1031789779663</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G911" t="n">
-        <v>12.2367315292358</v>
+        <v>12.2367334365845</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>14.5</v>
       </c>
       <c r="G914" t="n">
-        <v>12.1031799316406</v>
+        <v>12.1031789779663</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G915" t="n">
-        <v>11.6190519332886</v>
+        <v>11.6190528869629</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G916" t="n">
-        <v>11.8026876449585</v>
+        <v>11.8026866912842</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G919" t="n">
-        <v>11.235089302063</v>
+        <v>11.2350902557373</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>11.1850061416626</v>
+        <v>11.1850070953369</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G923" t="n">
-        <v>11.5021934509277</v>
+        <v>11.5021944046021</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>11.6023578643799</v>
+        <v>11.6023588180542</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G926" t="n">
-        <v>11.7025232315063</v>
+        <v>11.7025241851807</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G927" t="n">
-        <v>11.8026876449585</v>
+        <v>11.8026866912842</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G928" t="n">
-        <v>11.8026876449585</v>
+        <v>11.8026866912842</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G929" t="n">
-        <v>11.6023578643799</v>
+        <v>11.6023588180542</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G932" t="n">
-        <v>11.452112197876</v>
+        <v>11.4521131515503</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G935" t="n">
-        <v>11.235089302063</v>
+        <v>11.2350902557373</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>11.1850061416626</v>
+        <v>11.1850070953369</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>11.1850061416626</v>
+        <v>11.1850070953369</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G940" t="n">
-        <v>11.2851724624634</v>
+        <v>11.2851715087891</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>11.1850061416626</v>
+        <v>11.1850070953369</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G946" t="n">
-        <v>11.0681486129761</v>
+        <v>11.0681505203247</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G951" t="n">
-        <v>10.8344326019287</v>
+        <v>10.8344316482544</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G954" t="n">
-        <v>10.9179019927979</v>
+        <v>10.9179029464722</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G956" t="n">
-        <v>10.8344326019287</v>
+        <v>10.8344316482544</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G960" t="n">
-        <v>10.8344326019287</v>
+        <v>10.8344316482544</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G963" t="n">
-        <v>10.5840225219727</v>
+        <v>10.584023475647</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G967" t="n">
-        <v>10.4170808792114</v>
+        <v>10.4170818328857</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G969" t="n">
-        <v>10.5840225219727</v>
+        <v>10.584023475647</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G972" t="n">
-        <v>10.1833648681641</v>
+        <v>10.1833639144897</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>10.1666717529297</v>
+        <v>10.1666707992554</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>12</v>
       </c>
       <c r="G976" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164241790771</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G979" t="n">
-        <v>10.7008810043335</v>
+        <v>10.7008790969849</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G983" t="n">
-        <v>10.5339393615723</v>
+        <v>10.5339403152466</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G984" t="n">
-        <v>10.4003877639771</v>
+        <v>10.4003868103027</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G985" t="n">
-        <v>10.5339393615723</v>
+        <v>10.5339403152466</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G986" t="n">
-        <v>10.567328453064</v>
+        <v>10.5673274993896</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G989" t="n">
-        <v>10.3503046035767</v>
+        <v>10.350305557251</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G991" t="n">
-        <v>10.4003877639771</v>
+        <v>10.4003868103027</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G992" t="n">
-        <v>10.5840225219727</v>
+        <v>10.584023475647</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G994" t="n">
-        <v>10.4003877639771</v>
+        <v>10.4003868103027</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G995" t="n">
-        <v>10.5339393615723</v>
+        <v>10.5339403152466</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G998" t="n">
-        <v>10.5840225219727</v>
+        <v>10.584023475647</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1002" t="n">
-        <v>11.21839427948</v>
+        <v>11.2183961868286</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1004" t="n">
-        <v>11.4855003356934</v>
+        <v>11.4855012893677</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1005" t="n">
-        <v>11.4354181289673</v>
+        <v>11.435417175293</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1008" t="n">
-        <v>11.4187250137329</v>
+        <v>11.4187240600586</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1009" t="n">
-        <v>11.4354181289673</v>
+        <v>11.435417175293</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1015" t="n">
-        <v>11.1850061416626</v>
+        <v>11.1850070953369</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1018" t="n">
-        <v>11.4855003356934</v>
+        <v>11.4855012893677</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1022" t="n">
-        <v>11.5856647491455</v>
+        <v>11.5856637954712</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1023" t="n">
-        <v>11.6023578643799</v>
+        <v>11.6023588180542</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1027" t="n">
-        <v>11.4187250137329</v>
+        <v>11.4187240600586</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1028" t="n">
-        <v>11.5021934509277</v>
+        <v>11.5021944046021</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1029" t="n">
-        <v>11.6023578643799</v>
+        <v>11.6023588180542</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G1030" t="n">
-        <v>11.4688062667847</v>
+        <v>11.4688053131104</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1032" t="n">
-        <v>11.4354181289673</v>
+        <v>11.435417175293</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1037" t="n">
-        <v>11.0514554977417</v>
+        <v>11.0514545440674</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1043" t="n">
-        <v>11.2017030715942</v>
+        <v>11.2017011642456</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G1044" t="n">
-        <v>11.4187250137329</v>
+        <v>11.4187240600586</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1047" t="n">
-        <v>11.8360757827759</v>
+        <v>11.8360748291016</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1048" t="n">
-        <v>11.8360757827759</v>
+        <v>11.8360748291016</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1052" t="n">
-        <v>11.8026876449585</v>
+        <v>11.8026866912842</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.5339393615723</v>
+        <v>10.5339403152466</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.2668361663818</v>
+        <v>10.2668352127075</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>12</v>
       </c>
       <c r="G1061" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164241790771</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1062" t="n">
-        <v>9.29858207702637</v>
+        <v>9.29858016967773</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1064" t="n">
-        <v>8.66420745849609</v>
+        <v>8.66420650482178</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.66420745849609</v>
+        <v>8.66420650482178</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1068" t="n">
-        <v>7.84619903564453</v>
+        <v>7.84619998931885</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G1071" t="n">
-        <v>8.10495758056641</v>
+        <v>8.10495662689209</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>9.75</v>
       </c>
       <c r="G1073" t="n">
-        <v>8.13834476470947</v>
+        <v>8.13834571838379</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1074" t="n">
-        <v>7.97140598297119</v>
+        <v>7.97140407562256</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1075" t="n">
-        <v>7.97975254058838</v>
+        <v>7.97975158691406</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1076" t="n">
-        <v>7.97140598297119</v>
+        <v>7.97140407562256</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.03818225860596</v>
+        <v>8.03818130493164</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1079" t="n">
-        <v>7.946364402771</v>
+        <v>7.94636344909668</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1082" t="n">
-        <v>8.14669132232666</v>
+        <v>8.14669322967529</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>8.28024482727051</v>
+        <v>8.28024387359619</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1084" t="n">
-        <v>8.33032608032227</v>
+        <v>8.33032703399658</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1088" t="n">
-        <v>8.14669132232666</v>
+        <v>8.14669322967529</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1092" t="n">
-        <v>8.80610656738281</v>
+        <v>8.80610752105713</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1093" t="n">
-        <v>8.80610656738281</v>
+        <v>8.80610752105713</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>10.5</v>
       </c>
       <c r="G1095" t="n">
-        <v>8.76437187194824</v>
+        <v>8.76437091827393</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>8.8478422164917</v>
+        <v>8.84784126281738</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1097" t="n">
-        <v>9.0147819519043</v>
+        <v>9.01478290557861</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>11</v>
       </c>
       <c r="G1099" t="n">
-        <v>9.18172168731689</v>
+        <v>9.18172264099121</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1101" t="n">
-        <v>9.0147819519043</v>
+        <v>9.01478290557861</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1102" t="n">
-        <v>9.0147819519043</v>
+        <v>9.01478290557861</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1114" t="n">
-        <v>8.24685573577881</v>
+        <v>8.24685668945312</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.24685573577881</v>
+        <v>8.24685668945312</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1116" t="n">
-        <v>8.21346950531006</v>
+        <v>8.21346759796143</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>11</v>
       </c>
       <c r="G1122" t="n">
-        <v>9.18172168731689</v>
+        <v>9.18172264099121</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1124" t="n">
-        <v>9.43213367462158</v>
+        <v>9.43213272094727</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>11.5</v>
       </c>
       <c r="G1125" t="n">
-        <v>9.59907341003418</v>
+        <v>9.5990743637085</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>9.68254470825195</v>
+        <v>9.68254375457764</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1127" t="n">
-        <v>9.43213367462158</v>
+        <v>9.43213272094727</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1128" t="n">
-        <v>9.43213367462158</v>
+        <v>9.43213272094727</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>9.68254470825195</v>
+        <v>9.68254375457764</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1132" t="n">
-        <v>9.64080810546875</v>
+        <v>9.64081001281738</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1133" t="n">
-        <v>9.68254470825195</v>
+        <v>9.68254375457764</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1134" t="n">
-        <v>9.55733871459961</v>
+        <v>9.55733776092529</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1137" t="n">
-        <v>9.43213367462158</v>
+        <v>9.43213272094727</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1138" t="n">
-        <v>9.34866333007812</v>
+        <v>9.34866428375244</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1139" t="n">
-        <v>9.34866333007812</v>
+        <v>9.34866428375244</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1141" t="n">
-        <v>9.22345733642578</v>
+        <v>9.2234582901001</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>11</v>
       </c>
       <c r="G1142" t="n">
-        <v>9.18172168731689</v>
+        <v>9.18172264099121</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1144" t="n">
-        <v>9.22345733642578</v>
+        <v>9.2234582901001</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>11</v>
       </c>
       <c r="G1145" t="n">
-        <v>9.18172168731689</v>
+        <v>9.18172264099121</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1147" t="n">
-        <v>9.34866333007812</v>
+        <v>9.34866428375244</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1151" t="n">
-        <v>9.43213367462158</v>
+        <v>9.43213272094727</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1153" t="n">
-        <v>9.43213367462158</v>
+        <v>9.43213272094727</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1154" t="n">
-        <v>9.55733871459961</v>
+        <v>9.55733776092529</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1155" t="n">
-        <v>9.76601409912109</v>
+        <v>9.76601314544678</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1156" t="n">
-        <v>9.55733871459961</v>
+        <v>9.55733776092529</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1157" t="n">
-        <v>9.34866333007812</v>
+        <v>9.34866428375244</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1159" t="n">
-        <v>9.43213367462158</v>
+        <v>9.43213272094727</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1160" t="n">
-        <v>9.34866333007812</v>
+        <v>9.34866428375244</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1161" t="n">
-        <v>9.34866333007812</v>
+        <v>9.34866428375244</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1162" t="n">
-        <v>9.22345733642578</v>
+        <v>9.2234582901001</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1163" t="n">
-        <v>9.34866333007812</v>
+        <v>9.34866428375244</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1164" t="n">
-        <v>9.22345733642578</v>
+        <v>9.2234582901001</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>9.34866333007812</v>
+        <v>9.34866428375244</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>11.5</v>
       </c>
       <c r="G1166" t="n">
-        <v>9.59907341003418</v>
+        <v>9.5990743637085</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1167" t="n">
-        <v>9.84948444366455</v>
+        <v>9.84948348999023</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>12</v>
       </c>
       <c r="G1168" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164241790771</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1171" t="n">
-        <v>10.5589799880981</v>
+        <v>10.5589809417725</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1173" t="n">
-        <v>10.3503046035767</v>
+        <v>10.350305557251</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1175" t="n">
-        <v>10.3085718154907</v>
+        <v>10.3085708618164</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1176" t="n">
-        <v>10.1833648681641</v>
+        <v>10.1833639144897</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1178" t="n">
-        <v>9.97468852996826</v>
+        <v>9.97468948364258</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>12</v>
       </c>
       <c r="G1180" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164241790771</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>12</v>
       </c>
       <c r="G1183" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164241790771</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>12</v>
       </c>
       <c r="G1185" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164241790771</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12</v>
       </c>
       <c r="G1188" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164241790771</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>12</v>
       </c>
       <c r="G1192" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164241790771</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>12</v>
       </c>
       <c r="G1197" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164241790771</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>12</v>
       </c>
       <c r="G1199" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164241790771</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>12</v>
       </c>
       <c r="G1201" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164241790771</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1205" t="n">
-        <v>10.5589799880981</v>
+        <v>10.5589809417725</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1210" t="n">
-        <v>10.9763307571411</v>
+        <v>10.9763317108154</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>14</v>
       </c>
       <c r="G1215" t="n">
-        <v>11.983286857605</v>
+        <v>11.9832878112793</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>14</v>
       </c>
       <c r="G1216" t="n">
-        <v>11.983286857605</v>
+        <v>11.9832878112793</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1217" t="n">
-        <v>11.5125131607056</v>
+        <v>11.5125150680542</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1220" t="n">
-        <v>11.2129316329956</v>
+        <v>11.2129325866699</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1224" t="n">
-        <v>11.2129316329956</v>
+        <v>11.2129325866699</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>13</v>
       </c>
       <c r="G1225" t="n">
-        <v>11.1273384094238</v>
+        <v>11.1273374557495</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1226" t="n">
-        <v>10.7849569320679</v>
+        <v>10.7849588394165</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1228" t="n">
-        <v>10.1001977920532</v>
+        <v>10.1001987457275</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1229" t="n">
-        <v>10.1001977920532</v>
+        <v>10.1001987457275</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>10.5709705352783</v>
+        <v>10.5709714889526</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1231" t="n">
-        <v>10.4425783157349</v>
+        <v>10.4425773620605</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1237" t="n">
-        <v>11.6837043762207</v>
+        <v>11.6837034225464</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1242" t="n">
-        <v>11.640908241272</v>
+        <v>11.6409072875977</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1243" t="n">
-        <v>11.5125131607056</v>
+        <v>11.5125150680542</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>11.6837043762207</v>
+        <v>11.6837034225464</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>13</v>
       </c>
       <c r="G1247" t="n">
-        <v>11.1273384094238</v>
+        <v>11.1273374557495</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1252" t="n">
-        <v>12.8820323944092</v>
+        <v>12.8820343017578</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>13.3528051376343</v>
+        <v>13.35280418396</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1256" t="n">
-        <v>13.4383993148804</v>
+        <v>13.4384002685547</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1257" t="n">
-        <v>12.3684644699097</v>
+        <v>12.3684635162354</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1258" t="n">
-        <v>12.5396528244019</v>
+        <v>12.5396518707275</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>13.1816148757935</v>
+        <v>13.1816139221191</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1261" t="n">
-        <v>13.1816148757935</v>
+        <v>13.1816139221191</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1262" t="n">
-        <v>13.2244119644165</v>
+        <v>13.2244129180908</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1263" t="n">
-        <v>13.3528051376343</v>
+        <v>13.35280418396</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>15</v>
       </c>
       <c r="G1265" t="n">
-        <v>12.8392343521118</v>
+        <v>12.8392353057861</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>15</v>
       </c>
       <c r="G1266" t="n">
-        <v>12.8392343521118</v>
+        <v>12.8392353057861</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>13.1816148757935</v>
+        <v>13.1816139221191</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1268" t="n">
-        <v>13.3956022262573</v>
+        <v>13.395601272583</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1269" t="n">
-        <v>13.2244119644165</v>
+        <v>13.2244129180908</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1270" t="n">
-        <v>12.8820323944092</v>
+        <v>12.8820343017578</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>12.7108430862427</v>
+        <v>12.710844039917</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>15.25</v>
       </c>
       <c r="G1274" t="n">
-        <v>13.05322265625</v>
+        <v>13.0532236099243</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1275" t="n">
-        <v>13.3100080490112</v>
+        <v>13.3100090026855</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1276" t="n">
-        <v>13.1816148757935</v>
+        <v>13.1816139221191</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1277" t="n">
-        <v>13.3100080490112</v>
+        <v>13.3100090026855</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1278" t="n">
-        <v>13.2244119644165</v>
+        <v>13.2244129180908</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>15.25</v>
       </c>
       <c r="G1279" t="n">
-        <v>13.05322265625</v>
+        <v>13.0532236099243</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>17.75</v>
       </c>
       <c r="G1292" t="n">
-        <v>15.1930952072144</v>
+        <v>15.193097114563</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>18</v>
       </c>
       <c r="G1294" t="n">
-        <v>15.4070835113525</v>
+        <v>15.4070816040039</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1296" t="n">
-        <v>16.2202339172363</v>
+        <v>16.220235824585</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1299" t="n">
-        <v>16.9905891418457</v>
+        <v>16.9905872344971</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1300" t="n">
-        <v>17.0333843231201</v>
+        <v>17.0333862304688</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G1301" t="n">
-        <v>17.0761833190918</v>
+        <v>17.0761852264404</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1303" t="n">
-        <v>17.2901725769043</v>
+        <v>17.2901706695557</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1305" t="n">
-        <v>17.2901725769043</v>
+        <v>17.2901706695557</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1309" t="n">
-        <v>17.0333843231201</v>
+        <v>17.0333862304688</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1310" t="n">
-        <v>16.0062503814697</v>
+        <v>16.0062484741211</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>20.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>17.5469532012939</v>
+        <v>17.5469551086426</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1312" t="n">
-        <v>16.8621959686279</v>
+        <v>16.8621940612793</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1313" t="n">
-        <v>17.4613628387451</v>
+        <v>17.4613590240479</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1314" t="n">
-        <v>17.4613628387451</v>
+        <v>17.4613590240479</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>17.4613628387451</v>
+        <v>17.4613590240479</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>20.5</v>
       </c>
       <c r="G1318" t="n">
-        <v>17.5469532012939</v>
+        <v>17.5469551086426</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1319" t="n">
-        <v>17.4613628387451</v>
+        <v>17.4613590240479</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1321" t="n">
-        <v>17.2045745849609</v>
+        <v>17.2045764923096</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>17.2901725769043</v>
+        <v>17.2901706695557</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G1323" t="n">
-        <v>17.0761833190918</v>
+        <v>17.0761852264404</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G1324" t="n">
-        <v>17.0761833190918</v>
+        <v>17.0761852264404</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1325" t="n">
-        <v>17.2045745849609</v>
+        <v>17.2045764923096</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>17.4613628387451</v>
+        <v>17.4613590240479</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1327" t="n">
-        <v>17.2901725769043</v>
+        <v>17.2901706695557</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1328" t="n">
-        <v>18.2317123413086</v>
+        <v>18.2317142486572</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1329" t="n">
-        <v>19.3444499969482</v>
+        <v>19.3444480895996</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>23</v>
       </c>
       <c r="G1330" t="n">
-        <v>19.6868267059326</v>
+        <v>19.6868286132812</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1331" t="n">
-        <v>19.7724227905273</v>
+        <v>19.772424697876</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>23.5</v>
       </c>
       <c r="G1332" t="n">
-        <v>20.1148014068604</v>
+        <v>20.114803314209</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>23.5</v>
       </c>
       <c r="G1334" t="n">
-        <v>20.1148014068604</v>
+        <v>20.114803314209</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1335" t="n">
-        <v>20.2003955841064</v>
+        <v>20.2003974914551</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>23.5</v>
       </c>
       <c r="G1336" t="n">
-        <v>20.1148014068604</v>
+        <v>20.114803314209</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>23</v>
       </c>
       <c r="G1337" t="n">
-        <v>19.6868267059326</v>
+        <v>19.6868286132812</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1339" t="n">
-        <v>19.3444499969482</v>
+        <v>19.3444480895996</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1340" t="n">
-        <v>19.3444499969482</v>
+        <v>19.3444480895996</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1345" t="n">
-        <v>19.430046081543</v>
+        <v>19.4300422668457</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1347" t="n">
-        <v>19.0876636505127</v>
+        <v>19.0876617431641</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>18.7452850341797</v>
+        <v>18.7452831268311</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>23</v>
       </c>
       <c r="G1351" t="n">
-        <v>19.6868267059326</v>
+        <v>19.6868286132812</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1352" t="n">
-        <v>19.430046081543</v>
+        <v>19.4300422668457</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1354" t="n">
-        <v>19.0876636505127</v>
+        <v>19.0876617431641</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1355" t="n">
-        <v>19.430046081543</v>
+        <v>19.4300422668457</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1356" t="n">
-        <v>19.0876636505127</v>
+        <v>19.0876617431641</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>22</v>
       </c>
       <c r="G1357" t="n">
-        <v>18.8308792114258</v>
+        <v>18.8308811187744</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1360" t="n">
-        <v>18.2317123413086</v>
+        <v>18.2317142486572</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1361" t="n">
-        <v>18.7452850341797</v>
+        <v>18.7452831268311</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1362" t="n">
-        <v>20.2003955841064</v>
+        <v>20.2003974914551</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>23</v>
       </c>
       <c r="G1364" t="n">
-        <v>19.6868267059326</v>
+        <v>19.6868286132812</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1365" t="n">
-        <v>19.8580169677734</v>
+        <v>19.8580150604248</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1366" t="n">
-        <v>19.6012325286865</v>
+        <v>19.6012306213379</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>24</v>
       </c>
       <c r="G1367" t="n">
-        <v>20.5427742004395</v>
+        <v>20.5427761077881</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1368" t="n">
-        <v>20.4571800231934</v>
+        <v>20.457181930542</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1371" t="n">
-        <v>21.1419410705566</v>
+        <v>21.1419429779053</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1372" t="n">
-        <v>20.8851566314697</v>
+        <v>20.8851547241211</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1374" t="n">
-        <v>23.8825225830078</v>
+        <v>23.8825206756592</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1376" t="n">
-        <v>23.0077037811279</v>
+        <v>23.0077056884766</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1378" t="n">
-        <v>23.5325927734375</v>
+        <v>23.5325946807861</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>24.407413482666</v>
+        <v>24.4074115753174</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1385" t="n">
-        <v>22.9202213287354</v>
+        <v>22.920223236084</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1386" t="n">
-        <v>22.9202213287354</v>
+        <v>22.920223236084</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1389" t="n">
-        <v>23.0077037811279</v>
+        <v>23.0077056884766</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1390" t="n">
-        <v>22.9202213287354</v>
+        <v>22.920223236084</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1393" t="n">
-        <v>23.0077037811279</v>
+        <v>23.0077056884766</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>23.0077037811279</v>
+        <v>23.0077056884766</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1398" t="n">
-        <v>23.0077037811279</v>
+        <v>23.0077056884766</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>26</v>
       </c>
       <c r="G1402" t="n">
-        <v>22.7452621459961</v>
+        <v>22.7452602386475</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1408" t="n">
-        <v>22.9202213287354</v>
+        <v>22.920223236084</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>25</v>
       </c>
       <c r="G1410" t="n">
-        <v>21.8704433441162</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1411" t="n">
-        <v>21.345552444458</v>
+        <v>21.3455505371094</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>23.0077037811279</v>
+        <v>23.0077056884766</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1414" t="n">
-        <v>23.0077037811279</v>
+        <v>23.0077056884766</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1416" t="n">
-        <v>22.9202213287354</v>
+        <v>22.920223236084</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>26</v>
       </c>
       <c r="G1417" t="n">
-        <v>22.7452621459961</v>
+        <v>22.7452602386475</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>23.0077037811279</v>
+        <v>23.0077056884766</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1423" t="n">
-        <v>23.0077037811279</v>
+        <v>23.0077056884766</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1425" t="n">
-        <v>23.0077037811279</v>
+        <v>23.0077056884766</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1426" t="n">
-        <v>22.9202213287354</v>
+        <v>22.920223236084</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1427" t="n">
-        <v>22.9202213287354</v>
+        <v>22.920223236084</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1428" t="n">
-        <v>23.0077037811279</v>
+        <v>23.0077056884766</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>23.5325927734375</v>
+        <v>23.5325946807861</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>25</v>
       </c>
       <c r="G1433" t="n">
-        <v>21.8704433441162</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1434" t="n">
-        <v>21.7829608917236</v>
+        <v>21.782958984375</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1436" t="n">
-        <v>22.1328868865967</v>
+        <v>22.1328887939453</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>25</v>
       </c>
       <c r="G1440" t="n">
-        <v>21.8704433441162</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>25</v>
       </c>
       <c r="G1441" t="n">
-        <v>21.8704433441162</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>25</v>
       </c>
       <c r="G1442" t="n">
-        <v>21.8704433441162</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1443" t="n">
-        <v>21.7829608917236</v>
+        <v>21.782958984375</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>25</v>
       </c>
       <c r="G1447" t="n">
-        <v>21.8704433441162</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1448" t="n">
-        <v>21.2580699920654</v>
+        <v>21.2580680847168</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1454" t="n">
-        <v>21.2580699920654</v>
+        <v>21.2580680847168</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>20.6456966400146</v>
+        <v>20.6456985473633</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1458" t="n">
-        <v>20.9081401824951</v>
+        <v>20.9081420898438</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1467" t="n">
-        <v>18.8960628509521</v>
+        <v>18.8960647583008</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1473" t="n">
-        <v>21.2580699920654</v>
+        <v>21.2580680847168</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1475" t="n">
-        <v>22.1328868865967</v>
+        <v>22.1328887939453</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>28</v>
       </c>
       <c r="G1488" t="n">
-        <v>24.49489402771</v>
+        <v>24.4948959350586</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1489" t="n">
-        <v>24.2324504852295</v>
+        <v>24.2324523925781</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>23.8825225830078</v>
+        <v>23.8825206756592</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1493" t="n">
-        <v>23.5325927734375</v>
+        <v>23.5325946807861</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>26</v>
       </c>
       <c r="G1494" t="n">
-        <v>22.7452621459961</v>
+        <v>22.7452602386475</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1496" t="n">
-        <v>22.1328868865967</v>
+        <v>22.1328887939453</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1499" t="n">
-        <v>20.9081401824951</v>
+        <v>20.9081420898438</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>23</v>
       </c>
       <c r="G1503" t="n">
-        <v>20.1208057403564</v>
+        <v>20.1208076477051</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1506" t="n">
-        <v>20.6456966400146</v>
+        <v>20.6456985473633</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1507" t="n">
-        <v>20.2957706451416</v>
+        <v>20.295768737793</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1514" t="n">
-        <v>19.5959148406982</v>
+        <v>19.5959167480469</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.2957706451416</v>
+        <v>20.295768737793</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.2957706451416</v>
+        <v>20.295768737793</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1520" t="n">
-        <v>20.2957706451416</v>
+        <v>20.295768737793</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1523" t="n">
-        <v>21.2580699920654</v>
+        <v>21.2580680847168</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1524" t="n">
-        <v>21.2580699920654</v>
+        <v>21.2580680847168</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1525" t="n">
-        <v>21.2580699920654</v>
+        <v>21.2580680847168</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>21.345552444458</v>
+        <v>21.3455505371094</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1528" t="n">
-        <v>21.345552444458</v>
+        <v>21.3455505371094</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1529" t="n">
-        <v>21.345552444458</v>
+        <v>21.3455505371094</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1532" t="n">
-        <v>20.2957706451416</v>
+        <v>20.295768737793</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1536" t="n">
-        <v>21.345552444458</v>
+        <v>21.3455505371094</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1540" t="n">
-        <v>22.1328868865967</v>
+        <v>22.1328887939453</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1542" t="n">
-        <v>21.2580699920654</v>
+        <v>21.2580680847168</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1543" t="n">
-        <v>21.7829608917236</v>
+        <v>21.782958984375</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1548" t="n">
-        <v>21.7829608917236</v>
+        <v>21.782958984375</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1549" t="n">
-        <v>21.7829608917236</v>
+        <v>21.782958984375</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>26</v>
       </c>
       <c r="G1554" t="n">
-        <v>22.7452621459961</v>
+        <v>22.7452602386475</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>22.1328868865967</v>
+        <v>22.1328887939453</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1561" t="n">
-        <v>18.8960628509521</v>
+        <v>18.8960647583008</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>21</v>
       </c>
       <c r="G1564" t="n">
-        <v>18.3711719512939</v>
+        <v>18.3711700439453</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1566" t="n">
-        <v>17.8462829589844</v>
+        <v>17.8462810516357</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1567" t="n">
-        <v>17.3651313781738</v>
+        <v>17.3651294708252</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1575" t="n">
-        <v>16.009162902832</v>
+        <v>16.0091648101807</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1576" t="n">
-        <v>16.009162902832</v>
+        <v>16.0091648101807</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.9277229309082</v>
+        <v>16.9277248382568</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1578" t="n">
-        <v>16.5340538024902</v>
+        <v>16.5340557098389</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1584" t="n">
-        <v>17.8462829589844</v>
+        <v>17.8462810516357</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1585" t="n">
-        <v>17.7587985992432</v>
+        <v>17.7587966918945</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1588" t="n">
-        <v>18.6336135864258</v>
+        <v>18.6336154937744</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1589" t="n">
-        <v>18.8960628509521</v>
+        <v>18.8960647583008</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1590" t="n">
-        <v>19.5959148406982</v>
+        <v>19.5959167480469</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1592" t="n">
-        <v>21.345552444458</v>
+        <v>21.3455505371094</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1625" t="n">
-        <v>21.7392196655273</v>
+        <v>21.7392177581787</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>25</v>
       </c>
       <c r="G1626" t="n">
-        <v>21.8704433441162</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>25</v>
       </c>
       <c r="G1627" t="n">
-        <v>21.8704433441162</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>25.75</v>
       </c>
       <c r="G1629" t="n">
-        <v>22.526554107666</v>
+        <v>22.5265560150146</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>12.1999998092651</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>6739</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>12.1999998092651</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>11.8500003814697</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>11.8500003814697</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>11.3500003814697</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>11.1999998092651</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>9812</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>11.1499996185303</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>11.1499996185303</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>11.1999998092651</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>1670</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>11.3500003814697</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>11.1000003814697</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>11.1999998092651</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>2596</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>11.3500003814697</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>11.1999998092651</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>11.25</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>11.1999998092651</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>320</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>11.1499996185303</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>2289</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>11.1499996185303</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>11.1499996185303</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAB.MI.xlsx
+++ b/data/SAB.MI.xlsx
@@ -427,7 +427,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G2" t="n">
-        <v>8.2108154296875</v>
+        <v>8.21081733703613</v>
       </c>
       <c r="H2" t="n">
         <v>7057</v>
@@ -514,7 +514,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>7.98773574829102</v>
+        <v>7.98773670196533</v>
       </c>
       <c r="H5" t="n">
         <v>7293</v>
@@ -543,7 +543,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G6" t="n">
-        <v>8.02371692657471</v>
+        <v>8.02371597290039</v>
       </c>
       <c r="H6" t="n">
         <v>7155</v>
@@ -572,7 +572,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>8.02371692657471</v>
+        <v>8.02371597290039</v>
       </c>
       <c r="H7" t="n">
         <v>2915</v>
@@ -601,7 +601,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G8" t="n">
-        <v>7.97334289550781</v>
+        <v>7.97334384918213</v>
       </c>
       <c r="H8" t="n">
         <v>12005</v>
@@ -630,7 +630,7 @@
         <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>7.91577434539795</v>
+        <v>7.91577386856079</v>
       </c>
       <c r="H9" t="n">
         <v>6018</v>
@@ -688,7 +688,7 @@
         <v>10.5</v>
       </c>
       <c r="G11" t="n">
-        <v>7.55596542358398</v>
+        <v>7.5559663772583</v>
       </c>
       <c r="H11" t="n">
         <v>9401</v>
@@ -717,7 +717,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2177472114563</v>
+        <v>7.21774768829346</v>
       </c>
       <c r="H12" t="n">
         <v>6329</v>
@@ -775,7 +775,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G14" t="n">
-        <v>7.3112964630127</v>
+        <v>7.31129598617554</v>
       </c>
       <c r="H14" t="n">
         <v>10136</v>
@@ -804,7 +804,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G15" t="n">
-        <v>7.29690599441528</v>
+        <v>7.29690551757812</v>
       </c>
       <c r="H15" t="n">
         <v>15238</v>
@@ -862,7 +862,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G17" t="n">
-        <v>7.43363285064697</v>
+        <v>7.43363189697266</v>
       </c>
       <c r="H17" t="n">
         <v>7439</v>
@@ -891,7 +891,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G18" t="n">
-        <v>7.44802522659302</v>
+        <v>7.44802474975586</v>
       </c>
       <c r="H18" t="n">
         <v>11495</v>
@@ -920,7 +920,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G19" t="n">
-        <v>7.57035970687866</v>
+        <v>7.57035875320435</v>
       </c>
       <c r="H19" t="n">
         <v>681</v>
@@ -949,7 +949,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>7.30410051345825</v>
+        <v>7.30410099029541</v>
       </c>
       <c r="H20" t="n">
         <v>4238</v>
@@ -978,7 +978,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>7.44802522659302</v>
+        <v>7.44802474975586</v>
       </c>
       <c r="H21" t="n">
         <v>5210</v>
@@ -1007,7 +1007,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G22" t="n">
-        <v>7.47680902481079</v>
+        <v>7.47680997848511</v>
       </c>
       <c r="H22" t="n">
         <v>8357</v>
@@ -1065,7 +1065,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G24" t="n">
-        <v>7.44802522659302</v>
+        <v>7.44802474975586</v>
       </c>
       <c r="H24" t="n">
         <v>6482</v>
@@ -1094,7 +1094,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>7.34008169174194</v>
+        <v>7.3400821685791</v>
       </c>
       <c r="H25" t="n">
         <v>12706</v>
@@ -1123,7 +1123,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>7.3112964630127</v>
+        <v>7.31129598617554</v>
       </c>
       <c r="H26" t="n">
         <v>771</v>
@@ -1152,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>7.19615888595581</v>
+        <v>7.19615936279297</v>
       </c>
       <c r="H27" t="n">
         <v>8538</v>
@@ -1181,7 +1181,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G28" t="n">
-        <v>7.03784322738647</v>
+        <v>7.03784418106079</v>
       </c>
       <c r="H28" t="n">
         <v>2209</v>
@@ -1210,7 +1210,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>7.23213958740234</v>
+        <v>7.23213815689087</v>
       </c>
       <c r="H29" t="n">
         <v>5710</v>
@@ -1239,7 +1239,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G30" t="n">
-        <v>7.08461904525757</v>
+        <v>7.08461761474609</v>
       </c>
       <c r="H30" t="n">
         <v>4854</v>
@@ -1326,7 +1326,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G33" t="n">
-        <v>7.4983959197998</v>
+        <v>7.49839687347412</v>
       </c>
       <c r="H33" t="n">
         <v>4353</v>
@@ -1355,7 +1355,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>7.75026321411133</v>
+        <v>7.75026226043701</v>
       </c>
       <c r="H34" t="n">
         <v>7846</v>
@@ -1384,7 +1384,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G35" t="n">
-        <v>7.77904844284058</v>
+        <v>7.77904653549194</v>
       </c>
       <c r="H35" t="n">
         <v>22361</v>
@@ -1413,7 +1413,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>7.62792921066284</v>
+        <v>7.62792778015137</v>
       </c>
       <c r="H36" t="n">
         <v>2038</v>
@@ -1529,7 +1529,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G40" t="n">
-        <v>7.45521879196167</v>
+        <v>7.45521974563599</v>
       </c>
       <c r="H40" t="n">
         <v>5533</v>
@@ -1558,7 +1558,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>7.54157400131226</v>
+        <v>7.54157447814941</v>
       </c>
       <c r="H41" t="n">
         <v>5422</v>
@@ -1587,7 +1587,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>7.48400592803955</v>
+        <v>7.48400354385376</v>
       </c>
       <c r="H42" t="n">
         <v>9819</v>
@@ -1616,7 +1616,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G43" t="n">
-        <v>7.65671300888062</v>
+        <v>7.65671396255493</v>
       </c>
       <c r="H43" t="n">
         <v>2678</v>
@@ -1645,7 +1645,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G44" t="n">
-        <v>7.70708513259888</v>
+        <v>7.70708560943604</v>
       </c>
       <c r="H44" t="n">
         <v>3027</v>
@@ -1732,7 +1732,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G47" t="n">
-        <v>7.63512325286865</v>
+        <v>7.63512372970581</v>
       </c>
       <c r="H47" t="n">
         <v>4249</v>
@@ -1761,7 +1761,7 @@
         <v>10.5</v>
       </c>
       <c r="G48" t="n">
-        <v>7.55596542358398</v>
+        <v>7.5559663772583</v>
       </c>
       <c r="H48" t="n">
         <v>679</v>
@@ -1790,7 +1790,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>7.62792921066284</v>
+        <v>7.62792778015137</v>
       </c>
       <c r="H49" t="n">
         <v>725</v>
@@ -1819,7 +1819,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G50" t="n">
-        <v>7.57755517959595</v>
+        <v>7.57755422592163</v>
       </c>
       <c r="H50" t="n">
         <v>2691</v>
@@ -1848,7 +1848,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G51" t="n">
-        <v>7.60633993148804</v>
+        <v>7.60633945465088</v>
       </c>
       <c r="H51" t="n">
         <v>2492</v>
@@ -1877,7 +1877,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G52" t="n">
-        <v>7.63512325286865</v>
+        <v>7.63512372970581</v>
       </c>
       <c r="H52" t="n">
         <v>2196</v>
@@ -1906,7 +1906,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G53" t="n">
-        <v>7.63512325286865</v>
+        <v>7.63512372970581</v>
       </c>
       <c r="H53" t="n">
         <v>2571</v>
@@ -1935,7 +1935,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G54" t="n">
-        <v>7.56316184997559</v>
+        <v>7.5631628036499</v>
       </c>
       <c r="H54" t="n">
         <v>3953</v>
@@ -1964,7 +1964,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G55" t="n">
-        <v>7.4983959197998</v>
+        <v>7.49839687347412</v>
       </c>
       <c r="H55" t="n">
         <v>129</v>
@@ -2022,7 +2022,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G57" t="n">
-        <v>7.61353588104248</v>
+        <v>7.61353445053101</v>
       </c>
       <c r="H57" t="n">
         <v>8890</v>
@@ -2051,7 +2051,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G58" t="n">
-        <v>7.57755517959595</v>
+        <v>7.57755422592163</v>
       </c>
       <c r="H58" t="n">
         <v>15787</v>
@@ -2138,7 +2138,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G61" t="n">
-        <v>7.45521879196167</v>
+        <v>7.45521974563599</v>
       </c>
       <c r="H61" t="n">
         <v>4999</v>
@@ -2167,7 +2167,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>7.48400592803955</v>
+        <v>7.48400354385376</v>
       </c>
       <c r="H62" t="n">
         <v>6521</v>
@@ -2196,7 +2196,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>7.41204309463501</v>
+        <v>7.41204357147217</v>
       </c>
       <c r="H63" t="n">
         <v>5223</v>
@@ -2225,7 +2225,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G64" t="n">
-        <v>7.34008169174194</v>
+        <v>7.3400821685791</v>
       </c>
       <c r="H64" t="n">
         <v>5836</v>
@@ -2254,7 +2254,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>7.33288478851318</v>
+        <v>7.3328857421875</v>
       </c>
       <c r="H65" t="n">
         <v>3360</v>
@@ -2283,7 +2283,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>7.41204309463501</v>
+        <v>7.41204357147217</v>
       </c>
       <c r="H66" t="n">
         <v>6731</v>
@@ -2312,7 +2312,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G67" t="n">
-        <v>7.39765119552612</v>
+        <v>7.39765167236328</v>
       </c>
       <c r="H67" t="n">
         <v>1595</v>
@@ -2341,7 +2341,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G68" t="n">
-        <v>7.35447454452515</v>
+        <v>7.35447406768799</v>
       </c>
       <c r="H68" t="n">
         <v>2693</v>
@@ -2370,7 +2370,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>7.30410051345825</v>
+        <v>7.30410099029541</v>
       </c>
       <c r="H69" t="n">
         <v>2231</v>
@@ -2399,7 +2399,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G70" t="n">
-        <v>7.34008169174194</v>
+        <v>7.3400821685791</v>
       </c>
       <c r="H70" t="n">
         <v>2180</v>
@@ -2428,7 +2428,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G71" t="n">
-        <v>7.3184928894043</v>
+        <v>7.31849336624146</v>
       </c>
       <c r="H71" t="n">
         <v>2145</v>
@@ -2457,7 +2457,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G72" t="n">
-        <v>7.43363285064697</v>
+        <v>7.43363189697266</v>
       </c>
       <c r="H72" t="n">
         <v>3142</v>
@@ -2486,7 +2486,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G73" t="n">
-        <v>7.29690599441528</v>
+        <v>7.29690551757812</v>
       </c>
       <c r="H73" t="n">
         <v>3986</v>
@@ -2515,7 +2515,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G74" t="n">
-        <v>7.20335483551025</v>
+        <v>7.2033543586731</v>
       </c>
       <c r="H74" t="n">
         <v>1701</v>
@@ -2544,7 +2544,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G75" t="n">
-        <v>7.32569026947021</v>
+        <v>7.32568883895874</v>
       </c>
       <c r="H75" t="n">
         <v>8969</v>
@@ -2573,7 +2573,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>7.34008169174194</v>
+        <v>7.3400821685791</v>
       </c>
       <c r="H76" t="n">
         <v>33074</v>
@@ -2602,7 +2602,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G77" t="n">
-        <v>7.25372838973999</v>
+        <v>7.25372886657715</v>
       </c>
       <c r="H77" t="n">
         <v>6880</v>
@@ -2631,7 +2631,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G78" t="n">
-        <v>7.3112964630127</v>
+        <v>7.31129598617554</v>
       </c>
       <c r="H78" t="n">
         <v>2772</v>
@@ -2660,7 +2660,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G79" t="n">
-        <v>7.38325786590576</v>
+        <v>7.38325929641724</v>
       </c>
       <c r="H79" t="n">
         <v>3355</v>
@@ -2747,7 +2747,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>7.41204309463501</v>
+        <v>7.41204357147217</v>
       </c>
       <c r="H82" t="n">
         <v>1864</v>
@@ -2776,7 +2776,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G83" t="n">
-        <v>7.16017866134644</v>
+        <v>7.16017723083496</v>
       </c>
       <c r="H83" t="n">
         <v>33066</v>
@@ -2834,7 +2834,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G85" t="n">
-        <v>7.18176698684692</v>
+        <v>7.18176603317261</v>
       </c>
       <c r="H85" t="n">
         <v>3914</v>
@@ -2892,7 +2892,7 @@
         <v>9.90499973297119</v>
       </c>
       <c r="G87" t="n">
-        <v>7.12779474258423</v>
+        <v>7.12779569625854</v>
       </c>
       <c r="H87" t="n">
         <v>4280</v>
@@ -2921,7 +2921,7 @@
         <v>9.99499988555908</v>
       </c>
       <c r="G88" t="n">
-        <v>7.19256019592285</v>
+        <v>7.19255924224854</v>
       </c>
       <c r="H88" t="n">
         <v>2126</v>
@@ -2979,7 +2979,7 @@
         <v>10</v>
       </c>
       <c r="G90" t="n">
-        <v>7.19615888595581</v>
+        <v>7.19615936279297</v>
       </c>
       <c r="H90" t="n">
         <v>1349</v>
@@ -3008,7 +3008,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>7.23213958740234</v>
+        <v>7.23213815689087</v>
       </c>
       <c r="H91" t="n">
         <v>16005</v>
@@ -3066,7 +3066,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G93" t="n">
-        <v>7.28251218795776</v>
+        <v>7.28251123428345</v>
       </c>
       <c r="H93" t="n">
         <v>4060</v>
@@ -3095,7 +3095,7 @@
         <v>9.89500045776367</v>
       </c>
       <c r="G94" t="n">
-        <v>7.1205997467041</v>
+        <v>7.12059879302979</v>
       </c>
       <c r="H94" t="n">
         <v>10291</v>
@@ -3124,7 +3124,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>7.08101987838745</v>
+        <v>7.08102083206177</v>
       </c>
       <c r="H95" t="n">
         <v>5693</v>
@@ -3153,7 +3153,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G96" t="n">
-        <v>7.06662750244141</v>
+        <v>7.06662702560425</v>
       </c>
       <c r="H96" t="n">
         <v>6423</v>
@@ -3182,7 +3182,7 @@
         <v>9.75</v>
       </c>
       <c r="G97" t="n">
-        <v>7.01625537872314</v>
+        <v>7.01625490188599</v>
       </c>
       <c r="H97" t="n">
         <v>5738</v>
@@ -3211,7 +3211,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G98" t="n">
-        <v>6.98027420043945</v>
+        <v>6.98027324676514</v>
       </c>
       <c r="H98" t="n">
         <v>11377</v>
@@ -3240,7 +3240,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G99" t="n">
-        <v>7.08101987838745</v>
+        <v>7.08102083206177</v>
       </c>
       <c r="H99" t="n">
         <v>5130</v>
@@ -3269,7 +3269,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G100" t="n">
-        <v>7.20962810516357</v>
+        <v>7.20962762832642</v>
       </c>
       <c r="H100" t="n">
         <v>13703</v>
@@ -3298,7 +3298,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G101" t="n">
-        <v>7.48197507858276</v>
+        <v>7.48197555541992</v>
       </c>
       <c r="H101" t="n">
         <v>10696</v>
@@ -3327,7 +3327,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G102" t="n">
-        <v>7.42901945114136</v>
+        <v>7.42901849746704</v>
       </c>
       <c r="H102" t="n">
         <v>3570</v>
@@ -3356,7 +3356,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>7.43658494949341</v>
+        <v>7.43658351898193</v>
       </c>
       <c r="H103" t="n">
         <v>2431</v>
@@ -3385,7 +3385,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G104" t="n">
-        <v>7.48954057693481</v>
+        <v>7.48953914642334</v>
       </c>
       <c r="H104" t="n">
         <v>5396</v>
@@ -3414,7 +3414,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>7.53493165969849</v>
+        <v>7.53493309020996</v>
       </c>
       <c r="H105" t="n">
         <v>4428</v>
@@ -3443,7 +3443,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G106" t="n">
-        <v>7.43658494949341</v>
+        <v>7.43658351898193</v>
       </c>
       <c r="H106" t="n">
         <v>4278</v>
@@ -3472,7 +3472,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G107" t="n">
-        <v>7.48954057693481</v>
+        <v>7.48953914642334</v>
       </c>
       <c r="H107" t="n">
         <v>3326</v>
@@ -3530,7 +3530,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G109" t="n">
-        <v>7.27015018463135</v>
+        <v>7.27014875411987</v>
       </c>
       <c r="H109" t="n">
         <v>7010</v>
@@ -3559,7 +3559,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G110" t="n">
-        <v>7.20962810516357</v>
+        <v>7.20962762832642</v>
       </c>
       <c r="H110" t="n">
         <v>5673</v>
@@ -3588,7 +3588,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G111" t="n">
-        <v>7.3684983253479</v>
+        <v>7.36849784851074</v>
       </c>
       <c r="H111" t="n">
         <v>11079</v>
@@ -3617,7 +3617,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G112" t="n">
-        <v>7.2625846862793</v>
+        <v>7.26258611679077</v>
       </c>
       <c r="H112" t="n">
         <v>1809</v>
@@ -3646,7 +3646,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G113" t="n">
-        <v>7.22475910186768</v>
+        <v>7.22475957870483</v>
       </c>
       <c r="H113" t="n">
         <v>1787</v>
@@ -3675,7 +3675,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G114" t="n">
-        <v>7.2625846862793</v>
+        <v>7.26258611679077</v>
       </c>
       <c r="H114" t="n">
         <v>13073</v>
@@ -3704,7 +3704,7 @@
         <v>9.5</v>
       </c>
       <c r="G115" t="n">
-        <v>7.18693208694458</v>
+        <v>7.1869330406189</v>
       </c>
       <c r="H115" t="n">
         <v>9549</v>
@@ -3733,7 +3733,7 @@
         <v>9.5</v>
       </c>
       <c r="G116" t="n">
-        <v>7.18693208694458</v>
+        <v>7.1869330406189</v>
       </c>
       <c r="H116" t="n">
         <v>3463</v>
@@ -3762,7 +3762,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G117" t="n">
-        <v>6.98267316818237</v>
+        <v>6.98267269134521</v>
       </c>
       <c r="H117" t="n">
         <v>6492</v>
@@ -3791,7 +3791,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G118" t="n">
-        <v>6.63845634460449</v>
+        <v>6.63845586776733</v>
       </c>
       <c r="H118" t="n">
         <v>16538</v>
@@ -3878,7 +3878,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G121" t="n">
-        <v>7.14910650253296</v>
+        <v>7.14910697937012</v>
       </c>
       <c r="H121" t="n">
         <v>2449</v>
@@ -3907,7 +3907,7 @@
         <v>9.5</v>
       </c>
       <c r="G122" t="n">
-        <v>7.18693208694458</v>
+        <v>7.1869330406189</v>
       </c>
       <c r="H122" t="n">
         <v>2372</v>
@@ -3936,7 +3936,7 @@
         <v>9.5</v>
       </c>
       <c r="G123" t="n">
-        <v>7.18693208694458</v>
+        <v>7.1869330406189</v>
       </c>
       <c r="H123" t="n">
         <v>8131</v>
@@ -4023,7 +4023,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>6.96375942230225</v>
+        <v>6.96376037597656</v>
       </c>
       <c r="H126" t="n">
         <v>1445</v>
@@ -4052,7 +4052,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G127" t="n">
-        <v>7.04319381713867</v>
+        <v>7.04319429397583</v>
       </c>
       <c r="H127" t="n">
         <v>5726</v>
@@ -4081,7 +4081,7 @@
         <v>9.46500015258789</v>
       </c>
       <c r="G128" t="n">
-        <v>7.16045379638672</v>
+        <v>7.16045427322388</v>
       </c>
       <c r="H128" t="n">
         <v>753</v>
@@ -4110,7 +4110,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G129" t="n">
-        <v>7.06210613250732</v>
+        <v>7.06210708618164</v>
       </c>
       <c r="H129" t="n">
         <v>109</v>
@@ -4139,7 +4139,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G130" t="n">
-        <v>7.07345533370972</v>
+        <v>7.07345485687256</v>
       </c>
       <c r="H130" t="n">
         <v>3233</v>
@@ -4168,7 +4168,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G131" t="n">
-        <v>6.96375942230225</v>
+        <v>6.96376037597656</v>
       </c>
       <c r="H131" t="n">
         <v>693</v>
@@ -4197,7 +4197,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>6.83893346786499</v>
+        <v>6.83893394470215</v>
       </c>
       <c r="H132" t="n">
         <v>298</v>
@@ -4226,7 +4226,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>6.83893346786499</v>
+        <v>6.83893394470215</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G134" t="n">
-        <v>6.8918890953064</v>
+        <v>6.89189052581787</v>
       </c>
       <c r="H134" t="n">
         <v>725</v>
@@ -4313,7 +4313,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G136" t="n">
-        <v>6.85406446456909</v>
+        <v>6.85406398773193</v>
       </c>
       <c r="H136" t="n">
         <v>1888</v>
@@ -4371,7 +4371,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G138" t="n">
-        <v>6.8124566078186</v>
+        <v>6.81245517730713</v>
       </c>
       <c r="H138" t="n">
         <v>1921</v>
@@ -4458,7 +4458,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G141" t="n">
-        <v>6.88432645797729</v>
+        <v>6.88432502746582</v>
       </c>
       <c r="H141" t="n">
         <v>1708</v>
@@ -4487,7 +4487,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G142" t="n">
-        <v>6.92215061187744</v>
+        <v>6.9221510887146</v>
       </c>
       <c r="H142" t="n">
         <v>218</v>
@@ -4545,7 +4545,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G144" t="n">
-        <v>6.88432645797729</v>
+        <v>6.88432502746582</v>
       </c>
       <c r="H144" t="n">
         <v>218</v>
@@ -4574,7 +4574,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G145" t="n">
-        <v>6.9486289024353</v>
+        <v>6.94862842559814</v>
       </c>
       <c r="H145" t="n">
         <v>31</v>
@@ -4603,7 +4603,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G146" t="n">
-        <v>6.89945554733276</v>
+        <v>6.89945650100708</v>
       </c>
       <c r="H146" t="n">
         <v>714</v>
@@ -4632,7 +4632,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G147" t="n">
-        <v>6.888108253479</v>
+        <v>6.88810729980469</v>
       </c>
       <c r="H147" t="n">
         <v>3981</v>
@@ -4661,7 +4661,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G148" t="n">
-        <v>6.92593383789062</v>
+        <v>6.92593193054199</v>
       </c>
       <c r="H148" t="n">
         <v>2146</v>
@@ -4690,7 +4690,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G149" t="n">
-        <v>6.91080331802368</v>
+        <v>6.91080379486084</v>
       </c>
       <c r="H149" t="n">
         <v>1286</v>
@@ -4719,7 +4719,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G150" t="n">
-        <v>7.01293277740479</v>
+        <v>7.01293420791626</v>
       </c>
       <c r="H150" t="n">
         <v>987</v>
@@ -4748,7 +4748,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G151" t="n">
-        <v>6.8124566078186</v>
+        <v>6.81245517730713</v>
       </c>
       <c r="H151" t="n">
         <v>1901</v>
@@ -4864,7 +4864,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>6.86919450759888</v>
+        <v>6.86919498443604</v>
       </c>
       <c r="H155" t="n">
         <v>1552</v>
@@ -4893,7 +4893,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G156" t="n">
-        <v>6.94484758377075</v>
+        <v>6.94484615325928</v>
       </c>
       <c r="H156" t="n">
         <v>123</v>
@@ -4951,7 +4951,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>6.83515167236328</v>
+        <v>6.83515119552612</v>
       </c>
       <c r="H158" t="n">
         <v>1214</v>
@@ -5009,7 +5009,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G160" t="n">
-        <v>6.81623697280884</v>
+        <v>6.81623935699463</v>
       </c>
       <c r="H160" t="n">
         <v>4191</v>
@@ -5038,7 +5038,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G161" t="n">
-        <v>6.88054275512695</v>
+        <v>6.88054370880127</v>
       </c>
       <c r="H161" t="n">
         <v>664</v>
@@ -5154,7 +5154,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G165" t="n">
-        <v>6.94484758377075</v>
+        <v>6.94484615325928</v>
       </c>
       <c r="H165" t="n">
         <v>1518</v>
@@ -5183,7 +5183,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G166" t="n">
-        <v>6.94484758377075</v>
+        <v>6.94484615325928</v>
       </c>
       <c r="H166" t="n">
         <v>43</v>
@@ -5212,7 +5212,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G167" t="n">
-        <v>6.97510719299316</v>
+        <v>6.97510862350464</v>
       </c>
       <c r="H167" t="n">
         <v>1172</v>
@@ -5241,7 +5241,7 @@
         <v>9.25</v>
       </c>
       <c r="G168" t="n">
-        <v>6.99780321121216</v>
+        <v>6.997802734375</v>
       </c>
       <c r="H168" t="n">
         <v>1589</v>
@@ -5270,7 +5270,7 @@
         <v>9.25</v>
       </c>
       <c r="G169" t="n">
-        <v>6.99780321121216</v>
+        <v>6.997802734375</v>
       </c>
       <c r="H169" t="n">
         <v>272</v>
@@ -5299,7 +5299,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G170" t="n">
-        <v>6.99023818969727</v>
+        <v>6.99023771286011</v>
       </c>
       <c r="H170" t="n">
         <v>1824</v>
@@ -5328,7 +5328,7 @@
         <v>9.25</v>
       </c>
       <c r="G171" t="n">
-        <v>6.99780321121216</v>
+        <v>6.997802734375</v>
       </c>
       <c r="H171" t="n">
         <v>46</v>
@@ -5357,7 +5357,7 @@
         <v>9.25</v>
       </c>
       <c r="G172" t="n">
-        <v>6.99780321121216</v>
+        <v>6.997802734375</v>
       </c>
       <c r="H172" t="n">
         <v>2747</v>
@@ -5386,7 +5386,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G173" t="n">
-        <v>6.94106435775757</v>
+        <v>6.94106531143188</v>
       </c>
       <c r="H173" t="n">
         <v>1306</v>
@@ -5415,7 +5415,7 @@
         <v>9.25</v>
       </c>
       <c r="G174" t="n">
-        <v>6.99780321121216</v>
+        <v>6.997802734375</v>
       </c>
       <c r="H174" t="n">
         <v>6215</v>
@@ -5444,7 +5444,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G175" t="n">
-        <v>6.9486289024353</v>
+        <v>6.94862842559814</v>
       </c>
       <c r="H175" t="n">
         <v>2204</v>
@@ -5473,7 +5473,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G176" t="n">
-        <v>6.86919450759888</v>
+        <v>6.86919498443604</v>
       </c>
       <c r="H176" t="n">
         <v>26160</v>
@@ -5502,7 +5502,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>6.86919450759888</v>
+        <v>6.86919498443604</v>
       </c>
       <c r="H177" t="n">
         <v>3587</v>
@@ -5531,7 +5531,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G178" t="n">
-        <v>6.82380342483521</v>
+        <v>6.82380390167236</v>
       </c>
       <c r="H178" t="n">
         <v>3076</v>
@@ -5618,7 +5618,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>6.65736961364746</v>
+        <v>6.6573691368103</v>
       </c>
       <c r="H181" t="n">
         <v>2485</v>
@@ -5647,7 +5647,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>6.64602088928223</v>
+        <v>6.64602041244507</v>
       </c>
       <c r="H182" t="n">
         <v>3436</v>
@@ -5734,7 +5734,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>6.83515167236328</v>
+        <v>6.83515119552612</v>
       </c>
       <c r="H185" t="n">
         <v>2438</v>
@@ -5763,7 +5763,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G186" t="n">
-        <v>6.88054275512695</v>
+        <v>6.88054370880127</v>
       </c>
       <c r="H186" t="n">
         <v>2024</v>
@@ -5792,7 +5792,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G187" t="n">
-        <v>6.88432645797729</v>
+        <v>6.88432502746582</v>
       </c>
       <c r="H187" t="n">
         <v>718</v>
@@ -5821,7 +5821,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G188" t="n">
-        <v>6.91080331802368</v>
+        <v>6.91080379486084</v>
       </c>
       <c r="H188" t="n">
         <v>538</v>
@@ -5850,7 +5850,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G189" t="n">
-        <v>6.85784769058228</v>
+        <v>6.8578462600708</v>
       </c>
       <c r="H189" t="n">
         <v>3266</v>
@@ -5879,7 +5879,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G190" t="n">
-        <v>6.64602088928223</v>
+        <v>6.64602041244507</v>
       </c>
       <c r="H190" t="n">
         <v>4475</v>
@@ -5908,7 +5908,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G191" t="n">
-        <v>6.82380342483521</v>
+        <v>6.82380390167236</v>
       </c>
       <c r="H191" t="n">
         <v>2688</v>
@@ -5937,7 +5937,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G192" t="n">
-        <v>6.84271621704102</v>
+        <v>6.84271669387817</v>
       </c>
       <c r="H192" t="n">
         <v>1234</v>
@@ -5966,7 +5966,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>6.83893346786499</v>
+        <v>6.83893394470215</v>
       </c>
       <c r="H193" t="n">
         <v>3048</v>
@@ -5995,7 +5995,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G194" t="n">
-        <v>6.83515167236328</v>
+        <v>6.83515119552612</v>
       </c>
       <c r="H194" t="n">
         <v>5276</v>
@@ -6024,7 +6024,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G195" t="n">
-        <v>6.86162948608398</v>
+        <v>6.86162853240967</v>
       </c>
       <c r="H195" t="n">
         <v>1276</v>
@@ -6053,7 +6053,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G196" t="n">
-        <v>6.86162948608398</v>
+        <v>6.86162853240967</v>
       </c>
       <c r="H196" t="n">
         <v>906</v>
@@ -6082,7 +6082,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G197" t="n">
-        <v>6.76328182220459</v>
+        <v>6.76328134536743</v>
       </c>
       <c r="H197" t="n">
         <v>119</v>
@@ -6111,7 +6111,7 @@
         <v>9.0649995803833</v>
       </c>
       <c r="G198" t="n">
-        <v>6.85784769058228</v>
+        <v>6.8578462600708</v>
       </c>
       <c r="H198" t="n">
         <v>1975</v>
@@ -6140,7 +6140,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G199" t="n">
-        <v>6.88054275512695</v>
+        <v>6.88054370880127</v>
       </c>
       <c r="H199" t="n">
         <v>5221</v>
@@ -6169,7 +6169,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G200" t="n">
-        <v>6.85406446456909</v>
+        <v>6.85406398773193</v>
       </c>
       <c r="H200" t="n">
         <v>951</v>
@@ -6227,7 +6227,7 @@
         <v>8.95499992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>6.77463006973267</v>
+        <v>6.77463054656982</v>
       </c>
       <c r="H202" t="n">
         <v>13440</v>
@@ -6285,7 +6285,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G204" t="n">
-        <v>6.7330207824707</v>
+        <v>6.73302125930786</v>
       </c>
       <c r="H204" t="n">
         <v>4491</v>
@@ -6314,7 +6314,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G205" t="n">
-        <v>6.7330207824707</v>
+        <v>6.73302125930786</v>
       </c>
       <c r="H205" t="n">
         <v>5304</v>
@@ -6343,7 +6343,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G206" t="n">
-        <v>6.75571775436401</v>
+        <v>6.75571727752686</v>
       </c>
       <c r="H206" t="n">
         <v>701</v>
@@ -6372,7 +6372,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>6.77084684371948</v>
+        <v>6.77084589004517</v>
       </c>
       <c r="H207" t="n">
         <v>991</v>
@@ -6430,7 +6430,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G209" t="n">
-        <v>6.8124566078186</v>
+        <v>6.81245517730713</v>
       </c>
       <c r="H209" t="n">
         <v>2764</v>
@@ -6459,7 +6459,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G210" t="n">
-        <v>6.8124566078186</v>
+        <v>6.81245517730713</v>
       </c>
       <c r="H210" t="n">
         <v>1491</v>
@@ -6604,7 +6604,7 @@
         <v>8.92500019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>6.75193405151367</v>
+        <v>6.75193500518799</v>
       </c>
       <c r="H215" t="n">
         <v>999</v>
@@ -6633,7 +6633,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G216" t="n">
-        <v>6.74058628082275</v>
+        <v>6.7405858039856</v>
       </c>
       <c r="H216" t="n">
         <v>435</v>
@@ -6662,7 +6662,7 @@
         <v>8.94499969482422</v>
       </c>
       <c r="G217" t="n">
-        <v>6.76706457138062</v>
+        <v>6.76706504821777</v>
       </c>
       <c r="H217" t="n">
         <v>900</v>
@@ -6691,7 +6691,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G218" t="n">
-        <v>6.7330207824707</v>
+        <v>6.73302125930786</v>
       </c>
       <c r="H218" t="n">
         <v>4043</v>
@@ -6720,7 +6720,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G219" t="n">
-        <v>6.7330207824707</v>
+        <v>6.73302125930786</v>
       </c>
       <c r="H219" t="n">
         <v>5475</v>
@@ -6749,7 +6749,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G220" t="n">
-        <v>6.82380342483521</v>
+        <v>6.82380390167236</v>
       </c>
       <c r="H220" t="n">
         <v>6439</v>
@@ -6836,7 +6836,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G223" t="n">
-        <v>6.77084684371948</v>
+        <v>6.77084589004517</v>
       </c>
       <c r="H223" t="n">
         <v>1852</v>
@@ -6865,7 +6865,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G224" t="n">
-        <v>6.76328182220459</v>
+        <v>6.76328134536743</v>
       </c>
       <c r="H224" t="n">
         <v>5822</v>
@@ -6894,7 +6894,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G225" t="n">
-        <v>6.76328182220459</v>
+        <v>6.76328134536743</v>
       </c>
       <c r="H225" t="n">
         <v>2155</v>
@@ -6923,7 +6923,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>6.81623697280884</v>
+        <v>6.81623935699463</v>
       </c>
       <c r="H226" t="n">
         <v>559</v>
@@ -6952,7 +6952,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G227" t="n">
-        <v>6.92215061187744</v>
+        <v>6.9221510887146</v>
       </c>
       <c r="H227" t="n">
         <v>12368</v>
@@ -6981,7 +6981,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G228" t="n">
-        <v>6.87675952911377</v>
+        <v>6.87676000595093</v>
       </c>
       <c r="H228" t="n">
         <v>4340</v>
@@ -7068,7 +7068,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G231" t="n">
-        <v>6.76328182220459</v>
+        <v>6.76328134536743</v>
       </c>
       <c r="H231" t="n">
         <v>12292</v>
@@ -7097,7 +7097,7 @@
         <v>8.75</v>
       </c>
       <c r="G232" t="n">
-        <v>6.61954307556152</v>
+        <v>6.619544506073</v>
       </c>
       <c r="H232" t="n">
         <v>3899</v>
@@ -7126,7 +7126,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>6.62710857391357</v>
+        <v>6.62710905075073</v>
       </c>
       <c r="H233" t="n">
         <v>3219</v>
@@ -7184,7 +7184,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.65736961364746</v>
+        <v>6.6573691368103</v>
       </c>
       <c r="H235" t="n">
         <v>1254</v>
@@ -7213,7 +7213,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>6.65736961364746</v>
+        <v>6.6573691368103</v>
       </c>
       <c r="H236" t="n">
         <v>7146</v>
@@ -7242,7 +7242,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G237" t="n">
-        <v>6.63467359542847</v>
+        <v>6.63467407226562</v>
       </c>
       <c r="H237" t="n">
         <v>7793</v>
@@ -7271,7 +7271,7 @@
         <v>8.77000045776367</v>
       </c>
       <c r="G238" t="n">
-        <v>6.63467359542847</v>
+        <v>6.63467407226562</v>
       </c>
       <c r="H238" t="n">
         <v>3426</v>
@@ -7300,7 +7300,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G239" t="n">
-        <v>6.65736961364746</v>
+        <v>6.6573691368103</v>
       </c>
       <c r="H239" t="n">
         <v>5993</v>
@@ -7329,7 +7329,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>6.65358638763428</v>
+        <v>6.65358734130859</v>
       </c>
       <c r="H240" t="n">
         <v>21433</v>
@@ -7416,7 +7416,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G243" t="n">
-        <v>6.85406446456909</v>
+        <v>6.85406398773193</v>
       </c>
       <c r="H243" t="n">
         <v>7013</v>
@@ -7445,7 +7445,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G244" t="n">
-        <v>6.91080331802368</v>
+        <v>6.91080379486084</v>
       </c>
       <c r="H244" t="n">
         <v>5150</v>
@@ -7474,7 +7474,7 @@
         <v>9.13500022888184</v>
       </c>
       <c r="G245" t="n">
-        <v>6.91080331802368</v>
+        <v>6.91080379486084</v>
       </c>
       <c r="H245" t="n">
         <v>6673</v>
@@ -7503,7 +7503,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>6.84649991989136</v>
+        <v>6.8464994430542</v>
       </c>
       <c r="H246" t="n">
         <v>11340</v>
@@ -7532,7 +7532,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G247" t="n">
-        <v>6.88432645797729</v>
+        <v>6.88432502746582</v>
       </c>
       <c r="H247" t="n">
         <v>10930</v>
@@ -7561,7 +7561,7 @@
         <v>9.25</v>
       </c>
       <c r="G248" t="n">
-        <v>6.99780321121216</v>
+        <v>6.997802734375</v>
       </c>
       <c r="H248" t="n">
         <v>11173</v>
@@ -7590,7 +7590,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G249" t="n">
-        <v>7.14154052734375</v>
+        <v>7.14154100418091</v>
       </c>
       <c r="H249" t="n">
         <v>20317</v>
@@ -7619,7 +7619,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G250" t="n">
-        <v>7.14910650253296</v>
+        <v>7.14910697937012</v>
       </c>
       <c r="H250" t="n">
         <v>16489</v>
@@ -7677,7 +7677,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G252" t="n">
-        <v>7.48197507858276</v>
+        <v>7.48197555541992</v>
       </c>
       <c r="H252" t="n">
         <v>7563</v>
@@ -7706,7 +7706,7 @@
         <v>9.875</v>
       </c>
       <c r="G253" t="n">
-        <v>7.47062873840332</v>
+        <v>7.47062730789185</v>
       </c>
       <c r="H253" t="n">
         <v>4823</v>
@@ -7735,7 +7735,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G254" t="n">
-        <v>7.5954532623291</v>
+        <v>7.59545278549194</v>
       </c>
       <c r="H254" t="n">
         <v>5454</v>
@@ -7764,7 +7764,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G255" t="n">
-        <v>7.5954532623291</v>
+        <v>7.59545278549194</v>
       </c>
       <c r="H255" t="n">
         <v>2909</v>
@@ -7793,7 +7793,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G256" t="n">
-        <v>7.71649742126465</v>
+        <v>7.71649646759033</v>
       </c>
       <c r="H256" t="n">
         <v>15459</v>
@@ -7822,7 +7822,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>7.86780071258545</v>
+        <v>7.86780023574829</v>
       </c>
       <c r="H257" t="n">
         <v>14363</v>
@@ -7880,7 +7880,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G259" t="n">
-        <v>7.71649742126465</v>
+        <v>7.71649646759033</v>
       </c>
       <c r="H259" t="n">
         <v>14267</v>
@@ -7938,7 +7938,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G261" t="n">
-        <v>7.8602352142334</v>
+        <v>7.86023664474487</v>
       </c>
       <c r="H261" t="n">
         <v>16728</v>
@@ -7967,7 +7967,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>7.86780071258545</v>
+        <v>7.86780023574829</v>
       </c>
       <c r="H262" t="n">
         <v>11097</v>
@@ -8025,7 +8025,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>7.79214811325073</v>
+        <v>7.79214859008789</v>
       </c>
       <c r="H264" t="n">
         <v>4385</v>
@@ -8083,7 +8083,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G266" t="n">
-        <v>7.86780071258545</v>
+        <v>7.86780023574829</v>
       </c>
       <c r="H266" t="n">
         <v>7781</v>
@@ -8112,7 +8112,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G267" t="n">
-        <v>7.8602352142334</v>
+        <v>7.86023664474487</v>
       </c>
       <c r="H267" t="n">
         <v>9769</v>
@@ -8141,7 +8141,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G268" t="n">
-        <v>7.8602352142334</v>
+        <v>7.86023664474487</v>
       </c>
       <c r="H268" t="n">
         <v>21243</v>
@@ -8199,7 +8199,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G270" t="n">
-        <v>8.20066738128662</v>
+        <v>8.20066928863525</v>
       </c>
       <c r="H270" t="n">
         <v>17998</v>
@@ -8257,7 +8257,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G272" t="n">
-        <v>8.07962608337402</v>
+        <v>8.07962512969971</v>
       </c>
       <c r="H272" t="n">
         <v>7153</v>
@@ -8286,7 +8286,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G273" t="n">
-        <v>8.0115385055542</v>
+        <v>8.01153945922852</v>
       </c>
       <c r="H273" t="n">
         <v>12791</v>
@@ -8315,7 +8315,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G274" t="n">
-        <v>8.04936408996582</v>
+        <v>8.04936599731445</v>
       </c>
       <c r="H274" t="n">
         <v>9841</v>
@@ -8373,7 +8373,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>8.09475708007812</v>
+        <v>8.09475612640381</v>
       </c>
       <c r="H276" t="n">
         <v>9624</v>
@@ -8431,7 +8431,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G278" t="n">
-        <v>7.92075777053833</v>
+        <v>7.92075681686401</v>
       </c>
       <c r="H278" t="n">
         <v>7094</v>
@@ -8518,7 +8518,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G281" t="n">
-        <v>7.95858192443848</v>
+        <v>7.95858144760132</v>
       </c>
       <c r="H281" t="n">
         <v>6336</v>
@@ -8547,7 +8547,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G282" t="n">
-        <v>8.0115385055542</v>
+        <v>8.01153945922852</v>
       </c>
       <c r="H282" t="n">
         <v>2148</v>
@@ -8576,7 +8576,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G283" t="n">
-        <v>7.88293027877808</v>
+        <v>7.88293075561523</v>
       </c>
       <c r="H283" t="n">
         <v>5004</v>
@@ -8634,7 +8634,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G285" t="n">
-        <v>7.88293027877808</v>
+        <v>7.88293075561523</v>
       </c>
       <c r="H285" t="n">
         <v>1327</v>
@@ -8663,7 +8663,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G286" t="n">
-        <v>7.88293027877808</v>
+        <v>7.88293075561523</v>
       </c>
       <c r="H286" t="n">
         <v>2227</v>
@@ -8692,7 +8692,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G287" t="n">
-        <v>8.0115385055542</v>
+        <v>8.01153945922852</v>
       </c>
       <c r="H287" t="n">
         <v>3473</v>
@@ -8721,7 +8721,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G288" t="n">
-        <v>7.9131908416748</v>
+        <v>7.91319179534912</v>
       </c>
       <c r="H288" t="n">
         <v>2067</v>
@@ -8750,7 +8750,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G289" t="n">
-        <v>8.00397491455078</v>
+        <v>8.00397300720215</v>
       </c>
       <c r="H289" t="n">
         <v>23609</v>
@@ -8808,7 +8808,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G291" t="n">
-        <v>7.96614789962769</v>
+        <v>7.96614742279053</v>
       </c>
       <c r="H291" t="n">
         <v>15340</v>
@@ -8866,7 +8866,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G293" t="n">
-        <v>8.09475708007812</v>
+        <v>8.09475612640381</v>
       </c>
       <c r="H293" t="n">
         <v>10602</v>
@@ -8953,7 +8953,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G296" t="n">
-        <v>7.98884439468384</v>
+        <v>7.98884248733521</v>
       </c>
       <c r="H296" t="n">
         <v>5302</v>
@@ -9040,7 +9040,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G299" t="n">
-        <v>7.99640846252441</v>
+        <v>7.99640941619873</v>
       </c>
       <c r="H299" t="n">
         <v>6616</v>
@@ -9098,7 +9098,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G301" t="n">
-        <v>8.26875591278076</v>
+        <v>8.26875400543213</v>
       </c>
       <c r="H301" t="n">
         <v>24870</v>
@@ -9127,7 +9127,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G302" t="n">
-        <v>8.38223266601562</v>
+        <v>8.38223361968994</v>
       </c>
       <c r="H302" t="n">
         <v>20338</v>
@@ -9185,7 +9185,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G304" t="n">
-        <v>8.63188457489014</v>
+        <v>8.63188362121582</v>
       </c>
       <c r="H304" t="n">
         <v>14804</v>
@@ -9243,7 +9243,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G306" t="n">
-        <v>8.91936206817627</v>
+        <v>8.91936302185059</v>
       </c>
       <c r="H306" t="n">
         <v>17812</v>
@@ -9272,7 +9272,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G307" t="n">
-        <v>8.88153648376465</v>
+        <v>8.88153553009033</v>
       </c>
       <c r="H307" t="n">
         <v>11401</v>
@@ -9417,7 +9417,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G312" t="n">
-        <v>8.97988224029541</v>
+        <v>8.97988319396973</v>
       </c>
       <c r="H312" t="n">
         <v>4373</v>
@@ -9446,7 +9446,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>9.153883934021</v>
+        <v>9.15388298034668</v>
       </c>
       <c r="H313" t="n">
         <v>40987</v>
@@ -9475,7 +9475,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G314" t="n">
-        <v>9.27492618560791</v>
+        <v>9.27492427825928</v>
       </c>
       <c r="H314" t="n">
         <v>20308</v>
@@ -9504,7 +9504,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>9.34301471710205</v>
+        <v>9.34301280975342</v>
       </c>
       <c r="H315" t="n">
         <v>15327</v>
@@ -9533,7 +9533,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>9.79692268371582</v>
+        <v>9.79692363739014</v>
       </c>
       <c r="H316" t="n">
         <v>46314</v>
@@ -9562,7 +9562,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G317" t="n">
-        <v>10.0465745925903</v>
+        <v>10.0465755462646</v>
       </c>
       <c r="H317" t="n">
         <v>68015</v>
@@ -9620,7 +9620,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G319" t="n">
-        <v>9.86501026153564</v>
+        <v>9.86501312255859</v>
       </c>
       <c r="H319" t="n">
         <v>18915</v>
@@ -9678,7 +9678,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G321" t="n">
-        <v>9.72883701324463</v>
+        <v>9.72883796691895</v>
       </c>
       <c r="H321" t="n">
         <v>7777</v>
@@ -9707,7 +9707,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G322" t="n">
-        <v>9.66831588745117</v>
+        <v>9.66831493377686</v>
       </c>
       <c r="H322" t="n">
         <v>13581</v>
@@ -9736,7 +9736,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G323" t="n">
-        <v>9.60022830963135</v>
+        <v>9.60022926330566</v>
       </c>
       <c r="H323" t="n">
         <v>8295</v>
@@ -9765,7 +9765,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G324" t="n">
-        <v>9.68344593048096</v>
+        <v>9.68344688415527</v>
       </c>
       <c r="H324" t="n">
         <v>16199</v>
@@ -9823,7 +9823,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G326" t="n">
-        <v>9.74396800994873</v>
+        <v>9.74396896362305</v>
       </c>
       <c r="H326" t="n">
         <v>11054</v>
@@ -9852,7 +9852,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G327" t="n">
-        <v>9.63805484771729</v>
+        <v>9.63805389404297</v>
       </c>
       <c r="H327" t="n">
         <v>3087</v>
@@ -9881,7 +9881,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>9.75909900665283</v>
+        <v>9.75909614562988</v>
       </c>
       <c r="H328" t="n">
         <v>14145</v>
@@ -9910,7 +9910,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G329" t="n">
-        <v>9.69857501983643</v>
+        <v>9.69857597351074</v>
       </c>
       <c r="H329" t="n">
         <v>2883</v>
@@ -9968,7 +9968,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G331" t="n">
-        <v>9.76666450500488</v>
+        <v>9.76666259765625</v>
       </c>
       <c r="H331" t="n">
         <v>8027</v>
@@ -10084,7 +10084,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>9.68344593048096</v>
+        <v>9.68344688415527</v>
       </c>
       <c r="H335" t="n">
         <v>1344</v>
@@ -10142,7 +10142,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>9.72883701324463</v>
+        <v>9.72883796691895</v>
       </c>
       <c r="H337" t="n">
         <v>1865</v>
@@ -10171,7 +10171,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G338" t="n">
-        <v>10.0617074966431</v>
+        <v>10.0617065429688</v>
       </c>
       <c r="H338" t="n">
         <v>18269</v>
@@ -10200,7 +10200,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G339" t="n">
-        <v>9.98605346679688</v>
+        <v>9.98605442047119</v>
       </c>
       <c r="H339" t="n">
         <v>18500</v>
@@ -10229,7 +10229,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G340" t="n">
-        <v>9.8877067565918</v>
+        <v>9.88770580291748</v>
       </c>
       <c r="H340" t="n">
         <v>14749</v>
@@ -10287,7 +10287,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G342" t="n">
-        <v>10.0163145065308</v>
+        <v>10.0163135528564</v>
       </c>
       <c r="H342" t="n">
         <v>19839</v>
@@ -10316,7 +10316,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G343" t="n">
-        <v>10.1222257614136</v>
+        <v>10.1222267150879</v>
       </c>
       <c r="H343" t="n">
         <v>5896</v>
@@ -10374,7 +10374,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G345" t="n">
-        <v>10.1524887084961</v>
+        <v>10.1524868011475</v>
       </c>
       <c r="H345" t="n">
         <v>7753</v>
@@ -10403,7 +10403,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G346" t="n">
-        <v>10.5534439086914</v>
+        <v>10.5534429550171</v>
       </c>
       <c r="H346" t="n">
         <v>26275</v>
@@ -10461,7 +10461,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G348" t="n">
-        <v>10.8711824417114</v>
+        <v>10.8711814880371</v>
       </c>
       <c r="H348" t="n">
         <v>72067</v>
@@ -10635,7 +10635,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G354" t="n">
-        <v>11.756308555603</v>
+        <v>11.7563095092773</v>
       </c>
       <c r="H354" t="n">
         <v>49610</v>
@@ -10664,7 +10664,7 @@
         <v>16</v>
       </c>
       <c r="G355" t="n">
-        <v>12.1043090820312</v>
+        <v>12.1043081283569</v>
       </c>
       <c r="H355" t="n">
         <v>93167</v>
@@ -10693,7 +10693,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G356" t="n">
-        <v>12.021089553833</v>
+        <v>12.0210905075073</v>
       </c>
       <c r="H356" t="n">
         <v>43184</v>
@@ -10722,7 +10722,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G357" t="n">
-        <v>12.149697303772</v>
+        <v>12.1496992111206</v>
       </c>
       <c r="H357" t="n">
         <v>25539</v>
@@ -10751,7 +10751,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G358" t="n">
-        <v>12.2102203369141</v>
+        <v>12.2102193832397</v>
       </c>
       <c r="H358" t="n">
         <v>29292</v>
@@ -10780,7 +10780,7 @@
         <v>16</v>
       </c>
       <c r="G359" t="n">
-        <v>12.1043090820312</v>
+        <v>12.1043081283569</v>
       </c>
       <c r="H359" t="n">
         <v>41276</v>
@@ -10809,7 +10809,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G360" t="n">
-        <v>11.9561233520508</v>
+        <v>11.9561243057251</v>
       </c>
       <c r="H360" t="n">
         <v>20547</v>
@@ -10838,7 +10838,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G361" t="n">
-        <v>12.12770652771</v>
+        <v>12.127703666687</v>
       </c>
       <c r="H361" t="n">
         <v>25534</v>
@@ -10867,7 +10867,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G362" t="n">
-        <v>12.3148851394653</v>
+        <v>12.314884185791</v>
       </c>
       <c r="H362" t="n">
         <v>24890</v>
@@ -10896,7 +10896,7 @@
         <v>15.75</v>
       </c>
       <c r="G363" t="n">
-        <v>12.2836894989014</v>
+        <v>12.2836875915527</v>
       </c>
       <c r="H363" t="n">
         <v>16676</v>
@@ -10983,7 +10983,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>12.4006757736206</v>
+        <v>12.4006748199463</v>
       </c>
       <c r="H366" t="n">
         <v>23887</v>
@@ -11012,7 +11012,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G367" t="n">
-        <v>12.2758884429932</v>
+        <v>12.2758893966675</v>
       </c>
       <c r="H367" t="n">
         <v>26107</v>
@@ -11041,7 +11041,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G368" t="n">
-        <v>12.1199054718018</v>
+        <v>12.1199064254761</v>
       </c>
       <c r="H368" t="n">
         <v>15465</v>
@@ -11070,7 +11070,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>12.2914867401123</v>
+        <v>12.2914876937866</v>
       </c>
       <c r="H369" t="n">
         <v>12819</v>
@@ -11099,7 +11099,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G370" t="n">
-        <v>11.0436201095581</v>
+        <v>11.0436210632324</v>
       </c>
       <c r="H370" t="n">
         <v>49492</v>
@@ -11128,7 +11128,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G371" t="n">
-        <v>11.3555879592896</v>
+        <v>11.3555860519409</v>
       </c>
       <c r="H371" t="n">
         <v>41815</v>
@@ -11215,7 +11215,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G374" t="n">
-        <v>11.4335784912109</v>
+        <v>11.4335794448853</v>
       </c>
       <c r="H374" t="n">
         <v>18962</v>
@@ -11244,7 +11244,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G375" t="n">
-        <v>11.4647769927979</v>
+        <v>11.4647750854492</v>
       </c>
       <c r="H375" t="n">
         <v>12547</v>
@@ -11273,7 +11273,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G376" t="n">
-        <v>11.3165912628174</v>
+        <v>11.3165922164917</v>
       </c>
       <c r="H376" t="n">
         <v>6058</v>
@@ -11331,7 +11331,7 @@
         <v>14.75</v>
       </c>
       <c r="G378" t="n">
-        <v>11.5037708282471</v>
+        <v>11.5037717819214</v>
       </c>
       <c r="H378" t="n">
         <v>12849</v>
@@ -11360,7 +11360,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G379" t="n">
-        <v>11.4881725311279</v>
+        <v>11.4881734848022</v>
       </c>
       <c r="H379" t="n">
         <v>10371</v>
@@ -11389,7 +11389,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>11.5427684783936</v>
+        <v>11.5427675247192</v>
       </c>
       <c r="H380" t="n">
         <v>7043</v>
@@ -11418,7 +11418,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>11.5817632675171</v>
+        <v>11.5817642211914</v>
       </c>
       <c r="H381" t="n">
         <v>21653</v>
@@ -11505,7 +11505,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G384" t="n">
-        <v>11.2307996749878</v>
+        <v>11.2308015823364</v>
       </c>
       <c r="H384" t="n">
         <v>6211</v>
@@ -11534,7 +11534,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>10.996826171875</v>
+        <v>10.9968252182007</v>
       </c>
       <c r="H385" t="n">
         <v>24207</v>
@@ -11563,7 +11563,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G386" t="n">
-        <v>11.0748167037964</v>
+        <v>11.074818611145</v>
       </c>
       <c r="H386" t="n">
         <v>5290</v>
@@ -11621,7 +11621,7 @@
         <v>14.5</v>
       </c>
       <c r="G388" t="n">
-        <v>11.3087940216064</v>
+        <v>11.3087930679321</v>
       </c>
       <c r="H388" t="n">
         <v>14831</v>
@@ -11708,7 +11708,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G391" t="n">
-        <v>11.4647769927979</v>
+        <v>11.4647750854492</v>
       </c>
       <c r="H391" t="n">
         <v>13606</v>
@@ -11795,7 +11795,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G394" t="n">
-        <v>11.5739641189575</v>
+        <v>11.5739631652832</v>
       </c>
       <c r="H394" t="n">
         <v>13163</v>
@@ -11824,7 +11824,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G395" t="n">
-        <v>11.7221479415894</v>
+        <v>11.722146987915</v>
       </c>
       <c r="H395" t="n">
         <v>4470</v>
@@ -11911,7 +11911,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G398" t="n">
-        <v>11.6831512451172</v>
+        <v>11.6831541061401</v>
       </c>
       <c r="H398" t="n">
         <v>1877</v>
@@ -11940,7 +11940,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G399" t="n">
-        <v>11.5739641189575</v>
+        <v>11.5739631652832</v>
       </c>
       <c r="H399" t="n">
         <v>4249</v>
@@ -11998,7 +11998,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G401" t="n">
-        <v>11.644157409668</v>
+        <v>11.6441555023193</v>
       </c>
       <c r="H401" t="n">
         <v>4259</v>
@@ -12056,7 +12056,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G403" t="n">
-        <v>11.7455453872681</v>
+        <v>11.7455463409424</v>
       </c>
       <c r="H403" t="n">
         <v>11186</v>
@@ -12201,7 +12201,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G408" t="n">
-        <v>12.4084749221802</v>
+        <v>12.4084739685059</v>
       </c>
       <c r="H408" t="n">
         <v>48451</v>
@@ -12259,7 +12259,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>12.3616790771484</v>
+        <v>12.3616819381714</v>
       </c>
       <c r="H410" t="n">
         <v>10337</v>
@@ -12288,7 +12288,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>12.3616790771484</v>
+        <v>12.3616819381714</v>
       </c>
       <c r="H411" t="n">
         <v>12581</v>
@@ -12346,7 +12346,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G413" t="n">
-        <v>12.4162731170654</v>
+        <v>12.4162740707397</v>
       </c>
       <c r="H413" t="n">
         <v>26940</v>
@@ -12404,7 +12404,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G415" t="n">
-        <v>12.2056970596313</v>
+        <v>12.205696105957</v>
       </c>
       <c r="H415" t="n">
         <v>8987</v>
@@ -12433,7 +12433,7 @@
         <v>15.75</v>
       </c>
       <c r="G416" t="n">
-        <v>12.2836894989014</v>
+        <v>12.2836875915527</v>
       </c>
       <c r="H416" t="n">
         <v>4010</v>
@@ -12462,7 +12462,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G417" t="n">
-        <v>12.2056970596313</v>
+        <v>12.205696105957</v>
       </c>
       <c r="H417" t="n">
         <v>5317</v>
@@ -12549,7 +12549,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G420" t="n">
-        <v>12.4474716186523</v>
+        <v>12.447470664978</v>
       </c>
       <c r="H420" t="n">
         <v>15958</v>
@@ -12607,7 +12607,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>13.1181983947754</v>
+        <v>13.1181993484497</v>
       </c>
       <c r="H422" t="n">
         <v>99519</v>
@@ -12665,7 +12665,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>13.4145679473877</v>
+        <v>13.4145669937134</v>
       </c>
       <c r="H424" t="n">
         <v>19101</v>
@@ -12694,7 +12694,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G425" t="n">
-        <v>13.1805934906006</v>
+        <v>13.180591583252</v>
       </c>
       <c r="H425" t="n">
         <v>13472</v>
@@ -12752,7 +12752,7 @@
         <v>17</v>
       </c>
       <c r="G427" t="n">
-        <v>13.258584022522</v>
+        <v>13.2585849761963</v>
       </c>
       <c r="H427" t="n">
         <v>9262</v>
@@ -12839,7 +12839,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G430" t="n">
-        <v>13.5939474105835</v>
+        <v>13.5939483642578</v>
       </c>
       <c r="H430" t="n">
         <v>19167</v>
@@ -12868,7 +12868,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G431" t="n">
-        <v>13.5705509185791</v>
+        <v>13.5705490112305</v>
       </c>
       <c r="H431" t="n">
         <v>10700</v>
@@ -12897,7 +12897,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G432" t="n">
-        <v>13.6407442092896</v>
+        <v>13.6407432556152</v>
       </c>
       <c r="H432" t="n">
         <v>15115</v>
@@ -12926,7 +12926,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G433" t="n">
-        <v>14.1632862091064</v>
+        <v>14.1632881164551</v>
       </c>
       <c r="H433" t="n">
         <v>44798</v>
@@ -12955,7 +12955,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G434" t="n">
-        <v>14.685830116272</v>
+        <v>14.6858339309692</v>
       </c>
       <c r="H434" t="n">
         <v>64849</v>
@@ -12984,7 +12984,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G435" t="n">
-        <v>14.6624336242676</v>
+        <v>14.6624317169189</v>
       </c>
       <c r="H435" t="n">
         <v>43876</v>
@@ -13013,7 +13013,7 @@
         <v>19</v>
       </c>
       <c r="G436" t="n">
-        <v>14.8184175491333</v>
+        <v>14.8184185028076</v>
       </c>
       <c r="H436" t="n">
         <v>28634</v>
@@ -13042,7 +13042,7 @@
         <v>19</v>
       </c>
       <c r="G437" t="n">
-        <v>14.8184175491333</v>
+        <v>14.8184185028076</v>
       </c>
       <c r="H437" t="n">
         <v>126219</v>
@@ -13071,7 +13071,7 @@
         <v>19</v>
       </c>
       <c r="G438" t="n">
-        <v>14.8184175491333</v>
+        <v>14.8184185028076</v>
       </c>
       <c r="H438" t="n">
         <v>27923</v>
@@ -13100,7 +13100,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>15.1693820953369</v>
+        <v>15.1693811416626</v>
       </c>
       <c r="H439" t="n">
         <v>41919</v>
@@ -13129,7 +13129,7 @@
         <v>19.4099998474121</v>
       </c>
       <c r="G440" t="n">
-        <v>15.1381845474243</v>
+        <v>15.1381826400757</v>
       </c>
       <c r="H440" t="n">
         <v>21691</v>
@@ -13158,7 +13158,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G441" t="n">
-        <v>14.8652124404907</v>
+        <v>14.865213394165</v>
       </c>
       <c r="H441" t="n">
         <v>47517</v>
@@ -13187,7 +13187,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G442" t="n">
-        <v>15.192777633667</v>
+        <v>15.1927785873413</v>
       </c>
       <c r="H442" t="n">
         <v>24883</v>
@@ -13216,7 +13216,7 @@
         <v>19.5</v>
       </c>
       <c r="G443" t="n">
-        <v>15.2083768844604</v>
+        <v>15.2083759307861</v>
       </c>
       <c r="H443" t="n">
         <v>16389</v>
@@ -13245,7 +13245,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G444" t="n">
-        <v>14.8730096817017</v>
+        <v>14.8730115890503</v>
       </c>
       <c r="H444" t="n">
         <v>55824</v>
@@ -13274,7 +13274,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G445" t="n">
-        <v>15.3409605026245</v>
+        <v>15.3409614562988</v>
       </c>
       <c r="H445" t="n">
         <v>27974</v>
@@ -13303,7 +13303,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G446" t="n">
-        <v>15.5905351638794</v>
+        <v>15.5905342102051</v>
       </c>
       <c r="H446" t="n">
         <v>57037</v>
@@ -13332,7 +13332,7 @@
         <v>20.6200008392334</v>
       </c>
       <c r="G447" t="n">
-        <v>16.0818843841553</v>
+        <v>16.0818824768066</v>
       </c>
       <c r="H447" t="n">
         <v>34973</v>
@@ -13361,7 +13361,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G448" t="n">
-        <v>16.2534637451172</v>
+        <v>16.2534656524658</v>
       </c>
       <c r="H448" t="n">
         <v>34627</v>
@@ -13390,7 +13390,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G449" t="n">
-        <v>16.6902198791504</v>
+        <v>16.6902141571045</v>
       </c>
       <c r="H449" t="n">
         <v>39523</v>
@@ -13419,7 +13419,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G450" t="n">
-        <v>16.3392562866211</v>
+        <v>16.3392543792725</v>
       </c>
       <c r="H450" t="n">
         <v>22431</v>
@@ -13448,7 +13448,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G451" t="n">
-        <v>17.3297481536865</v>
+        <v>17.3297500610352</v>
       </c>
       <c r="H451" t="n">
         <v>84997</v>
@@ -13535,7 +13535,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G454" t="n">
-        <v>17.3063507080078</v>
+        <v>17.3063526153564</v>
       </c>
       <c r="H454" t="n">
         <v>24323</v>
@@ -13622,7 +13622,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G457" t="n">
-        <v>17.6495151519775</v>
+        <v>17.6495170593262</v>
       </c>
       <c r="H457" t="n">
         <v>26167</v>
@@ -13651,7 +13651,7 @@
         <v>22.3299999237061</v>
       </c>
       <c r="G458" t="n">
-        <v>17.4155387878418</v>
+        <v>17.4155406951904</v>
       </c>
       <c r="H458" t="n">
         <v>134001</v>
@@ -13680,7 +13680,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G459" t="n">
-        <v>17.3297481536865</v>
+        <v>17.3297500610352</v>
       </c>
       <c r="H459" t="n">
         <v>16845</v>
@@ -13709,7 +13709,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G460" t="n">
-        <v>17.4077415466309</v>
+        <v>17.4077396392822</v>
       </c>
       <c r="H460" t="n">
         <v>17684</v>
@@ -13738,7 +13738,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G461" t="n">
-        <v>17.1737670898438</v>
+        <v>17.1737651824951</v>
       </c>
       <c r="H461" t="n">
         <v>25306</v>
@@ -13767,7 +13767,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G462" t="n">
-        <v>16.5498313903809</v>
+        <v>16.5498332977295</v>
       </c>
       <c r="H462" t="n">
         <v>31087</v>
@@ -13941,7 +13941,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G468" t="n">
-        <v>16.1754741668701</v>
+        <v>16.1754722595215</v>
       </c>
       <c r="H468" t="n">
         <v>6648</v>
@@ -13999,7 +13999,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G470" t="n">
-        <v>16.3392562866211</v>
+        <v>16.3392543792725</v>
       </c>
       <c r="H470" t="n">
         <v>3651</v>
@@ -14028,7 +14028,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G471" t="n">
-        <v>16.1676731109619</v>
+        <v>16.1676712036133</v>
       </c>
       <c r="H471" t="n">
         <v>3125</v>
@@ -14057,7 +14057,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G472" t="n">
-        <v>16.0896797180176</v>
+        <v>16.0896816253662</v>
       </c>
       <c r="H472" t="n">
         <v>10550</v>
@@ -14144,7 +14144,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G475" t="n">
-        <v>16.2144680023193</v>
+        <v>16.214469909668</v>
       </c>
       <c r="H475" t="n">
         <v>24283</v>
@@ -14202,7 +14202,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>16.2612628936768</v>
+        <v>16.2612648010254</v>
       </c>
       <c r="H477" t="n">
         <v>30808</v>
@@ -14231,7 +14231,7 @@
         <v>20.75</v>
       </c>
       <c r="G478" t="n">
-        <v>16.1832733154297</v>
+        <v>16.1832695007324</v>
       </c>
       <c r="H478" t="n">
         <v>18766</v>
@@ -14260,7 +14260,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G479" t="n">
-        <v>16.2222709655762</v>
+        <v>16.2222671508789</v>
       </c>
       <c r="H479" t="n">
         <v>34494</v>
@@ -14289,7 +14289,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G480" t="n">
-        <v>16.425048828125</v>
+        <v>16.4250450134277</v>
       </c>
       <c r="H480" t="n">
         <v>23775</v>
@@ -14405,7 +14405,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G484" t="n">
-        <v>16.9319915771484</v>
+        <v>16.9319896697998</v>
       </c>
       <c r="H484" t="n">
         <v>33462</v>
@@ -14434,7 +14434,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G485" t="n">
-        <v>17.4701347351074</v>
+        <v>17.4701366424561</v>
       </c>
       <c r="H485" t="n">
         <v>40419</v>
@@ -14463,7 +14463,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G486" t="n">
-        <v>18.0784683227539</v>
+        <v>18.0784702301025</v>
       </c>
       <c r="H486" t="n">
         <v>52957</v>
@@ -14492,7 +14492,7 @@
         <v>23.4300003051758</v>
       </c>
       <c r="G487" t="n">
-        <v>18.2734508514404</v>
+        <v>18.2734470367432</v>
       </c>
       <c r="H487" t="n">
         <v>27763</v>
@@ -14550,7 +14550,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G489" t="n">
-        <v>17.8600959777832</v>
+        <v>17.8600940704346</v>
       </c>
       <c r="H489" t="n">
         <v>23095</v>
@@ -14608,7 +14608,7 @@
         <v>23</v>
       </c>
       <c r="G491" t="n">
-        <v>17.9380855560303</v>
+        <v>17.9380836486816</v>
       </c>
       <c r="H491" t="n">
         <v>19075</v>
@@ -14637,7 +14637,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>17.8210983276367</v>
+        <v>17.8210964202881</v>
       </c>
       <c r="H492" t="n">
         <v>10241</v>
@@ -14724,7 +14724,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G495" t="n">
-        <v>17.8444938659668</v>
+        <v>17.8444957733154</v>
       </c>
       <c r="H495" t="n">
         <v>10001</v>
@@ -14782,7 +14782,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G497" t="n">
-        <v>17.4545364379883</v>
+        <v>17.4545345306396</v>
       </c>
       <c r="H497" t="n">
         <v>8776</v>
@@ -14811,7 +14811,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G498" t="n">
-        <v>17.4077415466309</v>
+        <v>17.4077396392822</v>
       </c>
       <c r="H498" t="n">
         <v>6551</v>
@@ -14840,7 +14840,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G499" t="n">
-        <v>17.6963119506836</v>
+        <v>17.6963081359863</v>
       </c>
       <c r="H499" t="n">
         <v>15628</v>
@@ -14869,7 +14869,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G500" t="n">
-        <v>17.4077415466309</v>
+        <v>17.4077396392822</v>
       </c>
       <c r="H500" t="n">
         <v>28166</v>
@@ -14898,7 +14898,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G501" t="n">
-        <v>16.8150043487549</v>
+        <v>16.8150024414062</v>
       </c>
       <c r="H501" t="n">
         <v>25375</v>
@@ -14927,7 +14927,7 @@
         <v>20.6200008392334</v>
       </c>
       <c r="G502" t="n">
-        <v>16.0818843841553</v>
+        <v>16.0818824768066</v>
       </c>
       <c r="H502" t="n">
         <v>21726</v>
@@ -14985,7 +14985,7 @@
         <v>20.25</v>
       </c>
       <c r="G504" t="n">
-        <v>15.7933130264282</v>
+        <v>15.7933149337769</v>
       </c>
       <c r="H504" t="n">
         <v>15898</v>
@@ -15014,7 +15014,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G505" t="n">
-        <v>15.7153215408325</v>
+        <v>15.7153224945068</v>
       </c>
       <c r="H505" t="n">
         <v>32151</v>
@@ -15101,7 +15101,7 @@
         <v>20.0100002288818</v>
       </c>
       <c r="G508" t="n">
-        <v>15.6061344146729</v>
+        <v>15.6061353683472</v>
       </c>
       <c r="H508" t="n">
         <v>9612</v>
@@ -15130,7 +15130,7 @@
         <v>20.0100002288818</v>
       </c>
       <c r="G509" t="n">
-        <v>15.6061344146729</v>
+        <v>15.6061353683472</v>
       </c>
       <c r="H509" t="n">
         <v>30680</v>
@@ -15246,7 +15246,7 @@
         <v>20.25</v>
       </c>
       <c r="G513" t="n">
-        <v>15.7933130264282</v>
+        <v>15.7933149337769</v>
       </c>
       <c r="H513" t="n">
         <v>7582</v>
@@ -15275,7 +15275,7 @@
         <v>20</v>
       </c>
       <c r="G514" t="n">
-        <v>15.5983362197876</v>
+        <v>15.598334312439</v>
       </c>
       <c r="H514" t="n">
         <v>11599</v>
@@ -15304,7 +15304,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>15.7153215408325</v>
+        <v>15.7153224945068</v>
       </c>
       <c r="H515" t="n">
         <v>11510</v>
@@ -15333,7 +15333,7 @@
         <v>20.5</v>
       </c>
       <c r="G516" t="n">
-        <v>15.9882936477661</v>
+        <v>15.9882926940918</v>
       </c>
       <c r="H516" t="n">
         <v>12544</v>
@@ -15391,7 +15391,7 @@
         <v>20.75</v>
       </c>
       <c r="G518" t="n">
-        <v>16.1832733154297</v>
+        <v>16.1832695007324</v>
       </c>
       <c r="H518" t="n">
         <v>10114</v>
@@ -15478,7 +15478,7 @@
         <v>20.25</v>
       </c>
       <c r="G521" t="n">
-        <v>15.7933130264282</v>
+        <v>15.7933149337769</v>
       </c>
       <c r="H521" t="n">
         <v>9777</v>
@@ -15507,7 +15507,7 @@
         <v>20.25</v>
       </c>
       <c r="G522" t="n">
-        <v>15.7933130264282</v>
+        <v>15.7933149337769</v>
       </c>
       <c r="H522" t="n">
         <v>3622</v>
@@ -15565,7 +15565,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>15.7153215408325</v>
+        <v>15.7153224945068</v>
       </c>
       <c r="H524" t="n">
         <v>7860</v>
@@ -15594,7 +15594,7 @@
         <v>20.25</v>
       </c>
       <c r="G525" t="n">
-        <v>15.7933130264282</v>
+        <v>15.7933149337769</v>
       </c>
       <c r="H525" t="n">
         <v>4843</v>
@@ -15623,7 +15623,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G526" t="n">
-        <v>15.7153215408325</v>
+        <v>15.7153224945068</v>
       </c>
       <c r="H526" t="n">
         <v>6843</v>
@@ -15652,7 +15652,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>15.6373291015625</v>
+        <v>15.6373281478882</v>
       </c>
       <c r="H527" t="n">
         <v>40453</v>
@@ -15681,7 +15681,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G528" t="n">
-        <v>15.4267530441284</v>
+        <v>15.4267520904541</v>
       </c>
       <c r="H528" t="n">
         <v>11720</v>
@@ -15710,7 +15710,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>15.2863674163818</v>
+        <v>15.2863693237305</v>
       </c>
       <c r="H529" t="n">
         <v>17799</v>
@@ -15768,7 +15768,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>15.5203437805176</v>
+        <v>15.5203418731689</v>
       </c>
       <c r="H531" t="n">
         <v>12748</v>
@@ -15797,7 +15797,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>15.6763277053833</v>
+        <v>15.6763248443604</v>
       </c>
       <c r="H532" t="n">
         <v>16172</v>
@@ -15826,7 +15826,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>15.3643617630005</v>
+        <v>15.3643579483032</v>
       </c>
       <c r="H533" t="n">
         <v>6897</v>
@@ -15855,7 +15855,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G534" t="n">
-        <v>15.2551708221436</v>
+        <v>15.2551698684692</v>
       </c>
       <c r="H534" t="n">
         <v>9444</v>
@@ -15884,7 +15884,7 @@
         <v>19</v>
       </c>
       <c r="G535" t="n">
-        <v>14.8184175491333</v>
+        <v>14.8184185028076</v>
       </c>
       <c r="H535" t="n">
         <v>12086</v>
@@ -15913,7 +15913,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G536" t="n">
-        <v>14.5532484054565</v>
+        <v>14.5532445907593</v>
       </c>
       <c r="H536" t="n">
         <v>13995</v>
@@ -15942,7 +15942,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>14.3504676818848</v>
+        <v>14.3504657745361</v>
       </c>
       <c r="H537" t="n">
         <v>10942</v>
@@ -15971,7 +15971,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G538" t="n">
-        <v>14.4752550125122</v>
+        <v>14.4752531051636</v>
       </c>
       <c r="H538" t="n">
         <v>8493</v>
@@ -16000,7 +16000,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G539" t="n">
-        <v>14.2568769454956</v>
+        <v>14.2568778991699</v>
       </c>
       <c r="H539" t="n">
         <v>5266</v>
@@ -16116,7 +16116,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G543" t="n">
-        <v>14.2724742889404</v>
+        <v>14.2724752426147</v>
       </c>
       <c r="H543" t="n">
         <v>40089</v>
@@ -16145,7 +16145,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G544" t="n">
-        <v>14.5532484054565</v>
+        <v>14.5532445907593</v>
       </c>
       <c r="H544" t="n">
         <v>14801</v>
@@ -16203,7 +16203,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G546" t="n">
-        <v>14.7560243606567</v>
+        <v>14.7560224533081</v>
       </c>
       <c r="H546" t="n">
         <v>10816</v>
@@ -16261,7 +16261,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G548" t="n">
-        <v>14.3192720413208</v>
+        <v>14.3192701339722</v>
       </c>
       <c r="H548" t="n">
         <v>8314</v>
@@ -16290,7 +16290,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G549" t="n">
-        <v>13.9917058944702</v>
+        <v>13.9917068481445</v>
       </c>
       <c r="H549" t="n">
         <v>5634</v>
@@ -16319,7 +16319,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>13.8045272827148</v>
+        <v>13.8045253753662</v>
       </c>
       <c r="H550" t="n">
         <v>15745</v>
@@ -16377,7 +16377,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G552" t="n">
-        <v>13.5237560272217</v>
+        <v>13.5237579345703</v>
       </c>
       <c r="H552" t="n">
         <v>6004</v>
@@ -16406,7 +16406,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G553" t="n">
-        <v>13.4769639968872</v>
+        <v>13.4769620895386</v>
       </c>
       <c r="H553" t="n">
         <v>13153</v>
@@ -16435,7 +16435,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G554" t="n">
-        <v>13.336576461792</v>
+        <v>13.3365755081177</v>
       </c>
       <c r="H554" t="n">
         <v>12751</v>
@@ -16464,7 +16464,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G555" t="n">
-        <v>13.4301633834839</v>
+        <v>13.4301671981812</v>
       </c>
       <c r="H555" t="n">
         <v>9962</v>
@@ -16493,7 +16493,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G556" t="n">
-        <v>13.4769639968872</v>
+        <v>13.4769620895386</v>
       </c>
       <c r="H556" t="n">
         <v>5716</v>
@@ -16522,7 +16522,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>13.7265357971191</v>
+        <v>13.7265367507935</v>
       </c>
       <c r="H557" t="n">
         <v>6831</v>
@@ -16551,7 +16551,7 @@
         <v>18</v>
       </c>
       <c r="G558" t="n">
-        <v>14.0385026931763</v>
+        <v>14.0385007858276</v>
       </c>
       <c r="H558" t="n">
         <v>9649</v>
@@ -16609,7 +16609,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>14.116494178772</v>
+        <v>14.1164932250977</v>
       </c>
       <c r="H560" t="n">
         <v>13009</v>
@@ -16638,7 +16638,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G561" t="n">
-        <v>14.2568769454956</v>
+        <v>14.2568778991699</v>
       </c>
       <c r="H561" t="n">
         <v>18600</v>
@@ -16667,7 +16667,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G562" t="n">
-        <v>14.5844430923462</v>
+        <v>14.5844449996948</v>
       </c>
       <c r="H562" t="n">
         <v>12944</v>
@@ -16696,7 +16696,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>14.1944856643677</v>
+        <v>14.1944847106934</v>
       </c>
       <c r="H563" t="n">
         <v>6993</v>
@@ -16754,7 +16754,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G565" t="n">
-        <v>14.3348693847656</v>
+        <v>14.3348684310913</v>
       </c>
       <c r="H565" t="n">
         <v>6954</v>
@@ -16783,7 +16783,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G566" t="n">
-        <v>14.1788854598999</v>
+        <v>14.1788864135742</v>
       </c>
       <c r="H566" t="n">
         <v>9403</v>
@@ -16812,7 +16812,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G567" t="n">
-        <v>14.3504676818848</v>
+        <v>14.3504657745361</v>
       </c>
       <c r="H567" t="n">
         <v>10466</v>
@@ -16841,7 +16841,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G568" t="n">
-        <v>14.5844430923462</v>
+        <v>14.5844449996948</v>
       </c>
       <c r="H568" t="n">
         <v>12940</v>
@@ -16870,7 +16870,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>14.2724742889404</v>
+        <v>14.2724752426147</v>
       </c>
       <c r="H569" t="n">
         <v>12295</v>
@@ -16899,7 +16899,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G570" t="n">
-        <v>14.3192720413208</v>
+        <v>14.3192701339722</v>
       </c>
       <c r="H570" t="n">
         <v>13562</v>
@@ -16928,7 +16928,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G571" t="n">
-        <v>14.2568769454956</v>
+        <v>14.2568778991699</v>
       </c>
       <c r="H571" t="n">
         <v>18275</v>
@@ -16957,7 +16957,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>14.2724742889404</v>
+        <v>14.2724752426147</v>
       </c>
       <c r="H572" t="n">
         <v>17049</v>
@@ -16986,7 +16986,7 @@
         <v>18</v>
       </c>
       <c r="G573" t="n">
-        <v>14.0385026931763</v>
+        <v>14.0385007858276</v>
       </c>
       <c r="H573" t="n">
         <v>17675</v>
@@ -17015,7 +17015,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G574" t="n">
-        <v>13.6797389984131</v>
+        <v>13.6797409057617</v>
       </c>
       <c r="H574" t="n">
         <v>18409</v>
@@ -17044,7 +17044,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G575" t="n">
-        <v>14.3816652297974</v>
+        <v>14.381664276123</v>
       </c>
       <c r="H575" t="n">
         <v>8015</v>
@@ -17102,7 +17102,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G577" t="n">
-        <v>14.303674697876</v>
+        <v>14.3036727905273</v>
       </c>
       <c r="H577" t="n">
         <v>14113</v>
@@ -17131,7 +17131,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G578" t="n">
-        <v>14.2880735397339</v>
+        <v>14.2880754470825</v>
       </c>
       <c r="H578" t="n">
         <v>5629</v>
@@ -17160,7 +17160,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G579" t="n">
-        <v>14.3972635269165</v>
+        <v>14.3972625732422</v>
       </c>
       <c r="H579" t="n">
         <v>4755</v>
@@ -17189,7 +17189,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G580" t="n">
-        <v>14.3972635269165</v>
+        <v>14.3972625732422</v>
       </c>
       <c r="H580" t="n">
         <v>3867</v>
@@ -17218,7 +17218,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G581" t="n">
-        <v>14.3192720413208</v>
+        <v>14.3192701339722</v>
       </c>
       <c r="H581" t="n">
         <v>1909</v>
@@ -17247,7 +17247,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>14.3504676818848</v>
+        <v>14.3504657745361</v>
       </c>
       <c r="H582" t="n">
         <v>5064</v>
@@ -17305,7 +17305,7 @@
         <v>20</v>
       </c>
       <c r="G584" t="n">
-        <v>15.5983362197876</v>
+        <v>15.598334312439</v>
       </c>
       <c r="H584" t="n">
         <v>61328</v>
@@ -17363,7 +17363,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G586" t="n">
-        <v>15.2863674163818</v>
+        <v>15.2863693237305</v>
       </c>
       <c r="H586" t="n">
         <v>36274</v>
@@ -17392,7 +17392,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G587" t="n">
-        <v>15.4267530441284</v>
+        <v>15.4267520904541</v>
       </c>
       <c r="H587" t="n">
         <v>17493</v>
@@ -17450,7 +17450,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>15.3643617630005</v>
+        <v>15.3643579483032</v>
       </c>
       <c r="H589" t="n">
         <v>40159</v>
@@ -17479,7 +17479,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G590" t="n">
-        <v>15.192777633667</v>
+        <v>15.1927785873413</v>
       </c>
       <c r="H590" t="n">
         <v>14001</v>
@@ -17508,7 +17508,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G591" t="n">
-        <v>15.2863674163818</v>
+        <v>15.2863693237305</v>
       </c>
       <c r="H591" t="n">
         <v>8875</v>
@@ -17537,7 +17537,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G592" t="n">
-        <v>15.0835914611816</v>
+        <v>15.0835876464844</v>
       </c>
       <c r="H592" t="n">
         <v>3066</v>
@@ -17595,7 +17595,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G594" t="n">
-        <v>14.974401473999</v>
+        <v>14.9744005203247</v>
       </c>
       <c r="H594" t="n">
         <v>4689</v>
@@ -17624,7 +17624,7 @@
         <v>19</v>
       </c>
       <c r="G595" t="n">
-        <v>14.8184175491333</v>
+        <v>14.8184185028076</v>
       </c>
       <c r="H595" t="n">
         <v>42232</v>
@@ -17653,7 +17653,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>14.974401473999</v>
+        <v>14.9744005203247</v>
       </c>
       <c r="H596" t="n">
         <v>14486</v>
@@ -17682,7 +17682,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G597" t="n">
-        <v>15.5203437805176</v>
+        <v>15.5203418731689</v>
       </c>
       <c r="H597" t="n">
         <v>44610</v>
@@ -17711,7 +17711,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>15.3643617630005</v>
+        <v>15.3643579483032</v>
       </c>
       <c r="H598" t="n">
         <v>8315</v>
@@ -17740,7 +17740,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G599" t="n">
-        <v>15.2863674163818</v>
+        <v>15.2863693237305</v>
       </c>
       <c r="H599" t="n">
         <v>12564</v>
@@ -17769,7 +17769,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G600" t="n">
-        <v>15.270770072937</v>
+        <v>15.2707681655884</v>
       </c>
       <c r="H600" t="n">
         <v>2265</v>
@@ -17827,7 +17827,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G602" t="n">
-        <v>15.0679893493652</v>
+        <v>15.0679912567139</v>
       </c>
       <c r="H602" t="n">
         <v>3476</v>
@@ -17856,7 +17856,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G603" t="n">
-        <v>15.0523929595947</v>
+        <v>15.0523910522461</v>
       </c>
       <c r="H603" t="n">
         <v>4102</v>
@@ -17885,7 +17885,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G604" t="n">
-        <v>15.192777633667</v>
+        <v>15.1927785873413</v>
       </c>
       <c r="H604" t="n">
         <v>15104</v>
@@ -17914,7 +17914,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>14.974401473999</v>
+        <v>14.9744005203247</v>
       </c>
       <c r="H605" t="n">
         <v>8613</v>
@@ -17943,7 +17943,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G606" t="n">
-        <v>15.0211944580078</v>
+        <v>15.0211982727051</v>
       </c>
       <c r="H606" t="n">
         <v>3005</v>
@@ -17972,7 +17972,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G607" t="n">
-        <v>14.9588022232056</v>
+        <v>14.9588041305542</v>
       </c>
       <c r="H607" t="n">
         <v>21216</v>
@@ -18001,7 +18001,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G608" t="n">
-        <v>15.0835914611816</v>
+        <v>15.0835876464844</v>
       </c>
       <c r="H608" t="n">
         <v>1848</v>
@@ -18030,7 +18030,7 @@
         <v>19.5</v>
       </c>
       <c r="G609" t="n">
-        <v>15.2083768844604</v>
+        <v>15.2083759307861</v>
       </c>
       <c r="H609" t="n">
         <v>10728</v>
@@ -18059,7 +18059,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>15.0523929595947</v>
+        <v>15.0523910522461</v>
       </c>
       <c r="H610" t="n">
         <v>8178</v>
@@ -18088,7 +18088,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>15.0523929595947</v>
+        <v>15.0523910522461</v>
       </c>
       <c r="H611" t="n">
         <v>9456</v>
@@ -18175,7 +18175,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>14.3744325637817</v>
+        <v>14.3744316101074</v>
       </c>
       <c r="H614" t="n">
         <v>21750</v>
@@ -18204,7 +18204,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G615" t="n">
-        <v>14.4065561294556</v>
+        <v>14.4065551757812</v>
       </c>
       <c r="H615" t="n">
         <v>7455</v>
@@ -18233,7 +18233,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G616" t="n">
-        <v>14.4386768341064</v>
+        <v>14.4386758804321</v>
       </c>
       <c r="H616" t="n">
         <v>3365</v>
@@ -18291,7 +18291,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G618" t="n">
-        <v>14.5992841720581</v>
+        <v>14.5992860794067</v>
       </c>
       <c r="H618" t="n">
         <v>3594</v>
@@ -18320,7 +18320,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G619" t="n">
-        <v>14.8883781433105</v>
+        <v>14.8883790969849</v>
       </c>
       <c r="H619" t="n">
         <v>2520</v>
@@ -18349,7 +18349,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G620" t="n">
-        <v>15.0650510787964</v>
+        <v>15.0650482177734</v>
       </c>
       <c r="H620" t="n">
         <v>7515</v>
@@ -18378,7 +18378,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G621" t="n">
-        <v>15.2095966339111</v>
+        <v>15.2095975875854</v>
       </c>
       <c r="H621" t="n">
         <v>11643</v>
@@ -18407,7 +18407,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G622" t="n">
-        <v>15.0650510787964</v>
+        <v>15.0650482177734</v>
       </c>
       <c r="H622" t="n">
         <v>4433</v>
@@ -18436,7 +18436,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G623" t="n">
-        <v>14.9365634918213</v>
+        <v>14.936562538147</v>
       </c>
       <c r="H623" t="n">
         <v>1039</v>
@@ -18465,7 +18465,7 @@
         <v>18.5</v>
       </c>
       <c r="G624" t="n">
-        <v>14.8562593460083</v>
+        <v>14.8562574386597</v>
       </c>
       <c r="H624" t="n">
         <v>2578</v>
@@ -18494,7 +18494,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G625" t="n">
-        <v>14.8401966094971</v>
+        <v>14.8401956558228</v>
       </c>
       <c r="H625" t="n">
         <v>187</v>
@@ -18523,7 +18523,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>14.7759532928467</v>
+        <v>14.7759523391724</v>
       </c>
       <c r="H626" t="n">
         <v>2895</v>
@@ -18552,7 +18552,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>14.7759532928467</v>
+        <v>14.7759523391724</v>
       </c>
       <c r="H627" t="n">
         <v>2916</v>
@@ -18581,7 +18581,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G628" t="n">
-        <v>14.5511035919189</v>
+        <v>14.5511016845703</v>
       </c>
       <c r="H628" t="n">
         <v>1279</v>
@@ -18813,7 +18813,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G636" t="n">
-        <v>13.7641220092773</v>
+        <v>13.764121055603</v>
       </c>
       <c r="H636" t="n">
         <v>14347</v>
@@ -18842,7 +18842,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G637" t="n">
-        <v>13.7641220092773</v>
+        <v>13.764121055603</v>
       </c>
       <c r="H637" t="n">
         <v>6290</v>
@@ -18871,7 +18871,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G638" t="n">
-        <v>13.7641220092773</v>
+        <v>13.764121055603</v>
       </c>
       <c r="H638" t="n">
         <v>14957</v>
@@ -18900,7 +18900,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G639" t="n">
-        <v>13.7641220092773</v>
+        <v>13.764121055603</v>
       </c>
       <c r="H639" t="n">
         <v>8187</v>
@@ -18958,7 +18958,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G641" t="n">
-        <v>13.6677570343018</v>
+        <v>13.6677579879761</v>
       </c>
       <c r="H641" t="n">
         <v>3603</v>
@@ -18987,7 +18987,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G642" t="n">
-        <v>13.8604879379272</v>
+        <v>13.8604860305786</v>
       </c>
       <c r="H642" t="n">
         <v>1857</v>
@@ -19132,7 +19132,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G647" t="n">
-        <v>12.9289588928223</v>
+        <v>12.9289598464966</v>
       </c>
       <c r="H647" t="n">
         <v>4259</v>
@@ -19190,7 +19190,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>12.9289588928223</v>
+        <v>12.9289598464966</v>
       </c>
       <c r="H649" t="n">
         <v>19044</v>
@@ -19219,7 +19219,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G650" t="n">
-        <v>12.9771413803101</v>
+        <v>12.9771423339844</v>
       </c>
       <c r="H650" t="n">
         <v>1672</v>
@@ -19335,7 +19335,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G654" t="n">
-        <v>13.6035127639771</v>
+        <v>13.6035146713257</v>
       </c>
       <c r="H654" t="n">
         <v>8712</v>
@@ -19364,7 +19364,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G655" t="n">
-        <v>13.0253238677979</v>
+        <v>13.0253248214722</v>
       </c>
       <c r="H655" t="n">
         <v>2763</v>
@@ -19393,7 +19393,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G656" t="n">
-        <v>13.1216888427734</v>
+        <v>13.1216897964478</v>
       </c>
       <c r="H656" t="n">
         <v>338</v>
@@ -19422,7 +19422,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G657" t="n">
-        <v>12.8647174835205</v>
+        <v>12.8647165298462</v>
       </c>
       <c r="H657" t="n">
         <v>4595</v>
@@ -19451,7 +19451,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G658" t="n">
-        <v>12.9610815048218</v>
+        <v>12.9610795974731</v>
       </c>
       <c r="H658" t="n">
         <v>2168</v>
@@ -19480,7 +19480,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G659" t="n">
-        <v>13.0092649459839</v>
+        <v>13.0092639923096</v>
       </c>
       <c r="H659" t="n">
         <v>17996</v>
@@ -19538,7 +19538,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G661" t="n">
-        <v>12.7683525085449</v>
+        <v>12.7683506011963</v>
       </c>
       <c r="H661" t="n">
         <v>26698</v>
@@ -19596,7 +19596,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G663" t="n">
-        <v>12.6398639678955</v>
+        <v>12.6398649215698</v>
       </c>
       <c r="H663" t="n">
         <v>3035</v>
@@ -19625,7 +19625,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G664" t="n">
-        <v>12.671986579895</v>
+        <v>12.6719856262207</v>
       </c>
       <c r="H664" t="n">
         <v>1652</v>
@@ -19770,7 +19770,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G669" t="n">
-        <v>12.3186483383179</v>
+        <v>12.3186473846436</v>
       </c>
       <c r="H669" t="n">
         <v>27706</v>
@@ -19799,7 +19799,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G670" t="n">
-        <v>12.1580410003662</v>
+        <v>12.1580390930176</v>
       </c>
       <c r="H670" t="n">
         <v>8620</v>
@@ -19828,7 +19828,7 @@
         <v>15</v>
       </c>
       <c r="G671" t="n">
-        <v>12.045615196228</v>
+        <v>12.0456142425537</v>
       </c>
       <c r="H671" t="n">
         <v>6048</v>
@@ -19857,7 +19857,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G672" t="n">
-        <v>12.1580410003662</v>
+        <v>12.1580390930176</v>
       </c>
       <c r="H672" t="n">
         <v>2870</v>
@@ -19915,7 +19915,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G674" t="n">
-        <v>12.3025875091553</v>
+        <v>12.302586555481</v>
       </c>
       <c r="H674" t="n">
         <v>2424</v>
@@ -19973,7 +19973,7 @@
         <v>14.5</v>
       </c>
       <c r="G676" t="n">
-        <v>11.6440944671631</v>
+        <v>11.6440935134888</v>
       </c>
       <c r="H676" t="n">
         <v>6758</v>
@@ -20002,7 +20002,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G677" t="n">
-        <v>11.579852104187</v>
+        <v>11.5798511505127</v>
       </c>
       <c r="H677" t="n">
         <v>5149</v>
@@ -20031,7 +20031,7 @@
         <v>14.5</v>
       </c>
       <c r="G678" t="n">
-        <v>11.6440944671631</v>
+        <v>11.6440935134888</v>
       </c>
       <c r="H678" t="n">
         <v>5077</v>
@@ -20060,7 +20060,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G679" t="n">
-        <v>11.5637893676758</v>
+        <v>11.5637903213501</v>
       </c>
       <c r="H679" t="n">
         <v>3666</v>
@@ -20089,7 +20089,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>11.4834871292114</v>
+        <v>11.4834861755371</v>
       </c>
       <c r="H680" t="n">
         <v>3128</v>
@@ -20205,7 +20205,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G684" t="n">
-        <v>10.7607498168945</v>
+        <v>10.7607488632202</v>
       </c>
       <c r="H684" t="n">
         <v>17337</v>
@@ -20234,7 +20234,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G685" t="n">
-        <v>11.9171285629272</v>
+        <v>11.9171276092529</v>
       </c>
       <c r="H685" t="n">
         <v>27488</v>
@@ -20379,7 +20379,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>12.9289588928223</v>
+        <v>12.9289598464966</v>
       </c>
       <c r="H690" t="n">
         <v>26274</v>
@@ -20408,7 +20408,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G691" t="n">
-        <v>12.8647174835205</v>
+        <v>12.8647165298462</v>
       </c>
       <c r="H691" t="n">
         <v>7175</v>
@@ -20437,7 +20437,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G692" t="n">
-        <v>12.7362279891968</v>
+        <v>12.7362289428711</v>
       </c>
       <c r="H692" t="n">
         <v>3530</v>
@@ -20495,7 +20495,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G694" t="n">
-        <v>12.2383432388306</v>
+        <v>12.2383441925049</v>
       </c>
       <c r="H694" t="n">
         <v>7253</v>
@@ -20553,7 +20553,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G696" t="n">
-        <v>12.671986579895</v>
+        <v>12.6719856262207</v>
       </c>
       <c r="H696" t="n">
         <v>5744</v>
@@ -20582,7 +20582,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G697" t="n">
-        <v>12.8004732131958</v>
+        <v>12.8004722595215</v>
       </c>
       <c r="H697" t="n">
         <v>7167</v>
@@ -20669,7 +20669,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G700" t="n">
-        <v>12.6398639678955</v>
+        <v>12.6398649215698</v>
       </c>
       <c r="H700" t="n">
         <v>3473</v>
@@ -20785,7 +20785,7 @@
         <v>15</v>
       </c>
       <c r="G704" t="n">
-        <v>12.045615196228</v>
+        <v>12.0456142425537</v>
       </c>
       <c r="H704" t="n">
         <v>5751</v>
@@ -20814,7 +20814,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G705" t="n">
-        <v>12.1098575592041</v>
+        <v>12.1098566055298</v>
       </c>
       <c r="H705" t="n">
         <v>2559</v>
@@ -20843,7 +20843,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G706" t="n">
-        <v>12.1580410003662</v>
+        <v>12.1580390930176</v>
       </c>
       <c r="H706" t="n">
         <v>1230</v>
@@ -20872,7 +20872,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G707" t="n">
-        <v>12.3347082138062</v>
+        <v>12.3347091674805</v>
       </c>
       <c r="H707" t="n">
         <v>2522</v>
@@ -20901,7 +20901,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G708" t="n">
-        <v>12.1580410003662</v>
+        <v>12.1580390930176</v>
       </c>
       <c r="H708" t="n">
         <v>12456</v>
@@ -20930,7 +20930,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G709" t="n">
-        <v>12.3347082138062</v>
+        <v>12.3347091674805</v>
       </c>
       <c r="H709" t="n">
         <v>1057</v>
@@ -20959,7 +20959,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G710" t="n">
-        <v>11.5637893676758</v>
+        <v>11.5637903213501</v>
       </c>
       <c r="H710" t="n">
         <v>22279</v>
@@ -20988,7 +20988,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>11.5637893676758</v>
+        <v>11.5637903213501</v>
       </c>
       <c r="H711" t="n">
         <v>3305</v>
@@ -21017,7 +21017,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G712" t="n">
-        <v>11.3228778839111</v>
+        <v>11.3228759765625</v>
       </c>
       <c r="H712" t="n">
         <v>2460</v>
@@ -21046,7 +21046,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G713" t="n">
-        <v>11.1462078094482</v>
+        <v>11.1462097167969</v>
       </c>
       <c r="H713" t="n">
         <v>2810</v>
@@ -21075,7 +21075,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G714" t="n">
-        <v>11.13014793396</v>
+        <v>11.1301469802856</v>
       </c>
       <c r="H714" t="n">
         <v>4622</v>
@@ -21162,7 +21162,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G717" t="n">
-        <v>11.5637893676758</v>
+        <v>11.5637903213501</v>
       </c>
       <c r="H717" t="n">
         <v>6081</v>
@@ -21191,7 +21191,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G718" t="n">
-        <v>11.4031810760498</v>
+        <v>11.4031820297241</v>
       </c>
       <c r="H718" t="n">
         <v>4234</v>
@@ -21220,7 +21220,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G719" t="n">
-        <v>11.1783304214478</v>
+        <v>11.1783294677734</v>
       </c>
       <c r="H719" t="n">
         <v>4791</v>
@@ -21278,7 +21278,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G721" t="n">
-        <v>10.6162023544312</v>
+        <v>10.6162014007568</v>
       </c>
       <c r="H721" t="n">
         <v>14988</v>
@@ -21307,7 +21307,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G722" t="n">
-        <v>10.584080696106</v>
+        <v>10.5840797424316</v>
       </c>
       <c r="H722" t="n">
         <v>11354</v>
@@ -21336,7 +21336,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G723" t="n">
-        <v>10.6162023544312</v>
+        <v>10.6162014007568</v>
       </c>
       <c r="H723" t="n">
         <v>3206</v>
@@ -21365,7 +21365,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G724" t="n">
-        <v>10.5037746429443</v>
+        <v>10.503776550293</v>
       </c>
       <c r="H724" t="n">
         <v>4390</v>
@@ -21394,7 +21394,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G725" t="n">
-        <v>10.3110466003418</v>
+        <v>10.3110456466675</v>
       </c>
       <c r="H725" t="n">
         <v>5618</v>
@@ -21452,7 +21452,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G727" t="n">
-        <v>10.584080696106</v>
+        <v>10.5840797424316</v>
       </c>
       <c r="H727" t="n">
         <v>5354</v>
@@ -21481,7 +21481,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G728" t="n">
-        <v>10.5198373794556</v>
+        <v>10.5198383331299</v>
       </c>
       <c r="H728" t="n">
         <v>5181</v>
@@ -21510,7 +21510,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G729" t="n">
-        <v>10.6162023544312</v>
+        <v>10.6162014007568</v>
       </c>
       <c r="H729" t="n">
         <v>15986</v>
@@ -21539,7 +21539,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G730" t="n">
-        <v>11.2265119552612</v>
+        <v>11.2265110015869</v>
       </c>
       <c r="H730" t="n">
         <v>12830</v>
@@ -21626,7 +21626,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>11.3228778839111</v>
+        <v>11.3228759765625</v>
       </c>
       <c r="H733" t="n">
         <v>8610</v>
@@ -21655,7 +21655,7 @@
         <v>13.6800003051758</v>
       </c>
       <c r="G734" t="n">
-        <v>10.9855995178223</v>
+        <v>10.9856014251709</v>
       </c>
       <c r="H734" t="n">
         <v>5400</v>
@@ -21684,7 +21684,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G735" t="n">
-        <v>11.1783304214478</v>
+        <v>11.1783294677734</v>
       </c>
       <c r="H735" t="n">
         <v>6731</v>
@@ -21713,7 +21713,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G736" t="n">
-        <v>11.1462078094482</v>
+        <v>11.1462097167969</v>
       </c>
       <c r="H736" t="n">
         <v>4410</v>
@@ -21742,7 +21742,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G737" t="n">
-        <v>11.1462078094482</v>
+        <v>11.1462097167969</v>
       </c>
       <c r="H737" t="n">
         <v>1530</v>
@@ -21771,7 +21771,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G738" t="n">
-        <v>10.6965065002441</v>
+        <v>10.6965036392212</v>
       </c>
       <c r="H738" t="n">
         <v>4232</v>
@@ -21800,7 +21800,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G739" t="n">
-        <v>10.7607498168945</v>
+        <v>10.7607488632202</v>
       </c>
       <c r="H739" t="n">
         <v>2031</v>
@@ -21916,7 +21916,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G743" t="n">
-        <v>10.9052972793579</v>
+        <v>10.9052953720093</v>
       </c>
       <c r="H743" t="n">
         <v>14592</v>
@@ -21945,7 +21945,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>11.4031810760498</v>
+        <v>11.4031820297241</v>
       </c>
       <c r="H744" t="n">
         <v>13265</v>
@@ -21974,7 +21974,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G745" t="n">
-        <v>11.4834871292114</v>
+        <v>11.4834861755371</v>
       </c>
       <c r="H745" t="n">
         <v>3139</v>
@@ -22032,7 +22032,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G747" t="n">
-        <v>11.8850078582764</v>
+        <v>11.8850059509277</v>
       </c>
       <c r="H747" t="n">
         <v>8408</v>
@@ -22090,7 +22090,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G749" t="n">
-        <v>11.3068161010742</v>
+        <v>11.3068170547485</v>
       </c>
       <c r="H749" t="n">
         <v>34959</v>
@@ -22119,7 +22119,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G750" t="n">
-        <v>11.3871212005615</v>
+        <v>11.3871202468872</v>
       </c>
       <c r="H750" t="n">
         <v>3534</v>
@@ -22148,7 +22148,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G751" t="n">
-        <v>11.6922779083252</v>
+        <v>11.6922760009766</v>
       </c>
       <c r="H751" t="n">
         <v>7133</v>
@@ -22177,7 +22177,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G752" t="n">
-        <v>11.7404594421387</v>
+        <v>11.7404584884644</v>
       </c>
       <c r="H752" t="n">
         <v>11202</v>
@@ -22206,7 +22206,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>11.4031810760498</v>
+        <v>11.4031820297241</v>
       </c>
       <c r="H753" t="n">
         <v>7600</v>
@@ -22264,7 +22264,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G755" t="n">
-        <v>11.6280326843262</v>
+        <v>11.6280336380005</v>
       </c>
       <c r="H755" t="n">
         <v>1664</v>
@@ -22322,7 +22322,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G757" t="n">
-        <v>11.8689441680908</v>
+        <v>11.8689460754395</v>
       </c>
       <c r="H757" t="n">
         <v>3327</v>
@@ -22438,7 +22438,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G761" t="n">
-        <v>11.8850078582764</v>
+        <v>11.8850059509277</v>
       </c>
       <c r="H761" t="n">
         <v>2532</v>
@@ -22467,7 +22467,7 @@
         <v>14.5</v>
       </c>
       <c r="G762" t="n">
-        <v>11.6440944671631</v>
+        <v>11.6440935134888</v>
       </c>
       <c r="H762" t="n">
         <v>2418</v>
@@ -22496,7 +22496,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G763" t="n">
-        <v>11.9492483139038</v>
+        <v>11.9492492675781</v>
       </c>
       <c r="H763" t="n">
         <v>3819</v>
@@ -22728,7 +22728,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G771" t="n">
-        <v>12.4150133132935</v>
+        <v>12.4150142669678</v>
       </c>
       <c r="H771" t="n">
         <v>2007</v>
@@ -22757,7 +22757,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G772" t="n">
-        <v>12.4310741424561</v>
+        <v>12.4310731887817</v>
       </c>
       <c r="H772" t="n">
         <v>1674</v>
@@ -22786,7 +22786,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G773" t="n">
-        <v>12.6559267044067</v>
+        <v>12.6559257507324</v>
       </c>
       <c r="H773" t="n">
         <v>2828</v>
@@ -22815,7 +22815,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G774" t="n">
-        <v>12.6398639678955</v>
+        <v>12.6398649215698</v>
       </c>
       <c r="H774" t="n">
         <v>2439</v>
@@ -22844,7 +22844,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G775" t="n">
-        <v>12.4150133132935</v>
+        <v>12.4150142669678</v>
       </c>
       <c r="H775" t="n">
         <v>3615</v>
@@ -22931,7 +22931,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>12.206223487854</v>
+        <v>12.2062215805054</v>
       </c>
       <c r="H778" t="n">
         <v>2250</v>
@@ -22960,7 +22960,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G779" t="n">
-        <v>12.3186483383179</v>
+        <v>12.3186473846436</v>
       </c>
       <c r="H779" t="n">
         <v>3772</v>
@@ -23018,7 +23018,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G781" t="n">
-        <v>12.2865257263184</v>
+        <v>12.2865266799927</v>
       </c>
       <c r="H781" t="n">
         <v>815</v>
@@ -23047,7 +23047,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>12.125919342041</v>
+        <v>12.1259183883667</v>
       </c>
       <c r="H782" t="n">
         <v>2837</v>
@@ -23134,7 +23134,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G785" t="n">
-        <v>12.2865257263184</v>
+        <v>12.2865266799927</v>
       </c>
       <c r="H785" t="n">
         <v>1480</v>
@@ -23221,7 +23221,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G788" t="n">
-        <v>12.2383432388306</v>
+        <v>12.2383441925049</v>
       </c>
       <c r="H788" t="n">
         <v>33</v>
@@ -23366,7 +23366,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>12.125919342041</v>
+        <v>12.1259183883667</v>
       </c>
       <c r="H793" t="n">
         <v>8861</v>
@@ -23395,7 +23395,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G794" t="n">
-        <v>12.1580410003662</v>
+        <v>12.1580390930176</v>
       </c>
       <c r="H794" t="n">
         <v>3981</v>
@@ -23424,7 +23424,7 @@
         <v>15</v>
       </c>
       <c r="G795" t="n">
-        <v>12.045615196228</v>
+        <v>12.0456142425537</v>
       </c>
       <c r="H795" t="n">
         <v>412</v>
@@ -23453,7 +23453,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>12.125919342041</v>
+        <v>12.1259183883667</v>
       </c>
       <c r="H796" t="n">
         <v>652</v>
@@ -23540,7 +23540,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G799" t="n">
-        <v>12.2383432388306</v>
+        <v>12.2383441925049</v>
       </c>
       <c r="H799" t="n">
         <v>324</v>
@@ -23569,7 +23569,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G800" t="n">
-        <v>12.3347082138062</v>
+        <v>12.3347091674805</v>
       </c>
       <c r="H800" t="n">
         <v>805</v>
@@ -23656,7 +23656,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G803" t="n">
-        <v>12.2383432388306</v>
+        <v>12.2383441925049</v>
       </c>
       <c r="H803" t="n">
         <v>9071</v>
@@ -23685,7 +23685,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G804" t="n">
-        <v>12.4631967544556</v>
+        <v>12.4631958007812</v>
       </c>
       <c r="H804" t="n">
         <v>2852</v>
@@ -23801,7 +23801,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G808" t="n">
-        <v>12.4150133132935</v>
+        <v>12.4150142669678</v>
       </c>
       <c r="H808" t="n">
         <v>299</v>
@@ -23830,7 +23830,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G809" t="n">
-        <v>12.4310741424561</v>
+        <v>12.4310731887817</v>
       </c>
       <c r="H809" t="n">
         <v>355</v>
@@ -23859,7 +23859,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G810" t="n">
-        <v>12.3347082138062</v>
+        <v>12.3347091674805</v>
       </c>
       <c r="H810" t="n">
         <v>1305</v>
@@ -23917,7 +23917,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>12.125919342041</v>
+        <v>12.1259183883667</v>
       </c>
       <c r="H812" t="n">
         <v>3825</v>
@@ -23946,7 +23946,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G813" t="n">
-        <v>12.0295524597168</v>
+        <v>12.0295543670654</v>
       </c>
       <c r="H813" t="n">
         <v>751</v>
@@ -24004,7 +24004,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G815" t="n">
-        <v>12.3989515304565</v>
+        <v>12.3989524841309</v>
       </c>
       <c r="H815" t="n">
         <v>1817</v>
@@ -24033,7 +24033,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>12.2865257263184</v>
+        <v>12.2865266799927</v>
       </c>
       <c r="H816" t="n">
         <v>407</v>
@@ -24091,7 +24091,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G818" t="n">
-        <v>12.3989515304565</v>
+        <v>12.3989524841309</v>
       </c>
       <c r="H818" t="n">
         <v>2316</v>
@@ -24149,7 +24149,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G820" t="n">
-        <v>12.8325929641724</v>
+        <v>12.832594871521</v>
       </c>
       <c r="H820" t="n">
         <v>5200</v>
@@ -24178,7 +24178,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G821" t="n">
-        <v>13.057445526123</v>
+        <v>13.0574464797974</v>
       </c>
       <c r="H821" t="n">
         <v>33150</v>
@@ -24207,7 +24207,7 @@
         <v>16.5</v>
       </c>
       <c r="G822" t="n">
-        <v>13.2501754760742</v>
+        <v>13.2501764297485</v>
       </c>
       <c r="H822" t="n">
         <v>7501</v>
@@ -24236,7 +24236,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>13.0092649459839</v>
+        <v>13.0092639923096</v>
       </c>
       <c r="H823" t="n">
         <v>15368</v>
@@ -24265,7 +24265,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G824" t="n">
-        <v>13.1216888427734</v>
+        <v>13.1216897964478</v>
       </c>
       <c r="H824" t="n">
         <v>8538</v>
@@ -24323,7 +24323,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G826" t="n">
-        <v>12.8647174835205</v>
+        <v>12.8647165298462</v>
       </c>
       <c r="H826" t="n">
         <v>3098</v>
@@ -24352,7 +24352,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G827" t="n">
-        <v>12.8647174835205</v>
+        <v>12.8647165298462</v>
       </c>
       <c r="H827" t="n">
         <v>2014</v>
@@ -24381,7 +24381,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G828" t="n">
-        <v>12.9771413803101</v>
+        <v>12.9771423339844</v>
       </c>
       <c r="H828" t="n">
         <v>1278</v>
@@ -24410,7 +24410,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G829" t="n">
-        <v>13.0092649459839</v>
+        <v>13.0092639923096</v>
       </c>
       <c r="H829" t="n">
         <v>15135</v>
@@ -24439,7 +24439,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G830" t="n">
-        <v>12.8968372344971</v>
+        <v>12.8968381881714</v>
       </c>
       <c r="H830" t="n">
         <v>8421</v>
@@ -24497,7 +24497,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G832" t="n">
-        <v>13.0735082626343</v>
+        <v>13.0735063552856</v>
       </c>
       <c r="H832" t="n">
         <v>8485</v>
@@ -24526,7 +24526,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G833" t="n">
-        <v>13.1538095474243</v>
+        <v>13.1538105010986</v>
       </c>
       <c r="H833" t="n">
         <v>9552</v>
@@ -24555,7 +24555,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G834" t="n">
-        <v>12.8165340423584</v>
+        <v>12.8165330886841</v>
       </c>
       <c r="H834" t="n">
         <v>10366</v>
@@ -24613,7 +24613,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G836" t="n">
-        <v>12.9610815048218</v>
+        <v>12.9610795974731</v>
       </c>
       <c r="H836" t="n">
         <v>8853</v>
@@ -24642,7 +24642,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G837" t="n">
-        <v>13.057445526123</v>
+        <v>13.0574464797974</v>
       </c>
       <c r="H837" t="n">
         <v>17047</v>
@@ -24671,7 +24671,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G838" t="n">
-        <v>12.9289588928223</v>
+        <v>12.9289598464966</v>
       </c>
       <c r="H838" t="n">
         <v>509</v>
@@ -24700,7 +24700,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G839" t="n">
-        <v>12.6559267044067</v>
+        <v>12.6559257507324</v>
       </c>
       <c r="H839" t="n">
         <v>12183</v>
@@ -24816,7 +24816,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G843" t="n">
-        <v>12.3989515304565</v>
+        <v>12.3989524841309</v>
       </c>
       <c r="H843" t="n">
         <v>1601</v>
@@ -24845,7 +24845,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G844" t="n">
-        <v>12.6238040924072</v>
+        <v>12.6238050460815</v>
       </c>
       <c r="H844" t="n">
         <v>9977</v>
@@ -24903,7 +24903,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G846" t="n">
-        <v>12.5595607757568</v>
+        <v>12.5595626831055</v>
       </c>
       <c r="H846" t="n">
         <v>717</v>
@@ -24932,7 +24932,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G847" t="n">
-        <v>12.6559267044067</v>
+        <v>12.6559257507324</v>
       </c>
       <c r="H847" t="n">
         <v>706</v>
@@ -25135,7 +25135,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G854" t="n">
-        <v>12.3186483383179</v>
+        <v>12.3186473846436</v>
       </c>
       <c r="H854" t="n">
         <v>1051</v>
@@ -25222,7 +25222,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G857" t="n">
-        <v>11.9813709259033</v>
+        <v>11.9813718795776</v>
       </c>
       <c r="H857" t="n">
         <v>1172</v>
@@ -25251,7 +25251,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G858" t="n">
-        <v>11.9813709259033</v>
+        <v>11.9813718795776</v>
       </c>
       <c r="H858" t="n">
         <v>9798</v>
@@ -25280,7 +25280,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G859" t="n">
-        <v>11.8689441680908</v>
+        <v>11.8689460754395</v>
       </c>
       <c r="H859" t="n">
         <v>2240</v>
@@ -25367,7 +25367,7 @@
         <v>14.5</v>
       </c>
       <c r="G862" t="n">
-        <v>11.6440944671631</v>
+        <v>11.6440935134888</v>
       </c>
       <c r="H862" t="n">
         <v>9312</v>
@@ -25396,7 +25396,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G863" t="n">
-        <v>12.2200384140015</v>
+        <v>12.2200393676758</v>
       </c>
       <c r="H863" t="n">
         <v>3725</v>
@@ -25425,7 +25425,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G864" t="n">
-        <v>12.0530977249146</v>
+        <v>12.0530967712402</v>
       </c>
       <c r="H864" t="n">
         <v>2617</v>
@@ -25483,7 +25483,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G866" t="n">
-        <v>11.7192163467407</v>
+        <v>11.7192182540894</v>
       </c>
       <c r="H866" t="n">
         <v>6056</v>
@@ -25599,7 +25599,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G870" t="n">
-        <v>11.7192163467407</v>
+        <v>11.7192182540894</v>
       </c>
       <c r="H870" t="n">
         <v>8692</v>
@@ -25657,7 +25657,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G872" t="n">
-        <v>11.6190528869629</v>
+        <v>11.6190519332886</v>
       </c>
       <c r="H872" t="n">
         <v>4224</v>
@@ -25918,7 +25918,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G881" t="n">
-        <v>12.0530977249146</v>
+        <v>12.0530967712402</v>
       </c>
       <c r="H881" t="n">
         <v>728</v>
@@ -26063,7 +26063,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G886" t="n">
-        <v>11.6357479095459</v>
+        <v>11.6357460021973</v>
       </c>
       <c r="H886" t="n">
         <v>3471</v>
@@ -26092,7 +26092,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G887" t="n">
-        <v>11.5522756576538</v>
+        <v>11.5522766113281</v>
       </c>
       <c r="H887" t="n">
         <v>1540</v>
@@ -26121,7 +26121,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G888" t="n">
-        <v>11.4020290374756</v>
+        <v>11.4020299911499</v>
       </c>
       <c r="H888" t="n">
         <v>8012</v>
@@ -26150,7 +26150,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G889" t="n">
-        <v>11.6190528869629</v>
+        <v>11.6190519332886</v>
       </c>
       <c r="H889" t="n">
         <v>7228</v>
@@ -26179,7 +26179,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G890" t="n">
-        <v>11.702522277832</v>
+        <v>11.7025241851807</v>
       </c>
       <c r="H890" t="n">
         <v>2642</v>
@@ -26237,7 +26237,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G892" t="n">
-        <v>12.2868146896362</v>
+        <v>12.2868156433105</v>
       </c>
       <c r="H892" t="n">
         <v>3875</v>
@@ -26382,7 +26382,7 @@
         <v>14.5</v>
       </c>
       <c r="G897" t="n">
-        <v>12.1031808853149</v>
+        <v>12.1031799316406</v>
       </c>
       <c r="H897" t="n">
         <v>10711</v>
@@ -26411,7 +26411,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G898" t="n">
-        <v>12.2200384140015</v>
+        <v>12.2200393676758</v>
       </c>
       <c r="H898" t="n">
         <v>1870</v>
@@ -26498,7 +26498,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G901" t="n">
-        <v>12.4370594024658</v>
+        <v>12.4370603561401</v>
       </c>
       <c r="H901" t="n">
         <v>5603</v>
@@ -26527,7 +26527,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G902" t="n">
-        <v>12.4203653335571</v>
+        <v>12.4203672409058</v>
       </c>
       <c r="H902" t="n">
         <v>601</v>
@@ -26672,7 +26672,7 @@
         <v>14.5</v>
       </c>
       <c r="G907" t="n">
-        <v>12.1031808853149</v>
+        <v>12.1031799316406</v>
       </c>
       <c r="H907" t="n">
         <v>963</v>
@@ -26701,7 +26701,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G908" t="n">
-        <v>12.2701206207275</v>
+        <v>12.2701196670532</v>
       </c>
       <c r="H908" t="n">
         <v>8409</v>
@@ -26730,7 +26730,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>12.353590965271</v>
+        <v>12.3535900115967</v>
       </c>
       <c r="H909" t="n">
         <v>387</v>
@@ -26759,7 +26759,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G910" t="n">
-        <v>12.353590965271</v>
+        <v>12.3535900115967</v>
       </c>
       <c r="H910" t="n">
         <v>80</v>
@@ -26846,7 +26846,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G913" t="n">
-        <v>12.2868146896362</v>
+        <v>12.2868156433105</v>
       </c>
       <c r="H913" t="n">
         <v>1510</v>
@@ -26875,7 +26875,7 @@
         <v>14.5</v>
       </c>
       <c r="G914" t="n">
-        <v>12.1031808853149</v>
+        <v>12.1031799316406</v>
       </c>
       <c r="H914" t="n">
         <v>1463</v>
@@ -26904,7 +26904,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G915" t="n">
-        <v>11.6190528869629</v>
+        <v>11.6190519332886</v>
       </c>
       <c r="H915" t="n">
         <v>12167</v>
@@ -26991,7 +26991,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G918" t="n">
-        <v>11.5355825424194</v>
+        <v>11.5355815887451</v>
       </c>
       <c r="H918" t="n">
         <v>1539</v>
@@ -27020,7 +27020,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G919" t="n">
-        <v>11.235089302063</v>
+        <v>11.2350883483887</v>
       </c>
       <c r="H919" t="n">
         <v>2073</v>
@@ -27107,7 +27107,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>11.1850080490112</v>
+        <v>11.1850070953369</v>
       </c>
       <c r="H922" t="n">
         <v>1721</v>
@@ -27136,7 +27136,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G923" t="n">
-        <v>11.5021944046021</v>
+        <v>11.5021953582764</v>
       </c>
       <c r="H923" t="n">
         <v>11826</v>
@@ -27165,7 +27165,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G924" t="n">
-        <v>11.5689706802368</v>
+        <v>11.5689697265625</v>
       </c>
       <c r="H924" t="n">
         <v>2893</v>
@@ -27223,7 +27223,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G926" t="n">
-        <v>11.702522277832</v>
+        <v>11.7025241851807</v>
       </c>
       <c r="H926" t="n">
         <v>10</v>
@@ -27339,7 +27339,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G930" t="n">
-        <v>11.3018655776978</v>
+        <v>11.3018665313721</v>
       </c>
       <c r="H930" t="n">
         <v>26239</v>
@@ -27397,7 +27397,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G932" t="n">
-        <v>11.4521131515503</v>
+        <v>11.4521112442017</v>
       </c>
       <c r="H932" t="n">
         <v>300</v>
@@ -27484,7 +27484,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G935" t="n">
-        <v>11.235089302063</v>
+        <v>11.2350883483887</v>
       </c>
       <c r="H935" t="n">
         <v>3146</v>
@@ -27513,7 +27513,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>11.1850080490112</v>
+        <v>11.1850070953369</v>
       </c>
       <c r="H936" t="n">
         <v>1522</v>
@@ -27600,7 +27600,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>11.1850080490112</v>
+        <v>11.1850070953369</v>
       </c>
       <c r="H939" t="n">
         <v>2926</v>
@@ -27629,7 +27629,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G940" t="n">
-        <v>11.2851724624634</v>
+        <v>11.2851734161377</v>
       </c>
       <c r="H940" t="n">
         <v>990</v>
@@ -27687,7 +27687,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>11.1850080490112</v>
+        <v>11.1850070953369</v>
       </c>
       <c r="H942" t="n">
         <v>2523</v>
@@ -27832,7 +27832,7 @@
         <v>13</v>
       </c>
       <c r="G947" t="n">
-        <v>10.8511266708374</v>
+        <v>10.8511257171631</v>
       </c>
       <c r="H947" t="n">
         <v>4999</v>
@@ -27890,7 +27890,7 @@
         <v>13</v>
       </c>
       <c r="G949" t="n">
-        <v>10.8511266708374</v>
+        <v>10.8511257171631</v>
       </c>
       <c r="H949" t="n">
         <v>2160</v>
@@ -27919,7 +27919,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>10.9345979690552</v>
+        <v>10.9345970153809</v>
       </c>
       <c r="H950" t="n">
         <v>11227</v>
@@ -28006,7 +28006,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G953" t="n">
-        <v>10.9345979690552</v>
+        <v>10.9345970153809</v>
       </c>
       <c r="H953" t="n">
         <v>1862</v>
@@ -28035,7 +28035,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G954" t="n">
-        <v>10.9179019927979</v>
+        <v>10.9179039001465</v>
       </c>
       <c r="H954" t="n">
         <v>889</v>
@@ -28064,7 +28064,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G955" t="n">
-        <v>10.9345979690552</v>
+        <v>10.9345970153809</v>
       </c>
       <c r="H955" t="n">
         <v>763</v>
@@ -28151,7 +28151,7 @@
         <v>13</v>
       </c>
       <c r="G958" t="n">
-        <v>10.8511266708374</v>
+        <v>10.8511257171631</v>
       </c>
       <c r="H958" t="n">
         <v>1510</v>
@@ -28180,7 +28180,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G959" t="n">
-        <v>10.9345979690552</v>
+        <v>10.9345970153809</v>
       </c>
       <c r="H959" t="n">
         <v>3358</v>
@@ -28412,7 +28412,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G967" t="n">
-        <v>10.4170818328857</v>
+        <v>10.4170808792114</v>
       </c>
       <c r="H967" t="n">
         <v>4723</v>
@@ -28441,7 +28441,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G968" t="n">
-        <v>10.5172462463379</v>
+        <v>10.5172472000122</v>
       </c>
       <c r="H968" t="n">
         <v>373</v>
@@ -28528,7 +28528,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G971" t="n">
-        <v>10.383692741394</v>
+        <v>10.3836936950684</v>
       </c>
       <c r="H971" t="n">
         <v>5479</v>
@@ -28586,7 +28586,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>10.1666717529297</v>
+        <v>10.166672706604</v>
       </c>
       <c r="H973" t="n">
         <v>3344</v>
@@ -28615,7 +28615,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G974" t="n">
-        <v>10.1499767303467</v>
+        <v>10.149977684021</v>
       </c>
       <c r="H974" t="n">
         <v>1750</v>
@@ -28644,7 +28644,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G975" t="n">
-        <v>10.0832004547119</v>
+        <v>10.0832014083862</v>
       </c>
       <c r="H975" t="n">
         <v>6489</v>
@@ -28673,7 +28673,7 @@
         <v>12</v>
       </c>
       <c r="G976" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164232254028</v>
       </c>
       <c r="H976" t="n">
         <v>10308</v>
@@ -28702,7 +28702,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G977" t="n">
-        <v>10.2167530059814</v>
+        <v>10.2167520523071</v>
       </c>
       <c r="H977" t="n">
         <v>1828</v>
@@ -28731,7 +28731,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G978" t="n">
-        <v>10.333610534668</v>
+        <v>10.3336114883423</v>
       </c>
       <c r="H978" t="n">
         <v>2415</v>
@@ -28760,7 +28760,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G979" t="n">
-        <v>10.7008800506592</v>
+        <v>10.7008810043335</v>
       </c>
       <c r="H979" t="n">
         <v>6485</v>
@@ -28818,7 +28818,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G981" t="n">
-        <v>10.5172462463379</v>
+        <v>10.5172472000122</v>
       </c>
       <c r="H981" t="n">
         <v>3272</v>
@@ -28847,7 +28847,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G982" t="n">
-        <v>10.600715637207</v>
+        <v>10.6007165908813</v>
       </c>
       <c r="H982" t="n">
         <v>3441</v>
@@ -28876,7 +28876,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G983" t="n">
-        <v>10.5339393615723</v>
+        <v>10.5339403152466</v>
       </c>
       <c r="H983" t="n">
         <v>1814</v>
@@ -28934,7 +28934,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G985" t="n">
-        <v>10.5339393615723</v>
+        <v>10.5339403152466</v>
       </c>
       <c r="H985" t="n">
         <v>7371</v>
@@ -28992,7 +28992,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G987" t="n">
-        <v>10.600715637207</v>
+        <v>10.6007165908813</v>
       </c>
       <c r="H987" t="n">
         <v>2372</v>
@@ -29021,7 +29021,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G988" t="n">
-        <v>10.5506343841553</v>
+        <v>10.550633430481</v>
       </c>
       <c r="H988" t="n">
         <v>2213</v>
@@ -29166,7 +29166,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G993" t="n">
-        <v>10.5506343841553</v>
+        <v>10.550633430481</v>
       </c>
       <c r="H993" t="n">
         <v>213</v>
@@ -29224,7 +29224,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G995" t="n">
-        <v>10.5339393615723</v>
+        <v>10.5339403152466</v>
       </c>
       <c r="H995" t="n">
         <v>10390</v>
@@ -29282,7 +29282,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G997" t="n">
-        <v>10.6341037750244</v>
+        <v>10.6341028213501</v>
       </c>
       <c r="H997" t="n">
         <v>7089</v>
@@ -29340,7 +29340,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>10.5172462463379</v>
+        <v>10.5172472000122</v>
       </c>
       <c r="H999" t="n">
         <v>28574</v>
@@ -29369,7 +29369,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>10.5172462463379</v>
+        <v>10.5172472000122</v>
       </c>
       <c r="H1000" t="n">
         <v>13370</v>
@@ -29398,7 +29398,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1001" t="n">
-        <v>10.5172462463379</v>
+        <v>10.5172472000122</v>
       </c>
       <c r="H1001" t="n">
         <v>9377</v>
@@ -29427,7 +29427,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1002" t="n">
-        <v>11.21839427948</v>
+        <v>11.2183952331543</v>
       </c>
       <c r="H1002" t="n">
         <v>48955</v>
@@ -29514,7 +29514,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1005" t="n">
-        <v>11.4354190826416</v>
+        <v>11.435417175293</v>
       </c>
       <c r="H1005" t="n">
         <v>6551</v>
@@ -29543,7 +29543,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1006" t="n">
-        <v>11.5355825424194</v>
+        <v>11.5355815887451</v>
       </c>
       <c r="H1006" t="n">
         <v>4158</v>
@@ -29630,7 +29630,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1009" t="n">
-        <v>11.4354190826416</v>
+        <v>11.435417175293</v>
       </c>
       <c r="H1009" t="n">
         <v>2711</v>
@@ -29659,7 +29659,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1010" t="n">
-        <v>11.4020290374756</v>
+        <v>11.4020299911499</v>
       </c>
       <c r="H1010" t="n">
         <v>4622</v>
@@ -29775,7 +29775,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1014" t="n">
-        <v>11.3018655776978</v>
+        <v>11.3018665313721</v>
       </c>
       <c r="H1014" t="n">
         <v>830</v>
@@ -29804,7 +29804,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1015" t="n">
-        <v>11.1850080490112</v>
+        <v>11.1850070953369</v>
       </c>
       <c r="H1015" t="n">
         <v>2786</v>
@@ -29833,7 +29833,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1016" t="n">
-        <v>11.5355825424194</v>
+        <v>11.5355815887451</v>
       </c>
       <c r="H1016" t="n">
         <v>26434</v>
@@ -29862,7 +29862,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1017" t="n">
-        <v>11.5689706802368</v>
+        <v>11.5689697265625</v>
       </c>
       <c r="H1017" t="n">
         <v>7961</v>
@@ -30065,7 +30065,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1024" t="n">
-        <v>11.5522756576538</v>
+        <v>11.5522766113281</v>
       </c>
       <c r="H1024" t="n">
         <v>5480</v>
@@ -30123,7 +30123,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1026" t="n">
-        <v>11.3018655776978</v>
+        <v>11.3018665313721</v>
       </c>
       <c r="H1026" t="n">
         <v>9833</v>
@@ -30181,7 +30181,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1028" t="n">
-        <v>11.5021944046021</v>
+        <v>11.5021953582764</v>
       </c>
       <c r="H1028" t="n">
         <v>1927</v>
@@ -30239,7 +30239,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G1030" t="n">
-        <v>11.4688062667847</v>
+        <v>11.468807220459</v>
       </c>
       <c r="H1030" t="n">
         <v>602</v>
@@ -30268,7 +30268,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1031" t="n">
-        <v>11.4020290374756</v>
+        <v>11.4020299911499</v>
       </c>
       <c r="H1031" t="n">
         <v>1496</v>
@@ -30297,7 +30297,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1032" t="n">
-        <v>11.4354190826416</v>
+        <v>11.435417175293</v>
       </c>
       <c r="H1032" t="n">
         <v>3187</v>
@@ -30442,7 +30442,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1037" t="n">
-        <v>11.0514545440674</v>
+        <v>11.0514535903931</v>
       </c>
       <c r="H1037" t="n">
         <v>4522</v>
@@ -30471,7 +30471,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1038" t="n">
-        <v>11.0180683135986</v>
+        <v>11.01806640625</v>
       </c>
       <c r="H1038" t="n">
         <v>1255</v>
@@ -30500,7 +30500,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>11.1015367507935</v>
+        <v>11.1015386581421</v>
       </c>
       <c r="H1039" t="n">
         <v>666</v>
@@ -30529,7 +30529,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1040" t="n">
-        <v>11.1015367507935</v>
+        <v>11.1015386581421</v>
       </c>
       <c r="H1040" t="n">
         <v>3834</v>
@@ -30558,7 +30558,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1041" t="n">
-        <v>11.1015367507935</v>
+        <v>11.1015386581421</v>
       </c>
       <c r="H1041" t="n">
         <v>703</v>
@@ -30616,7 +30616,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1043" t="n">
-        <v>11.2017011642456</v>
+        <v>11.2017021179199</v>
       </c>
       <c r="H1043" t="n">
         <v>10534</v>
@@ -30906,7 +30906,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1053" t="n">
-        <v>11.3018655776978</v>
+        <v>11.3018665313721</v>
       </c>
       <c r="H1053" t="n">
         <v>14855</v>
@@ -30993,7 +30993,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1056" t="n">
-        <v>10.600715637207</v>
+        <v>10.6007165908813</v>
       </c>
       <c r="H1056" t="n">
         <v>6271</v>
@@ -31022,7 +31022,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1057" t="n">
-        <v>10.383692741394</v>
+        <v>10.3836936950684</v>
       </c>
       <c r="H1057" t="n">
         <v>12567</v>
@@ -31051,7 +31051,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1058" t="n">
-        <v>10.333610534668</v>
+        <v>10.3336114883423</v>
       </c>
       <c r="H1058" t="n">
         <v>13328</v>
@@ -31080,7 +31080,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.5339393615723</v>
+        <v>10.5339403152466</v>
       </c>
       <c r="H1059" t="n">
         <v>9369</v>
@@ -31109,7 +31109,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.2668371200562</v>
+        <v>10.2668361663818</v>
       </c>
       <c r="H1060" t="n">
         <v>12496</v>
@@ -31138,7 +31138,7 @@
         <v>12</v>
       </c>
       <c r="G1061" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164232254028</v>
       </c>
       <c r="H1061" t="n">
         <v>7373</v>
@@ -31225,7 +31225,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1064" t="n">
-        <v>8.66420745849609</v>
+        <v>8.66420841217041</v>
       </c>
       <c r="H1064" t="n">
         <v>15377</v>
@@ -31254,7 +31254,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1065" t="n">
-        <v>8.6141242980957</v>
+        <v>8.61412715911865</v>
       </c>
       <c r="H1065" t="n">
         <v>3639</v>
@@ -31312,7 +31312,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.66420745849609</v>
+        <v>8.66420841217041</v>
       </c>
       <c r="H1067" t="n">
         <v>6786</v>
@@ -31341,7 +31341,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1068" t="n">
-        <v>7.84619808197021</v>
+        <v>7.84619998931885</v>
       </c>
       <c r="H1068" t="n">
         <v>4271</v>
@@ -31428,7 +31428,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G1071" t="n">
-        <v>8.10495758056641</v>
+        <v>8.10495662689209</v>
       </c>
       <c r="H1071" t="n">
         <v>5706</v>
@@ -31457,7 +31457,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1072" t="n">
-        <v>8.18008041381836</v>
+        <v>8.18008136749268</v>
       </c>
       <c r="H1072" t="n">
         <v>3034</v>
@@ -31515,7 +31515,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1074" t="n">
-        <v>7.97140598297119</v>
+        <v>7.97140550613403</v>
       </c>
       <c r="H1074" t="n">
         <v>23115</v>
@@ -31544,7 +31544,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1075" t="n">
-        <v>7.97975158691406</v>
+        <v>7.97975254058838</v>
       </c>
       <c r="H1075" t="n">
         <v>5777</v>
@@ -31573,7 +31573,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1076" t="n">
-        <v>7.97140598297119</v>
+        <v>7.97140550613403</v>
       </c>
       <c r="H1076" t="n">
         <v>2832</v>
@@ -31660,7 +31660,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1079" t="n">
-        <v>7.946364402771</v>
+        <v>7.94636344909668</v>
       </c>
       <c r="H1079" t="n">
         <v>4659</v>
@@ -31776,7 +31776,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>8.28024578094482</v>
+        <v>8.28024482727051</v>
       </c>
       <c r="H1083" t="n">
         <v>10652</v>
@@ -31805,7 +31805,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1084" t="n">
-        <v>8.33032703399658</v>
+        <v>8.33032608032227</v>
       </c>
       <c r="H1084" t="n">
         <v>11957</v>
@@ -31834,7 +31834,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.31363296508789</v>
+        <v>8.31363201141357</v>
       </c>
       <c r="H1085" t="n">
         <v>1440</v>
@@ -31950,7 +31950,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.38875484466553</v>
+        <v>8.38875579833984</v>
       </c>
       <c r="H1089" t="n">
         <v>6721</v>
@@ -31979,7 +31979,7 @@
         <v>10</v>
       </c>
       <c r="G1090" t="n">
-        <v>8.34702110290527</v>
+        <v>8.34702014923096</v>
       </c>
       <c r="H1090" t="n">
         <v>1670</v>
@@ -32008,7 +32008,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>8.4722261428833</v>
+        <v>8.47222518920898</v>
       </c>
       <c r="H1091" t="n">
         <v>162</v>
@@ -32037,7 +32037,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1092" t="n">
-        <v>8.80610752105713</v>
+        <v>8.80610656738281</v>
       </c>
       <c r="H1092" t="n">
         <v>3130</v>
@@ -32066,7 +32066,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1093" t="n">
-        <v>8.80610752105713</v>
+        <v>8.80610656738281</v>
       </c>
       <c r="H1093" t="n">
         <v>3641</v>
@@ -32095,7 +32095,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1094" t="n">
-        <v>8.68090152740479</v>
+        <v>8.68089962005615</v>
       </c>
       <c r="H1094" t="n">
         <v>4252</v>
@@ -32124,7 +32124,7 @@
         <v>10.5</v>
       </c>
       <c r="G1095" t="n">
-        <v>8.76437187194824</v>
+        <v>8.76437091827393</v>
       </c>
       <c r="H1095" t="n">
         <v>589</v>
@@ -32153,7 +32153,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>8.8478422164917</v>
+        <v>8.84784317016602</v>
       </c>
       <c r="H1096" t="n">
         <v>1866</v>
@@ -32269,7 +32269,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1100" t="n">
-        <v>8.93131256103516</v>
+        <v>8.93131160736084</v>
       </c>
       <c r="H1100" t="n">
         <v>2494</v>
@@ -32356,7 +32356,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1103" t="n">
-        <v>8.68090152740479</v>
+        <v>8.68089962005615</v>
       </c>
       <c r="H1103" t="n">
         <v>2194</v>
@@ -32414,7 +32414,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1105" t="n">
-        <v>8.4722261428833</v>
+        <v>8.47222518920898</v>
       </c>
       <c r="H1105" t="n">
         <v>4137</v>
@@ -32443,7 +32443,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1106" t="n">
-        <v>8.4722261428833</v>
+        <v>8.47222518920898</v>
       </c>
       <c r="H1106" t="n">
         <v>3978</v>
@@ -32501,7 +32501,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1108" t="n">
-        <v>8.4722261428833</v>
+        <v>8.47222518920898</v>
       </c>
       <c r="H1108" t="n">
         <v>4096</v>
@@ -32530,7 +32530,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.38875484466553</v>
+        <v>8.38875579833984</v>
       </c>
       <c r="H1109" t="n">
         <v>636</v>
@@ -32559,7 +32559,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1110" t="n">
-        <v>8.38875484466553</v>
+        <v>8.38875579833984</v>
       </c>
       <c r="H1110" t="n">
         <v>4352</v>
@@ -32617,7 +32617,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1112" t="n">
-        <v>8.16338634490967</v>
+        <v>8.16338539123535</v>
       </c>
       <c r="H1112" t="n">
         <v>5199</v>
@@ -32646,7 +32646,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1113" t="n">
-        <v>8.18008041381836</v>
+        <v>8.18008136749268</v>
       </c>
       <c r="H1113" t="n">
         <v>4115</v>
@@ -32791,7 +32791,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>8.4722261428833</v>
+        <v>8.47222518920898</v>
       </c>
       <c r="H1118" t="n">
         <v>20052</v>
@@ -32849,7 +32849,7 @@
         <v>10.75</v>
       </c>
       <c r="G1120" t="n">
-        <v>8.97304725646973</v>
+        <v>8.97304630279541</v>
       </c>
       <c r="H1120" t="n">
         <v>30143</v>
@@ -32965,7 +32965,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1124" t="n">
-        <v>9.43213367462158</v>
+        <v>9.4321346282959</v>
       </c>
       <c r="H1124" t="n">
         <v>9637</v>
@@ -32994,7 +32994,7 @@
         <v>11.5</v>
       </c>
       <c r="G1125" t="n">
-        <v>9.59907531738281</v>
+        <v>9.59907341003418</v>
       </c>
       <c r="H1125" t="n">
         <v>7846</v>
@@ -33023,7 +33023,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>9.68254470825195</v>
+        <v>9.68254375457764</v>
       </c>
       <c r="H1126" t="n">
         <v>24070</v>
@@ -33052,7 +33052,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1127" t="n">
-        <v>9.43213367462158</v>
+        <v>9.4321346282959</v>
       </c>
       <c r="H1127" t="n">
         <v>6547</v>
@@ -33081,7 +33081,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1128" t="n">
-        <v>9.43213367462158</v>
+        <v>9.4321346282959</v>
       </c>
       <c r="H1128" t="n">
         <v>11792</v>
@@ -33168,7 +33168,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>9.68254470825195</v>
+        <v>9.68254375457764</v>
       </c>
       <c r="H1131" t="n">
         <v>7529</v>
@@ -33197,7 +33197,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1132" t="n">
-        <v>9.64081001281738</v>
+        <v>9.64080905914307</v>
       </c>
       <c r="H1132" t="n">
         <v>1910</v>
@@ -33226,7 +33226,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1133" t="n">
-        <v>9.68254470825195</v>
+        <v>9.68254375457764</v>
       </c>
       <c r="H1133" t="n">
         <v>2518</v>
@@ -33255,7 +33255,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1134" t="n">
-        <v>9.55733966827393</v>
+        <v>9.55733776092529</v>
       </c>
       <c r="H1134" t="n">
         <v>3097</v>
@@ -33342,7 +33342,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1137" t="n">
-        <v>9.43213367462158</v>
+        <v>9.4321346282959</v>
       </c>
       <c r="H1137" t="n">
         <v>2150</v>
@@ -33371,7 +33371,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1138" t="n">
-        <v>9.34866428375244</v>
+        <v>9.34866333007812</v>
       </c>
       <c r="H1138" t="n">
         <v>2993</v>
@@ -33400,7 +33400,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1139" t="n">
-        <v>9.34866428375244</v>
+        <v>9.34866333007812</v>
       </c>
       <c r="H1139" t="n">
         <v>10011</v>
@@ -33458,7 +33458,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1141" t="n">
-        <v>9.22345733642578</v>
+        <v>9.2234582901001</v>
       </c>
       <c r="H1141" t="n">
         <v>9914</v>
@@ -33545,7 +33545,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1144" t="n">
-        <v>9.22345733642578</v>
+        <v>9.2234582901001</v>
       </c>
       <c r="H1144" t="n">
         <v>4146</v>
@@ -33632,7 +33632,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1147" t="n">
-        <v>9.34866428375244</v>
+        <v>9.34866333007812</v>
       </c>
       <c r="H1147" t="n">
         <v>1716</v>
@@ -33748,7 +33748,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1151" t="n">
-        <v>9.43213367462158</v>
+        <v>9.4321346282959</v>
       </c>
       <c r="H1151" t="n">
         <v>3373</v>
@@ -33806,7 +33806,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1153" t="n">
-        <v>9.43213367462158</v>
+        <v>9.4321346282959</v>
       </c>
       <c r="H1153" t="n">
         <v>15926</v>
@@ -33835,7 +33835,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1154" t="n">
-        <v>9.55733966827393</v>
+        <v>9.55733776092529</v>
       </c>
       <c r="H1154" t="n">
         <v>13519</v>
@@ -33864,7 +33864,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1155" t="n">
-        <v>9.76601314544678</v>
+        <v>9.76601409912109</v>
       </c>
       <c r="H1155" t="n">
         <v>8079</v>
@@ -33893,7 +33893,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1156" t="n">
-        <v>9.55733966827393</v>
+        <v>9.55733776092529</v>
       </c>
       <c r="H1156" t="n">
         <v>9249</v>
@@ -33922,7 +33922,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1157" t="n">
-        <v>9.34866428375244</v>
+        <v>9.34866333007812</v>
       </c>
       <c r="H1157" t="n">
         <v>11746</v>
@@ -33980,7 +33980,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1159" t="n">
-        <v>9.43213367462158</v>
+        <v>9.4321346282959</v>
       </c>
       <c r="H1159" t="n">
         <v>1058</v>
@@ -34009,7 +34009,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1160" t="n">
-        <v>9.34866428375244</v>
+        <v>9.34866333007812</v>
       </c>
       <c r="H1160" t="n">
         <v>1440</v>
@@ -34038,7 +34038,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1161" t="n">
-        <v>9.34866428375244</v>
+        <v>9.34866333007812</v>
       </c>
       <c r="H1161" t="n">
         <v>1490</v>
@@ -34067,7 +34067,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1162" t="n">
-        <v>9.22345733642578</v>
+        <v>9.2234582901001</v>
       </c>
       <c r="H1162" t="n">
         <v>4292</v>
@@ -34096,7 +34096,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1163" t="n">
-        <v>9.34866428375244</v>
+        <v>9.34866333007812</v>
       </c>
       <c r="H1163" t="n">
         <v>2719</v>
@@ -34125,7 +34125,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1164" t="n">
-        <v>9.22345733642578</v>
+        <v>9.2234582901001</v>
       </c>
       <c r="H1164" t="n">
         <v>2370</v>
@@ -34154,7 +34154,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>9.34866428375244</v>
+        <v>9.34866333007812</v>
       </c>
       <c r="H1165" t="n">
         <v>1482</v>
@@ -34183,7 +34183,7 @@
         <v>11.5</v>
       </c>
       <c r="G1166" t="n">
-        <v>9.59907531738281</v>
+        <v>9.59907341003418</v>
       </c>
       <c r="H1166" t="n">
         <v>2282</v>
@@ -34212,7 +34212,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1167" t="n">
-        <v>9.84948444366455</v>
+        <v>9.84948539733887</v>
       </c>
       <c r="H1167" t="n">
         <v>6576</v>
@@ -34241,7 +34241,7 @@
         <v>12</v>
       </c>
       <c r="G1168" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164232254028</v>
       </c>
       <c r="H1168" t="n">
         <v>46586</v>
@@ -34270,7 +34270,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>10.0998964309692</v>
+        <v>10.0998954772949</v>
       </c>
       <c r="H1169" t="n">
         <v>154870</v>
@@ -34299,7 +34299,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1170" t="n">
-        <v>10.475510597229</v>
+        <v>10.4755125045776</v>
       </c>
       <c r="H1170" t="n">
         <v>12346</v>
@@ -34415,7 +34415,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1174" t="n">
-        <v>10.475510597229</v>
+        <v>10.4755125045776</v>
       </c>
       <c r="H1174" t="n">
         <v>4354</v>
@@ -34444,7 +34444,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1175" t="n">
-        <v>10.3085708618164</v>
+        <v>10.3085699081421</v>
       </c>
       <c r="H1175" t="n">
         <v>4032</v>
@@ -34502,7 +34502,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.058159828186</v>
+        <v>10.0581607818604</v>
       </c>
       <c r="H1177" t="n">
         <v>3813</v>
@@ -34560,7 +34560,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1179" t="n">
-        <v>9.93295478820801</v>
+        <v>9.93295383453369</v>
       </c>
       <c r="H1179" t="n">
         <v>7550</v>
@@ -34589,7 +34589,7 @@
         <v>12</v>
       </c>
       <c r="G1180" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164232254028</v>
       </c>
       <c r="H1180" t="n">
         <v>4852</v>
@@ -34618,7 +34618,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>10.0998964309692</v>
+        <v>10.0998954772949</v>
       </c>
       <c r="H1181" t="n">
         <v>12510</v>
@@ -34647,7 +34647,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1182" t="n">
-        <v>10.058159828186</v>
+        <v>10.0581607818604</v>
       </c>
       <c r="H1182" t="n">
         <v>13318</v>
@@ -34676,7 +34676,7 @@
         <v>12</v>
       </c>
       <c r="G1183" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164232254028</v>
       </c>
       <c r="H1183" t="n">
         <v>5640</v>
@@ -34705,7 +34705,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1184" t="n">
-        <v>10.058159828186</v>
+        <v>10.0581607818604</v>
       </c>
       <c r="H1184" t="n">
         <v>1979</v>
@@ -34734,7 +34734,7 @@
         <v>12</v>
       </c>
       <c r="G1185" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164232254028</v>
       </c>
       <c r="H1185" t="n">
         <v>5958</v>
@@ -34763,7 +34763,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1186" t="n">
-        <v>10.0998964309692</v>
+        <v>10.0998954772949</v>
       </c>
       <c r="H1186" t="n">
         <v>629</v>
@@ -34792,7 +34792,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1187" t="n">
-        <v>10.058159828186</v>
+        <v>10.0581607818604</v>
       </c>
       <c r="H1187" t="n">
         <v>363</v>
@@ -34821,7 +34821,7 @@
         <v>12</v>
       </c>
       <c r="G1188" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164232254028</v>
       </c>
       <c r="H1188" t="n">
         <v>2912</v>
@@ -34850,7 +34850,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1189" t="n">
-        <v>10.0998964309692</v>
+        <v>10.0998954772949</v>
       </c>
       <c r="H1189" t="n">
         <v>6099</v>
@@ -34937,7 +34937,7 @@
         <v>12</v>
       </c>
       <c r="G1192" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164232254028</v>
       </c>
       <c r="H1192" t="n">
         <v>2116</v>
@@ -34966,7 +34966,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1193" t="n">
-        <v>10.058159828186</v>
+        <v>10.0581607818604</v>
       </c>
       <c r="H1193" t="n">
         <v>2336</v>
@@ -34995,7 +34995,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1194" t="n">
-        <v>10.0998964309692</v>
+        <v>10.0998954772949</v>
       </c>
       <c r="H1194" t="n">
         <v>809</v>
@@ -35024,7 +35024,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1195" t="n">
-        <v>10.0998964309692</v>
+        <v>10.0998954772949</v>
       </c>
       <c r="H1195" t="n">
         <v>1</v>
@@ -35053,7 +35053,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1196" t="n">
-        <v>9.93295478820801</v>
+        <v>9.93295383453369</v>
       </c>
       <c r="H1196" t="n">
         <v>2178</v>
@@ -35082,7 +35082,7 @@
         <v>12</v>
       </c>
       <c r="G1197" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164232254028</v>
       </c>
       <c r="H1197" t="n">
         <v>3494</v>
@@ -35140,7 +35140,7 @@
         <v>12</v>
       </c>
       <c r="G1199" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164232254028</v>
       </c>
       <c r="H1199" t="n">
         <v>1926</v>
@@ -35169,7 +35169,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1200" t="n">
-        <v>9.93295478820801</v>
+        <v>9.93295383453369</v>
       </c>
       <c r="H1200" t="n">
         <v>2638</v>
@@ -35198,7 +35198,7 @@
         <v>12</v>
       </c>
       <c r="G1201" t="n">
-        <v>10.0164251327515</v>
+        <v>10.0164232254028</v>
       </c>
       <c r="H1201" t="n">
         <v>255</v>
@@ -35227,7 +35227,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1202" t="n">
-        <v>10.058159828186</v>
+        <v>10.0581607818604</v>
       </c>
       <c r="H1202" t="n">
         <v>3494</v>
@@ -35256,7 +35256,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1203" t="n">
-        <v>10.475510597229</v>
+        <v>10.4755125045776</v>
       </c>
       <c r="H1203" t="n">
         <v>9397</v>
@@ -35285,7 +35285,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1204" t="n">
-        <v>10.5172462463379</v>
+        <v>10.5172472000122</v>
       </c>
       <c r="H1204" t="n">
         <v>6497</v>
@@ -35401,7 +35401,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1208" t="n">
-        <v>10.8093919754028</v>
+        <v>10.8093910217285</v>
       </c>
       <c r="H1208" t="n">
         <v>2158</v>
@@ -35430,7 +35430,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1209" t="n">
-        <v>11.0180683135986</v>
+        <v>11.01806640625</v>
       </c>
       <c r="H1209" t="n">
         <v>13216</v>
@@ -35459,7 +35459,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1210" t="n">
-        <v>10.9763326644897</v>
+        <v>10.9763317108154</v>
       </c>
       <c r="H1210" t="n">
         <v>5745</v>
@@ -35488,7 +35488,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1211" t="n">
-        <v>11.5188884735107</v>
+        <v>11.5188894271851</v>
       </c>
       <c r="H1211" t="n">
         <v>53658</v>
@@ -35662,7 +35662,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1217" t="n">
-        <v>11.5125141143799</v>
+        <v>11.5125131607056</v>
       </c>
       <c r="H1217" t="n">
         <v>24338</v>
@@ -35894,7 +35894,7 @@
         <v>13</v>
       </c>
       <c r="G1225" t="n">
-        <v>11.1273384094238</v>
+        <v>11.1273365020752</v>
       </c>
       <c r="H1225" t="n">
         <v>9975</v>
@@ -35981,7 +35981,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1228" t="n">
-        <v>10.1001987457275</v>
+        <v>10.1001996994019</v>
       </c>
       <c r="H1228" t="n">
         <v>7794</v>
@@ -36010,7 +36010,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1229" t="n">
-        <v>10.1001987457275</v>
+        <v>10.1001996994019</v>
       </c>
       <c r="H1229" t="n">
         <v>2173</v>
@@ -36039,7 +36039,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>10.5709714889526</v>
+        <v>10.5709705352783</v>
       </c>
       <c r="H1230" t="n">
         <v>3566</v>
@@ -36068,7 +36068,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1231" t="n">
-        <v>10.4425773620605</v>
+        <v>10.4425783157349</v>
       </c>
       <c r="H1231" t="n">
         <v>2053</v>
@@ -36155,7 +36155,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>10.6137676239014</v>
+        <v>10.6137685775757</v>
       </c>
       <c r="H1234" t="n">
         <v>1169</v>
@@ -36242,7 +36242,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1237" t="n">
-        <v>11.6837034225464</v>
+        <v>11.6837043762207</v>
       </c>
       <c r="H1237" t="n">
         <v>8256</v>
@@ -36271,7 +36271,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1238" t="n">
-        <v>11.7265024185181</v>
+        <v>11.7265005111694</v>
       </c>
       <c r="H1238" t="n">
         <v>10921</v>
@@ -36300,7 +36300,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1239" t="n">
-        <v>11.8120975494385</v>
+        <v>11.8120965957642</v>
       </c>
       <c r="H1239" t="n">
         <v>15218</v>
@@ -36416,7 +36416,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1243" t="n">
-        <v>11.5125141143799</v>
+        <v>11.5125131607056</v>
       </c>
       <c r="H1243" t="n">
         <v>10071</v>
@@ -36445,7 +36445,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1244" t="n">
-        <v>11.8120975494385</v>
+        <v>11.8120965957642</v>
       </c>
       <c r="H1244" t="n">
         <v>10091</v>
@@ -36474,7 +36474,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>11.6837034225464</v>
+        <v>11.6837043762207</v>
       </c>
       <c r="H1245" t="n">
         <v>3727</v>
@@ -36532,7 +36532,7 @@
         <v>13</v>
       </c>
       <c r="G1247" t="n">
-        <v>11.1273384094238</v>
+        <v>11.1273365020752</v>
       </c>
       <c r="H1247" t="n">
         <v>13029</v>
@@ -36561,7 +36561,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1248" t="n">
-        <v>11.2985277175903</v>
+        <v>11.298526763916</v>
       </c>
       <c r="H1248" t="n">
         <v>5444</v>
@@ -36619,7 +36619,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1250" t="n">
-        <v>11.2985277175903</v>
+        <v>11.298526763916</v>
       </c>
       <c r="H1250" t="n">
         <v>3466</v>
@@ -36822,7 +36822,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1257" t="n">
-        <v>12.3684635162354</v>
+        <v>12.368462562561</v>
       </c>
       <c r="H1257" t="n">
         <v>21463</v>
@@ -36909,7 +36909,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>13.1816158294678</v>
+        <v>13.1816148757935</v>
       </c>
       <c r="H1260" t="n">
         <v>18198</v>
@@ -36938,7 +36938,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1261" t="n">
-        <v>13.1816158294678</v>
+        <v>13.1816148757935</v>
       </c>
       <c r="H1261" t="n">
         <v>7835</v>
@@ -37054,7 +37054,7 @@
         <v>15</v>
       </c>
       <c r="G1265" t="n">
-        <v>12.8392353057861</v>
+        <v>12.8392362594604</v>
       </c>
       <c r="H1265" t="n">
         <v>7835</v>
@@ -37083,7 +37083,7 @@
         <v>15</v>
       </c>
       <c r="G1266" t="n">
-        <v>12.8392353057861</v>
+        <v>12.8392362594604</v>
       </c>
       <c r="H1266" t="n">
         <v>7398</v>
@@ -37112,7 +37112,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>13.1816158294678</v>
+        <v>13.1816148757935</v>
       </c>
       <c r="H1267" t="n">
         <v>3935</v>
@@ -37141,7 +37141,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1268" t="n">
-        <v>13.3956031799316</v>
+        <v>13.3956022262573</v>
       </c>
       <c r="H1268" t="n">
         <v>5679</v>
@@ -37228,7 +37228,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>12.7108449935913</v>
+        <v>12.7108430862427</v>
       </c>
       <c r="H1271" t="n">
         <v>8018</v>
@@ -37286,7 +37286,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1273" t="n">
-        <v>13.096019744873</v>
+        <v>13.0960206985474</v>
       </c>
       <c r="H1273" t="n">
         <v>4480</v>
@@ -37373,7 +37373,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1276" t="n">
-        <v>13.1816158294678</v>
+        <v>13.1816148757935</v>
       </c>
       <c r="H1276" t="n">
         <v>6956</v>
@@ -37489,7 +37489,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1280" t="n">
-        <v>14.0375642776489</v>
+        <v>14.0375633239746</v>
       </c>
       <c r="H1280" t="n">
         <v>96511</v>
@@ -37576,7 +37576,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1283" t="n">
-        <v>14.2943496704102</v>
+        <v>14.2943487167358</v>
       </c>
       <c r="H1283" t="n">
         <v>12050</v>
@@ -37605,7 +37605,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1284" t="n">
-        <v>14.4655389785767</v>
+        <v>14.465537071228</v>
       </c>
       <c r="H1284" t="n">
         <v>11199</v>
@@ -37663,7 +37663,7 @@
         <v>16.5</v>
       </c>
       <c r="G1286" t="n">
-        <v>14.1231603622437</v>
+        <v>14.1231594085693</v>
       </c>
       <c r="H1286" t="n">
         <v>6800</v>
@@ -37779,7 +37779,7 @@
         <v>16.5</v>
       </c>
       <c r="G1290" t="n">
-        <v>14.1231603622437</v>
+        <v>14.1231594085693</v>
       </c>
       <c r="H1290" t="n">
         <v>7589</v>
@@ -37808,7 +37808,7 @@
         <v>17</v>
       </c>
       <c r="G1291" t="n">
-        <v>14.5511350631714</v>
+        <v>14.5511341094971</v>
       </c>
       <c r="H1291" t="n">
         <v>17665</v>
@@ -37837,7 +37837,7 @@
         <v>17.75</v>
       </c>
       <c r="G1292" t="n">
-        <v>15.1930961608887</v>
+        <v>15.19309425354</v>
       </c>
       <c r="H1292" t="n">
         <v>28793</v>
@@ -37895,7 +37895,7 @@
         <v>18</v>
       </c>
       <c r="G1294" t="n">
-        <v>15.4070835113525</v>
+        <v>15.4070825576782</v>
       </c>
       <c r="H1294" t="n">
         <v>7300</v>
@@ -37924,7 +37924,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1295" t="n">
-        <v>15.7066669464111</v>
+        <v>15.7066679000854</v>
       </c>
       <c r="H1295" t="n">
         <v>17672</v>
@@ -38011,7 +38011,7 @@
         <v>18.75</v>
       </c>
       <c r="G1298" t="n">
-        <v>16.0490455627441</v>
+        <v>16.0490436553955</v>
       </c>
       <c r="H1298" t="n">
         <v>22745</v>
@@ -38301,7 +38301,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1308" t="n">
-        <v>17.8037414550781</v>
+        <v>17.8037376403809</v>
       </c>
       <c r="H1308" t="n">
         <v>17211</v>
@@ -38359,7 +38359,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1310" t="n">
-        <v>16.0062503814697</v>
+        <v>16.0062484741211</v>
       </c>
       <c r="H1310" t="n">
         <v>42308</v>
@@ -38417,7 +38417,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1312" t="n">
-        <v>16.8621978759766</v>
+        <v>16.8621959686279</v>
       </c>
       <c r="H1312" t="n">
         <v>20354</v>
@@ -38504,7 +38504,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1315" t="n">
-        <v>17.8037414550781</v>
+        <v>17.8037376403809</v>
       </c>
       <c r="H1315" t="n">
         <v>27947</v>
@@ -38533,7 +38533,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1316" t="n">
-        <v>17.8037414550781</v>
+        <v>17.8037376403809</v>
       </c>
       <c r="H1316" t="n">
         <v>12313</v>
@@ -38678,7 +38678,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1321" t="n">
-        <v>17.2045745849609</v>
+        <v>17.2045764923096</v>
       </c>
       <c r="H1321" t="n">
         <v>4688</v>
@@ -38794,7 +38794,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1325" t="n">
-        <v>17.2045745849609</v>
+        <v>17.2045764923096</v>
       </c>
       <c r="H1325" t="n">
         <v>6859</v>
@@ -38881,7 +38881,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1328" t="n">
-        <v>18.2317161560059</v>
+        <v>18.2317142486572</v>
       </c>
       <c r="H1328" t="n">
         <v>72182</v>
@@ -38910,7 +38910,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1329" t="n">
-        <v>19.3444480895996</v>
+        <v>19.3444499969482</v>
       </c>
       <c r="H1329" t="n">
         <v>106445</v>
@@ -38939,7 +38939,7 @@
         <v>23</v>
       </c>
       <c r="G1330" t="n">
-        <v>19.6868286132812</v>
+        <v>19.6868267059326</v>
       </c>
       <c r="H1330" t="n">
         <v>54575</v>
@@ -38968,7 +38968,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1331" t="n">
-        <v>19.772424697876</v>
+        <v>19.7724227905273</v>
       </c>
       <c r="H1331" t="n">
         <v>31059</v>
@@ -38997,7 +38997,7 @@
         <v>23.5</v>
       </c>
       <c r="G1332" t="n">
-        <v>20.1148052215576</v>
+        <v>20.1148014068604</v>
       </c>
       <c r="H1332" t="n">
         <v>27330</v>
@@ -39026,7 +39026,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>19.9436111450195</v>
+        <v>19.9436092376709</v>
       </c>
       <c r="H1333" t="n">
         <v>15836</v>
@@ -39055,7 +39055,7 @@
         <v>23.5</v>
       </c>
       <c r="G1334" t="n">
-        <v>20.1148052215576</v>
+        <v>20.1148014068604</v>
       </c>
       <c r="H1334" t="n">
         <v>9762</v>
@@ -39084,7 +39084,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1335" t="n">
-        <v>20.2003974914551</v>
+        <v>20.2003993988037</v>
       </c>
       <c r="H1335" t="n">
         <v>16834</v>
@@ -39113,7 +39113,7 @@
         <v>23.5</v>
       </c>
       <c r="G1336" t="n">
-        <v>20.1148052215576</v>
+        <v>20.1148014068604</v>
       </c>
       <c r="H1336" t="n">
         <v>12232</v>
@@ -39142,7 +39142,7 @@
         <v>23</v>
       </c>
       <c r="G1337" t="n">
-        <v>19.6868286132812</v>
+        <v>19.6868267059326</v>
       </c>
       <c r="H1337" t="n">
         <v>8454</v>
@@ -39171,7 +39171,7 @@
         <v>22.5</v>
       </c>
       <c r="G1338" t="n">
-        <v>19.2588539123535</v>
+        <v>19.2588520050049</v>
       </c>
       <c r="H1338" t="n">
         <v>33692</v>
@@ -39200,7 +39200,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1339" t="n">
-        <v>19.3444480895996</v>
+        <v>19.3444499969482</v>
       </c>
       <c r="H1339" t="n">
         <v>16518</v>
@@ -39229,7 +39229,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1340" t="n">
-        <v>19.3444480895996</v>
+        <v>19.3444499969482</v>
       </c>
       <c r="H1340" t="n">
         <v>5695</v>
@@ -39258,7 +39258,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1341" t="n">
-        <v>19.1732597351074</v>
+        <v>19.1732578277588</v>
       </c>
       <c r="H1341" t="n">
         <v>4895</v>
@@ -39316,7 +39316,7 @@
         <v>22.5</v>
       </c>
       <c r="G1343" t="n">
-        <v>19.2588539123535</v>
+        <v>19.2588520050049</v>
       </c>
       <c r="H1343" t="n">
         <v>12812</v>
@@ -39345,7 +39345,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1344" t="n">
-        <v>19.1732597351074</v>
+        <v>19.1732578277588</v>
       </c>
       <c r="H1344" t="n">
         <v>9559</v>
@@ -39374,7 +39374,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1345" t="n">
-        <v>19.4300441741943</v>
+        <v>19.430046081543</v>
       </c>
       <c r="H1345" t="n">
         <v>8019</v>
@@ -39403,7 +39403,7 @@
         <v>21.5</v>
       </c>
       <c r="G1346" t="n">
-        <v>18.402904510498</v>
+        <v>18.4029026031494</v>
       </c>
       <c r="H1346" t="n">
         <v>17880</v>
@@ -39461,7 +39461,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1348" t="n">
-        <v>18.7452850341797</v>
+        <v>18.7452831268311</v>
       </c>
       <c r="H1348" t="n">
         <v>10424</v>
@@ -39519,7 +39519,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1350" t="n">
-        <v>19.1732597351074</v>
+        <v>19.1732578277588</v>
       </c>
       <c r="H1350" t="n">
         <v>6638</v>
@@ -39548,7 +39548,7 @@
         <v>23</v>
       </c>
       <c r="G1351" t="n">
-        <v>19.6868286132812</v>
+        <v>19.6868267059326</v>
       </c>
       <c r="H1351" t="n">
         <v>7787</v>
@@ -39577,7 +39577,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1352" t="n">
-        <v>19.4300441741943</v>
+        <v>19.430046081543</v>
       </c>
       <c r="H1352" t="n">
         <v>11192</v>
@@ -39606,7 +39606,7 @@
         <v>22.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>19.2588539123535</v>
+        <v>19.2588520050049</v>
       </c>
       <c r="H1353" t="n">
         <v>5112</v>
@@ -39664,7 +39664,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1355" t="n">
-        <v>19.4300441741943</v>
+        <v>19.430046081543</v>
       </c>
       <c r="H1355" t="n">
         <v>10678</v>
@@ -39722,7 +39722,7 @@
         <v>22</v>
       </c>
       <c r="G1357" t="n">
-        <v>18.8308811187744</v>
+        <v>18.8308792114258</v>
       </c>
       <c r="H1357" t="n">
         <v>6465</v>
@@ -39751,7 +39751,7 @@
         <v>21.5</v>
       </c>
       <c r="G1358" t="n">
-        <v>18.402904510498</v>
+        <v>18.4029026031494</v>
       </c>
       <c r="H1358" t="n">
         <v>18338</v>
@@ -39809,7 +39809,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1360" t="n">
-        <v>18.2317161560059</v>
+        <v>18.2317142486572</v>
       </c>
       <c r="H1360" t="n">
         <v>26182</v>
@@ -39838,7 +39838,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1361" t="n">
-        <v>18.7452850341797</v>
+        <v>18.7452831268311</v>
       </c>
       <c r="H1361" t="n">
         <v>11869</v>
@@ -39867,7 +39867,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1362" t="n">
-        <v>20.2003974914551</v>
+        <v>20.2003993988037</v>
       </c>
       <c r="H1362" t="n">
         <v>49903</v>
@@ -39896,7 +39896,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1363" t="n">
-        <v>19.9436111450195</v>
+        <v>19.9436092376709</v>
       </c>
       <c r="H1363" t="n">
         <v>35290</v>
@@ -39925,7 +39925,7 @@
         <v>23</v>
       </c>
       <c r="G1364" t="n">
-        <v>19.6868286132812</v>
+        <v>19.6868267059326</v>
       </c>
       <c r="H1364" t="n">
         <v>22052</v>
@@ -39954,7 +39954,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1365" t="n">
-        <v>19.8580169677734</v>
+        <v>19.8580188751221</v>
       </c>
       <c r="H1365" t="n">
         <v>8145</v>
@@ -40012,7 +40012,7 @@
         <v>24</v>
       </c>
       <c r="G1367" t="n">
-        <v>20.5427780151367</v>
+        <v>20.5427742004395</v>
       </c>
       <c r="H1367" t="n">
         <v>36680</v>
@@ -40041,7 +40041,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1368" t="n">
-        <v>20.4571838378906</v>
+        <v>20.457181930542</v>
       </c>
       <c r="H1368" t="n">
         <v>35409</v>
@@ -40128,7 +40128,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1371" t="n">
-        <v>21.1419429779053</v>
+        <v>21.1419410705566</v>
       </c>
       <c r="H1371" t="n">
         <v>37830</v>
@@ -40157,7 +40157,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1372" t="n">
-        <v>20.8851547241211</v>
+        <v>20.8851566314697</v>
       </c>
       <c r="H1372" t="n">
         <v>33182</v>
@@ -40186,7 +40186,7 @@
         <v>25.5</v>
       </c>
       <c r="G1373" t="n">
-        <v>21.8267021179199</v>
+        <v>21.8266983032227</v>
       </c>
       <c r="H1373" t="n">
         <v>62996</v>
@@ -40273,7 +40273,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1376" t="n">
-        <v>23.0077056884766</v>
+        <v>23.0077037811279</v>
       </c>
       <c r="H1376" t="n">
         <v>20151</v>
@@ -40302,7 +40302,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1377" t="n">
-        <v>22.8327407836914</v>
+        <v>22.83274269104</v>
       </c>
       <c r="H1377" t="n">
         <v>23527</v>
@@ -40389,7 +40389,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>24.407413482666</v>
+        <v>24.4074115753174</v>
       </c>
       <c r="H1380" t="n">
         <v>38724</v>
@@ -40505,7 +40505,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1384" t="n">
-        <v>23.3576335906982</v>
+        <v>23.3576316833496</v>
       </c>
       <c r="H1384" t="n">
         <v>14143</v>
@@ -40650,7 +40650,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1389" t="n">
-        <v>23.0077056884766</v>
+        <v>23.0077037811279</v>
       </c>
       <c r="H1389" t="n">
         <v>14174</v>
@@ -40766,7 +40766,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1393" t="n">
-        <v>23.0077056884766</v>
+        <v>23.0077037811279</v>
       </c>
       <c r="H1393" t="n">
         <v>5779</v>
@@ -40882,7 +40882,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>23.0077056884766</v>
+        <v>23.0077037811279</v>
       </c>
       <c r="H1397" t="n">
         <v>10286</v>
@@ -40911,7 +40911,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1398" t="n">
-        <v>23.0077056884766</v>
+        <v>23.0077037811279</v>
       </c>
       <c r="H1398" t="n">
         <v>6704</v>
@@ -40969,7 +40969,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>23.3576335906982</v>
+        <v>23.3576316833496</v>
       </c>
       <c r="H1400" t="n">
         <v>18372</v>
@@ -41027,7 +41027,7 @@
         <v>26</v>
       </c>
       <c r="G1402" t="n">
-        <v>22.7452602386475</v>
+        <v>22.7452583312988</v>
       </c>
       <c r="H1402" t="n">
         <v>10864</v>
@@ -41259,7 +41259,7 @@
         <v>25</v>
       </c>
       <c r="G1410" t="n">
-        <v>21.8704395294189</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1410" t="n">
         <v>11069</v>
@@ -41346,7 +41346,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>23.0077056884766</v>
+        <v>23.0077037811279</v>
       </c>
       <c r="H1413" t="n">
         <v>9509</v>
@@ -41375,7 +41375,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1414" t="n">
-        <v>23.0077056884766</v>
+        <v>23.0077037811279</v>
       </c>
       <c r="H1414" t="n">
         <v>18045</v>
@@ -41462,7 +41462,7 @@
         <v>26</v>
       </c>
       <c r="G1417" t="n">
-        <v>22.7452602386475</v>
+        <v>22.7452583312988</v>
       </c>
       <c r="H1417" t="n">
         <v>12511</v>
@@ -41549,7 +41549,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1420" t="n">
-        <v>23.3576335906982</v>
+        <v>23.3576316833496</v>
       </c>
       <c r="H1420" t="n">
         <v>34491</v>
@@ -41607,7 +41607,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>23.0077056884766</v>
+        <v>23.0077037811279</v>
       </c>
       <c r="H1422" t="n">
         <v>23041</v>
@@ -41636,7 +41636,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1423" t="n">
-        <v>23.0077056884766</v>
+        <v>23.0077037811279</v>
       </c>
       <c r="H1423" t="n">
         <v>11195</v>
@@ -41694,7 +41694,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1425" t="n">
-        <v>23.0077056884766</v>
+        <v>23.0077037811279</v>
       </c>
       <c r="H1425" t="n">
         <v>9938</v>
@@ -41781,7 +41781,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1428" t="n">
-        <v>23.0077056884766</v>
+        <v>23.0077037811279</v>
       </c>
       <c r="H1428" t="n">
         <v>10190</v>
@@ -41926,7 +41926,7 @@
         <v>25</v>
       </c>
       <c r="G1433" t="n">
-        <v>21.8704395294189</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1433" t="n">
         <v>24692</v>
@@ -41955,7 +41955,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1434" t="n">
-        <v>21.7829608917236</v>
+        <v>21.782958984375</v>
       </c>
       <c r="H1434" t="n">
         <v>20712</v>
@@ -42129,7 +42129,7 @@
         <v>25</v>
       </c>
       <c r="G1440" t="n">
-        <v>21.8704395294189</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1440" t="n">
         <v>8043</v>
@@ -42158,7 +42158,7 @@
         <v>25</v>
       </c>
       <c r="G1441" t="n">
-        <v>21.8704395294189</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1441" t="n">
         <v>9219</v>
@@ -42187,7 +42187,7 @@
         <v>25</v>
       </c>
       <c r="G1442" t="n">
-        <v>21.8704395294189</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1442" t="n">
         <v>4835</v>
@@ -42216,7 +42216,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1443" t="n">
-        <v>21.7829608917236</v>
+        <v>21.782958984375</v>
       </c>
       <c r="H1443" t="n">
         <v>3557</v>
@@ -42332,7 +42332,7 @@
         <v>25</v>
       </c>
       <c r="G1447" t="n">
-        <v>21.8704395294189</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1447" t="n">
         <v>11669</v>
@@ -42448,7 +42448,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>21.0831069946289</v>
+        <v>21.0831089019775</v>
       </c>
       <c r="H1451" t="n">
         <v>18355</v>
@@ -42477,7 +42477,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1452" t="n">
-        <v>21.1705894470215</v>
+        <v>21.1705875396729</v>
       </c>
       <c r="H1452" t="n">
         <v>9099</v>
@@ -42506,7 +42506,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1453" t="n">
-        <v>21.1705894470215</v>
+        <v>21.1705875396729</v>
       </c>
       <c r="H1453" t="n">
         <v>6065</v>
@@ -42564,7 +42564,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>20.6456985473633</v>
+        <v>20.6457004547119</v>
       </c>
       <c r="H1455" t="n">
         <v>11687</v>
@@ -42825,7 +42825,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1464" t="n">
-        <v>19.0710258483887</v>
+        <v>19.07102394104</v>
       </c>
       <c r="H1464" t="n">
         <v>36416</v>
@@ -42854,7 +42854,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1465" t="n">
-        <v>18.9835433959961</v>
+        <v>18.9835453033447</v>
       </c>
       <c r="H1465" t="n">
         <v>21119</v>
@@ -42883,7 +42883,7 @@
         <v>21.5</v>
       </c>
       <c r="G1466" t="n">
-        <v>18.8085803985596</v>
+        <v>18.8085784912109</v>
       </c>
       <c r="H1466" t="n">
         <v>14370</v>
@@ -42941,7 +42941,7 @@
         <v>21.5</v>
       </c>
       <c r="G1468" t="n">
-        <v>18.8085803985596</v>
+        <v>18.8085784912109</v>
       </c>
       <c r="H1468" t="n">
         <v>10972</v>
@@ -43028,7 +43028,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1471" t="n">
-        <v>21.0831069946289</v>
+        <v>21.0831089019775</v>
       </c>
       <c r="H1471" t="n">
         <v>46178</v>
@@ -43057,7 +43057,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1472" t="n">
-        <v>21.0831069946289</v>
+        <v>21.0831089019775</v>
       </c>
       <c r="H1472" t="n">
         <v>161358</v>
@@ -43289,7 +43289,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1480" t="n">
-        <v>23.3576335906982</v>
+        <v>23.3576316833496</v>
       </c>
       <c r="H1480" t="n">
         <v>41421</v>
@@ -43376,7 +43376,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1483" t="n">
-        <v>24.3199329376221</v>
+        <v>24.3199310302734</v>
       </c>
       <c r="H1483" t="n">
         <v>40447</v>
@@ -43434,7 +43434,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1485" t="n">
-        <v>24.5823783874512</v>
+        <v>24.5823764801025</v>
       </c>
       <c r="H1485" t="n">
         <v>35322</v>
@@ -43521,7 +43521,7 @@
         <v>28</v>
       </c>
       <c r="G1488" t="n">
-        <v>24.49489402771</v>
+        <v>24.4948959350586</v>
       </c>
       <c r="H1488" t="n">
         <v>22339</v>
@@ -43550,7 +43550,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1489" t="n">
-        <v>24.2324485778809</v>
+        <v>24.2324504852295</v>
       </c>
       <c r="H1489" t="n">
         <v>23588</v>
@@ -43695,7 +43695,7 @@
         <v>26</v>
       </c>
       <c r="G1494" t="n">
-        <v>22.7452602386475</v>
+        <v>22.7452583312988</v>
       </c>
       <c r="H1494" t="n">
         <v>30708</v>
@@ -43782,7 +43782,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>21.5205154418945</v>
+        <v>21.5205173492432</v>
       </c>
       <c r="H1497" t="n">
         <v>10240</v>
@@ -43811,7 +43811,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1498" t="n">
-        <v>21.5205154418945</v>
+        <v>21.5205173492432</v>
       </c>
       <c r="H1498" t="n">
         <v>19785</v>
@@ -43898,7 +43898,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>21.0831069946289</v>
+        <v>21.0831089019775</v>
       </c>
       <c r="H1501" t="n">
         <v>26590</v>
@@ -43956,7 +43956,7 @@
         <v>23</v>
       </c>
       <c r="G1503" t="n">
-        <v>20.1208076477051</v>
+        <v>20.1208057403564</v>
       </c>
       <c r="H1503" t="n">
         <v>14545</v>
@@ -43985,7 +43985,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1504" t="n">
-        <v>20.3832511901855</v>
+        <v>20.3832492828369</v>
       </c>
       <c r="H1504" t="n">
         <v>29092</v>
@@ -44043,7 +44043,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1506" t="n">
-        <v>20.6456985473633</v>
+        <v>20.6457004547119</v>
       </c>
       <c r="H1506" t="n">
         <v>27368</v>
@@ -44072,7 +44072,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1507" t="n">
-        <v>20.2957706451416</v>
+        <v>20.2957725524902</v>
       </c>
       <c r="H1507" t="n">
         <v>8921</v>
@@ -44275,7 +44275,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1514" t="n">
-        <v>19.5959167480469</v>
+        <v>19.5959148406982</v>
       </c>
       <c r="H1514" t="n">
         <v>22878</v>
@@ -44304,7 +44304,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.2957706451416</v>
+        <v>20.2957725524902</v>
       </c>
       <c r="H1515" t="n">
         <v>25381</v>
@@ -44333,7 +44333,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.2957706451416</v>
+        <v>20.2957725524902</v>
       </c>
       <c r="H1516" t="n">
         <v>21959</v>
@@ -44362,7 +44362,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1517" t="n">
-        <v>21.0831069946289</v>
+        <v>21.0831089019775</v>
       </c>
       <c r="H1517" t="n">
         <v>27200</v>
@@ -44391,7 +44391,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.3832511901855</v>
+        <v>20.3832492828369</v>
       </c>
       <c r="H1518" t="n">
         <v>13892</v>
@@ -44449,7 +44449,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1520" t="n">
-        <v>20.2957706451416</v>
+        <v>20.2957725524902</v>
       </c>
       <c r="H1520" t="n">
         <v>7126</v>
@@ -44623,7 +44623,7 @@
         <v>24</v>
       </c>
       <c r="G1526" t="n">
-        <v>20.9956245422363</v>
+        <v>20.9956226348877</v>
       </c>
       <c r="H1526" t="n">
         <v>17158</v>
@@ -44768,7 +44768,7 @@
         <v>24</v>
       </c>
       <c r="G1531" t="n">
-        <v>20.9956245422363</v>
+        <v>20.9956226348877</v>
       </c>
       <c r="H1531" t="n">
         <v>13405</v>
@@ -44797,7 +44797,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1532" t="n">
-        <v>20.2957706451416</v>
+        <v>20.2957725524902</v>
       </c>
       <c r="H1532" t="n">
         <v>22873</v>
@@ -44884,7 +44884,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1535" t="n">
-        <v>21.0831069946289</v>
+        <v>21.0831089019775</v>
       </c>
       <c r="H1535" t="n">
         <v>17158</v>
@@ -45116,7 +45116,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1543" t="n">
-        <v>21.7829608917236</v>
+        <v>21.782958984375</v>
       </c>
       <c r="H1543" t="n">
         <v>36351</v>
@@ -45145,7 +45145,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1544" t="n">
-        <v>21.6954803466797</v>
+        <v>21.6954784393311</v>
       </c>
       <c r="H1544" t="n">
         <v>17470</v>
@@ -45174,7 +45174,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1545" t="n">
-        <v>21.5205154418945</v>
+        <v>21.5205173492432</v>
       </c>
       <c r="H1545" t="n">
         <v>6512</v>
@@ -45232,7 +45232,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1547" t="n">
-        <v>21.5205154418945</v>
+        <v>21.5205173492432</v>
       </c>
       <c r="H1547" t="n">
         <v>8152</v>
@@ -45261,7 +45261,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1548" t="n">
-        <v>21.7829608917236</v>
+        <v>21.782958984375</v>
       </c>
       <c r="H1548" t="n">
         <v>6408</v>
@@ -45290,7 +45290,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1549" t="n">
-        <v>21.7829608917236</v>
+        <v>21.782958984375</v>
       </c>
       <c r="H1549" t="n">
         <v>6399</v>
@@ -45377,7 +45377,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1552" t="n">
-        <v>21.5205154418945</v>
+        <v>21.5205173492432</v>
       </c>
       <c r="H1552" t="n">
         <v>7407</v>
@@ -45406,7 +45406,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1553" t="n">
-        <v>21.5205154418945</v>
+        <v>21.5205173492432</v>
       </c>
       <c r="H1553" t="n">
         <v>6634</v>
@@ -45435,7 +45435,7 @@
         <v>26</v>
       </c>
       <c r="G1554" t="n">
-        <v>22.7452602386475</v>
+        <v>22.7452583312988</v>
       </c>
       <c r="H1554" t="n">
         <v>36776</v>
@@ -45493,7 +45493,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1556" t="n">
-        <v>21.5205154418945</v>
+        <v>21.5205173492432</v>
       </c>
       <c r="H1556" t="n">
         <v>25003</v>
@@ -45725,7 +45725,7 @@
         <v>21</v>
       </c>
       <c r="G1564" t="n">
-        <v>18.3711719512939</v>
+        <v>18.3711700439453</v>
       </c>
       <c r="H1564" t="n">
         <v>20211</v>
@@ -45754,7 +45754,7 @@
         <v>20</v>
       </c>
       <c r="G1565" t="n">
-        <v>17.4963550567627</v>
+        <v>17.4963531494141</v>
       </c>
       <c r="H1565" t="n">
         <v>12776</v>
@@ -45812,7 +45812,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1567" t="n">
-        <v>17.3651313781738</v>
+        <v>17.3651332855225</v>
       </c>
       <c r="H1567" t="n">
         <v>9789</v>
@@ -46044,7 +46044,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1575" t="n">
-        <v>16.0091648101807</v>
+        <v>16.009162902832</v>
       </c>
       <c r="H1575" t="n">
         <v>9583</v>
@@ -46073,7 +46073,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1576" t="n">
-        <v>16.0091648101807</v>
+        <v>16.009162902832</v>
       </c>
       <c r="H1576" t="n">
         <v>10761</v>
@@ -46102,7 +46102,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.9277229309082</v>
+        <v>16.9277248382568</v>
       </c>
       <c r="H1577" t="n">
         <v>14676</v>
@@ -46189,7 +46189,7 @@
         <v>20</v>
       </c>
       <c r="G1580" t="n">
-        <v>17.4963550567627</v>
+        <v>17.4963531494141</v>
       </c>
       <c r="H1580" t="n">
         <v>14947</v>
@@ -46247,7 +46247,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1582" t="n">
-        <v>18.4586524963379</v>
+        <v>18.4586544036865</v>
       </c>
       <c r="H1582" t="n">
         <v>12561</v>
@@ -46392,7 +46392,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1587" t="n">
-        <v>17.6713180541992</v>
+        <v>17.6713199615479</v>
       </c>
       <c r="H1587" t="n">
         <v>10608</v>
@@ -46421,7 +46421,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1588" t="n">
-        <v>18.6336154937744</v>
+        <v>18.633617401123</v>
       </c>
       <c r="H1588" t="n">
         <v>23467</v>
@@ -46479,7 +46479,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1590" t="n">
-        <v>19.5959167480469</v>
+        <v>19.5959148406982</v>
       </c>
       <c r="H1590" t="n">
         <v>43378</v>
@@ -46566,7 +46566,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1593" t="n">
-        <v>21.1705894470215</v>
+        <v>21.1705875396729</v>
       </c>
       <c r="H1593" t="n">
         <v>35100</v>
@@ -46595,7 +46595,7 @@
         <v>24</v>
       </c>
       <c r="G1594" t="n">
-        <v>20.9956245422363</v>
+        <v>20.9956226348877</v>
       </c>
       <c r="H1594" t="n">
         <v>24468</v>
@@ -46682,7 +46682,7 @@
         <v>24</v>
       </c>
       <c r="G1597" t="n">
-        <v>20.9956245422363</v>
+        <v>20.9956226348877</v>
       </c>
       <c r="H1597" t="n">
         <v>10364</v>
@@ -46711,7 +46711,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1598" t="n">
-        <v>21.0831069946289</v>
+        <v>21.0831089019775</v>
       </c>
       <c r="H1598" t="n">
         <v>13544</v>
@@ -46740,7 +46740,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1599" t="n">
-        <v>20.95188331604</v>
+        <v>20.9518852233887</v>
       </c>
       <c r="H1599" t="n">
         <v>20597</v>
@@ -46769,7 +46769,7 @@
         <v>24</v>
       </c>
       <c r="G1600" t="n">
-        <v>20.9956245422363</v>
+        <v>20.9956226348877</v>
       </c>
       <c r="H1600" t="n">
         <v>3923</v>
@@ -46798,7 +46798,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1601" t="n">
-        <v>21.0831069946289</v>
+        <v>21.0831089019775</v>
       </c>
       <c r="H1601" t="n">
         <v>3313</v>
@@ -46827,7 +46827,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1602" t="n">
-        <v>21.0831069946289</v>
+        <v>21.0831089019775</v>
       </c>
       <c r="H1602" t="n">
         <v>3223</v>
@@ -46885,7 +46885,7 @@
         <v>24</v>
       </c>
       <c r="G1604" t="n">
-        <v>20.9956245422363</v>
+        <v>20.9956226348877</v>
       </c>
       <c r="H1604" t="n">
         <v>5931</v>
@@ -46972,7 +46972,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1607" t="n">
-        <v>21.1705894470215</v>
+        <v>21.1705875396729</v>
       </c>
       <c r="H1607" t="n">
         <v>25364</v>
@@ -47001,7 +47001,7 @@
         <v>24</v>
       </c>
       <c r="G1608" t="n">
-        <v>20.9956245422363</v>
+        <v>20.9956226348877</v>
       </c>
       <c r="H1608" t="n">
         <v>5583</v>
@@ -47088,7 +47088,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1611" t="n">
-        <v>21.1705894470215</v>
+        <v>21.1705875396729</v>
       </c>
       <c r="H1611" t="n">
         <v>11238</v>
@@ -47204,7 +47204,7 @@
         <v>24</v>
       </c>
       <c r="G1615" t="n">
-        <v>20.9956245422363</v>
+        <v>20.9956226348877</v>
       </c>
       <c r="H1615" t="n">
         <v>7091</v>
@@ -47233,7 +47233,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1616" t="n">
-        <v>21.5205154418945</v>
+        <v>21.5205173492432</v>
       </c>
       <c r="H1616" t="n">
         <v>6784</v>
@@ -47291,7 +47291,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1618" t="n">
-        <v>21.5205154418945</v>
+        <v>21.5205173492432</v>
       </c>
       <c r="H1618" t="n">
         <v>20358</v>
@@ -47378,7 +47378,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1621" t="n">
-        <v>21.5205154418945</v>
+        <v>21.5205173492432</v>
       </c>
       <c r="H1621" t="n">
         <v>8516</v>
@@ -47436,7 +47436,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1623" t="n">
-        <v>21.6954803466797</v>
+        <v>21.6954784393311</v>
       </c>
       <c r="H1623" t="n">
         <v>13806</v>
@@ -47523,7 +47523,7 @@
         <v>25</v>
       </c>
       <c r="G1626" t="n">
-        <v>21.8704395294189</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1626" t="n">
         <v>10068</v>
@@ -47552,7 +47552,7 @@
         <v>25</v>
       </c>
       <c r="G1627" t="n">
-        <v>21.8704395294189</v>
+        <v>21.8704414367676</v>
       </c>
       <c r="H1627" t="n">
         <v>5138</v>
@@ -80067,6 +80067,35 @@
         <v>13321</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>10.5500001907349</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>10.5500001907349</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>10.5500001907349</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>2237</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>
